--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>77940137</v>
+        <v>125004576</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grunnfossgnollen, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385032.0330319937</v>
+        <v>385935</v>
       </c>
       <c r="R2" t="n">
-        <v>6796918.812237687</v>
+        <v>6796995</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-05-06</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-05-06</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,34 +771,7807 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125004325</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78834</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>385989</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6797025</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125004665</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>385935</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6796995</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125004324</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>385975</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6797012</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125004587</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>385935</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6796995</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125004366</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>385975</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6797012</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125004345</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>385975</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6797012</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125010553</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>385876</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6797310</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125014812</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>385618</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6797202</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125010604</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>385633</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6797363</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125006056</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>385924</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6797115</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125010000</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>385749</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6797429</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125014057</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>385607</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6797159</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125015572</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>385709</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6797118</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125014685</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79892</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>385571</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6797259</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125008506</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>385867</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6797218</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125015566</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>385640</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6797141</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125015347</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>385592</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6797161</v>
+      </c>
+      <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125014011</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56722</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>385610</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6797160</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125009781</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>385862</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6797329</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125008585</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>385867</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6797219</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125015299</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>385588</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6797184</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125014083</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78842</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>185</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>385689</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6797223</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125010560</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>385763</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6797307</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125016901</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>385697</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6796929</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125013949</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>385633</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6797184</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125014817</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79919</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>385541</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6797264</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125011588</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>385737</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6797241</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125014588</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>385586</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6797244</v>
+      </c>
+      <c r="S30" t="n">
+        <v>15</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125014757</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>385618</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6797202</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125009430</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>385862</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6797329</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125015275</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>385609</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6797178</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125015297</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>385569</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6797152</v>
+      </c>
+      <c r="S34" t="n">
+        <v>11</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125015273</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>385579</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6797173</v>
+      </c>
+      <c r="S35" t="n">
+        <v>7</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125013776</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>385692</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6797239</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125009952</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>385760</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6797317</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125010031</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>385750</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6797429</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>125013825</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79892</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>385689</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6797243</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>125009342</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79892</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>385861</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6797324</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>125016771</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>385674</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6796981</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>125010269</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>385756</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6797314</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>125011580</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>385738</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6797251</v>
+      </c>
+      <c r="S43" t="n">
+        <v>11</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>125014099</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78842</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>185</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>385699</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6797223</v>
+      </c>
+      <c r="S44" t="n">
+        <v>11</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>125008003</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>385900</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6797194</v>
+      </c>
+      <c r="S45" t="n">
+        <v>13</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>125012816</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>385738</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6797251</v>
+      </c>
+      <c r="S46" t="n">
+        <v>8</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125013977</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>385623</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6797166</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125009359</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>385862</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6797329</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125014700</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79919</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>385567</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6797275</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125016157</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>385706</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6797113</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125007590</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>385922</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6797211</v>
+      </c>
+      <c r="S51" t="n">
+        <v>12</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125006076</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>385896</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6797101</v>
+      </c>
+      <c r="S52" t="n">
+        <v>14</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125014208</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>385699</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6797223</v>
+      </c>
+      <c r="S53" t="n">
+        <v>12</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125015390</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>385632</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6797173</v>
+      </c>
+      <c r="S54" t="n">
+        <v>15</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125010793</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>385779</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6797286</v>
+      </c>
+      <c r="S55" t="n">
+        <v>15</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125016946</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>385697</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6796899</v>
+      </c>
+      <c r="S56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125010542</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>385634</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6797413</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125015401</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>385632</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6797173</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125014342</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>385611</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6797222</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125014853</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>385539</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6797252</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125014604</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>385586</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6797242</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>125014307</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>385616</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6797214</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>125008665</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>385900</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6797194</v>
+      </c>
+      <c r="S63" t="n">
+        <v>8</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>125006190</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>385871</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6797143</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>125008520</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>385868</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6797226</v>
+      </c>
+      <c r="S65" t="n">
+        <v>15</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>125008432</v>
+      </c>
+      <c r="B66" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>385888</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6797224</v>
+      </c>
+      <c r="S66" t="n">
+        <v>15</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>125014510</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78547</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>385699</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6797223</v>
+      </c>
+      <c r="S67" t="n">
+        <v>9</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>125015797</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79892</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>385690</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6797129</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125009311</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78546</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>385900</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6797194</v>
+      </c>
+      <c r="S69" t="n">
+        <v>9</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125014769</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Sätern, Sätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>385552</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6797252</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Vid myr, källa?</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>77940137</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78570</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Grunnfossgnollen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>385032.0330319937</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6796918.812237687</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2019-05-06</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2019-05-06</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
           <t>Andreas Öster</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX71" t="inlineStr">
         <is>
           <t>Andreas Öster</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125004576</v>
+        <v>125004324</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R2" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125004325</v>
+        <v>125004366</v>
       </c>
       <c r="B3" t="n">
-        <v>78834</v>
+        <v>79399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385989</v>
+        <v>385975</v>
       </c>
       <c r="R3" t="n">
-        <v>6797025</v>
+        <v>6797012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125004665</v>
+        <v>125004576</v>
       </c>
       <c r="B4" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125004324</v>
+        <v>125004325</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>78834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385975</v>
+        <v>385989</v>
       </c>
       <c r="R5" t="n">
-        <v>6797012</v>
+        <v>6797025</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125004587</v>
+        <v>125004665</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004366</v>
+        <v>125004587</v>
       </c>
       <c r="B7" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R7" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125010553</v>
+        <v>125007590</v>
       </c>
       <c r="B9" t="n">
         <v>78547</v>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385876</v>
+        <v>385922</v>
       </c>
       <c r="R9" t="n">
-        <v>6797310</v>
+        <v>6797211</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125014812</v>
+        <v>125014011</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,41 +1583,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385618</v>
+        <v>385610</v>
       </c>
       <c r="R10" t="n">
-        <v>6797202</v>
+        <v>6797160</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,19 +1683,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125010604</v>
+        <v>125010000</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1723,10 +1735,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385633</v>
+        <v>385749</v>
       </c>
       <c r="R11" t="n">
-        <v>6797363</v>
+        <v>6797429</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1758,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125006056</v>
+        <v>125015299</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,49 +1819,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385924</v>
+        <v>385588</v>
       </c>
       <c r="R12" t="n">
-        <v>6797115</v>
+        <v>6797184</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1888,7 +1892,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125010000</v>
+        <v>125011580</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1931,21 +1940,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1955,13 +1964,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385749</v>
+        <v>385738</v>
       </c>
       <c r="R13" t="n">
-        <v>6797429</v>
+        <v>6797251</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1990,7 +1999,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2000,7 +2009,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,22 +2024,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125014057</v>
+        <v>125014812</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,21 +2052,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2067,13 +2076,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385607</v>
+        <v>385618</v>
       </c>
       <c r="R14" t="n">
-        <v>6797159</v>
+        <v>6797202</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2102,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2121,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2127,22 +2136,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125015572</v>
+        <v>125008543</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,21 +2164,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385709</v>
+        <v>385867</v>
       </c>
       <c r="R15" t="n">
-        <v>6797118</v>
+        <v>6797219</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2214,7 +2223,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2224,7 +2233,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2251,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125014685</v>
+        <v>125009430</v>
       </c>
       <c r="B16" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2267,21 +2276,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2291,10 +2300,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385571</v>
+        <v>385862</v>
       </c>
       <c r="R16" t="n">
-        <v>6797259</v>
+        <v>6797329</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2326,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2336,7 +2345,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2351,22 +2360,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125008506</v>
+        <v>125013949</v>
       </c>
       <c r="B17" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2379,21 +2388,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2403,10 +2412,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385867</v>
+        <v>385633</v>
       </c>
       <c r="R17" t="n">
-        <v>6797218</v>
+        <v>6797184</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2438,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2448,7 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,22 +2472,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125015566</v>
+        <v>125010594</v>
       </c>
       <c r="B18" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2491,21 +2500,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2515,10 +2524,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385640</v>
+        <v>385633</v>
       </c>
       <c r="R18" t="n">
-        <v>6797141</v>
+        <v>6797363</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2550,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2560,7 +2569,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,22 +2584,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125015347</v>
+        <v>125015566</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2603,21 +2612,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2627,13 +2636,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385592</v>
+        <v>385640</v>
       </c>
       <c r="R19" t="n">
-        <v>6797161</v>
+        <v>6797141</v>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2662,7 +2671,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2672,7 +2681,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2687,22 +2696,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125014011</v>
+        <v>125016901</v>
       </c>
       <c r="B20" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2711,50 +2720,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385610</v>
+        <v>385697</v>
       </c>
       <c r="R20" t="n">
-        <v>6797160</v>
+        <v>6796929</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2786,7 +2783,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2796,7 +2793,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,10 +2820,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125009781</v>
+        <v>125014208</v>
       </c>
       <c r="B21" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2839,21 +2836,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2863,13 +2860,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385862</v>
+        <v>385699</v>
       </c>
       <c r="R21" t="n">
-        <v>6797329</v>
+        <v>6797223</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2898,7 +2895,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2905,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2923,22 +2920,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125008585</v>
+        <v>125010542</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2951,21 +2948,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2975,10 +2972,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385867</v>
+        <v>385634</v>
       </c>
       <c r="R22" t="n">
-        <v>6797219</v>
+        <v>6797413</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3010,7 +3007,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3020,7 +3017,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3047,7 +3044,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125015299</v>
+        <v>125013977</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3087,10 +3084,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385588</v>
+        <v>385623</v>
       </c>
       <c r="R23" t="n">
-        <v>6797184</v>
+        <v>6797166</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3122,7 +3119,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3132,12 +3129,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3152,22 +3144,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125014083</v>
+        <v>125010031</v>
       </c>
       <c r="B24" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3180,21 +3172,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3204,13 +3196,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385689</v>
+        <v>385750</v>
       </c>
       <c r="R24" t="n">
-        <v>6797223</v>
+        <v>6797429</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3239,7 +3231,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3249,7 +3241,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3264,19 +3256,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125010560</v>
+        <v>125015347</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3316,13 +3308,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385763</v>
+        <v>385592</v>
       </c>
       <c r="R25" t="n">
-        <v>6797307</v>
+        <v>6797161</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3351,7 +3343,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3361,7 +3353,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3376,19 +3368,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125016901</v>
+        <v>125012816</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3428,13 +3420,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385697</v>
+        <v>385738</v>
       </c>
       <c r="R26" t="n">
-        <v>6796929</v>
+        <v>6797251</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3463,7 +3455,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3473,7 +3465,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3488,22 +3480,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125013949</v>
+        <v>125014700</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3512,25 +3504,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3540,10 +3532,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385633</v>
+        <v>385567</v>
       </c>
       <c r="R27" t="n">
-        <v>6797184</v>
+        <v>6797275</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3575,7 +3567,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3585,7 +3577,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3600,22 +3592,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014817</v>
+        <v>125014342</v>
       </c>
       <c r="B28" t="n">
-        <v>79919</v>
+        <v>78547</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3624,25 +3616,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3652,10 +3644,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385541</v>
+        <v>385611</v>
       </c>
       <c r="R28" t="n">
-        <v>6797264</v>
+        <v>6797222</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3687,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3697,12 +3689,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Vid myr, tjärn</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,10 +3716,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125011588</v>
+        <v>125008506</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3745,21 +3732,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3769,13 +3756,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385737</v>
+        <v>385867</v>
       </c>
       <c r="R29" t="n">
-        <v>6797241</v>
+        <v>6797218</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3804,7 +3791,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3801,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3841,7 +3828,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125014588</v>
+        <v>125010560</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3881,10 +3868,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385586</v>
+        <v>385763</v>
       </c>
       <c r="R30" t="n">
-        <v>6797244</v>
+        <v>6797307</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3916,7 +3903,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3926,12 +3913,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3958,10 +3940,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125014757</v>
+        <v>125009342</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3974,21 +3956,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3998,13 +3980,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385618</v>
+        <v>385861</v>
       </c>
       <c r="R31" t="n">
-        <v>6797202</v>
+        <v>6797324</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4033,7 +4015,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4043,7 +4025,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4058,19 +4040,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125009430</v>
+        <v>125008432</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -4110,10 +4092,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385862</v>
+        <v>385888</v>
       </c>
       <c r="R32" t="n">
-        <v>6797329</v>
+        <v>6797224</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4145,7 +4127,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4155,7 +4137,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4182,10 +4164,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125015275</v>
+        <v>125010793</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4194,25 +4176,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4222,10 +4204,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385609</v>
+        <v>385779</v>
       </c>
       <c r="R33" t="n">
-        <v>6797178</v>
+        <v>6797286</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4257,7 +4239,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4267,7 +4249,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4282,22 +4264,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125015297</v>
+        <v>125014510</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4310,21 +4292,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4334,13 +4316,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385569</v>
+        <v>385699</v>
       </c>
       <c r="R34" t="n">
-        <v>6797152</v>
+        <v>6797223</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4369,7 +4351,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4379,7 +4361,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,10 +4388,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125015273</v>
+        <v>125014035</v>
       </c>
       <c r="B35" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4422,21 +4404,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4446,13 +4428,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385579</v>
+        <v>385607</v>
       </c>
       <c r="R35" t="n">
-        <v>6797173</v>
+        <v>6797159</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4481,7 +4463,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4491,7 +4473,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4506,19 +4488,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125013776</v>
+        <v>125010269</v>
       </c>
       <c r="B36" t="n">
         <v>79891</v>
@@ -4558,13 +4540,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385692</v>
+        <v>385756</v>
       </c>
       <c r="R36" t="n">
-        <v>6797239</v>
+        <v>6797314</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4593,7 +4575,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4603,7 +4585,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4618,22 +4605,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125009952</v>
+        <v>125009781</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4646,21 +4633,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4670,13 +4657,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385760</v>
+        <v>385862</v>
       </c>
       <c r="R37" t="n">
-        <v>6797317</v>
+        <v>6797329</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4705,7 +4692,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4715,7 +4702,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4730,22 +4717,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125010031</v>
+        <v>125014083</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4758,21 +4745,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4782,13 +4769,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385750</v>
+        <v>385689</v>
       </c>
       <c r="R38" t="n">
-        <v>6797429</v>
+        <v>6797223</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4817,7 +4804,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4827,7 +4814,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4842,22 +4829,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125013825</v>
+        <v>125008003</v>
       </c>
       <c r="B39" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4870,21 +4857,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4894,13 +4881,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385689</v>
+        <v>385900</v>
       </c>
       <c r="R39" t="n">
-        <v>6797243</v>
+        <v>6797194</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4929,7 +4916,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4939,7 +4926,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4954,22 +4941,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125009342</v>
+        <v>125010553</v>
       </c>
       <c r="B40" t="n">
-        <v>79892</v>
+        <v>78547</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4982,21 +4969,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5006,13 +4993,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385861</v>
+        <v>385876</v>
       </c>
       <c r="R40" t="n">
-        <v>6797324</v>
+        <v>6797310</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5041,7 +5028,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5051,7 +5038,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5066,22 +5053,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125016771</v>
+        <v>125008520</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5094,21 +5081,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5118,10 +5105,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385674</v>
+        <v>385868</v>
       </c>
       <c r="R41" t="n">
-        <v>6796981</v>
+        <v>6797226</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5153,7 +5140,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5163,7 +5150,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5190,10 +5177,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125010269</v>
+        <v>125016946</v>
       </c>
       <c r="B42" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5206,21 +5193,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5230,13 +5217,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385756</v>
+        <v>385697</v>
       </c>
       <c r="R42" t="n">
-        <v>6797314</v>
+        <v>6796899</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5265,7 +5252,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5275,12 +5262,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5295,19 +5277,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125011580</v>
+        <v>125013776</v>
       </c>
       <c r="B43" t="n">
         <v>79891</v>
@@ -5347,13 +5329,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385738</v>
+        <v>385692</v>
       </c>
       <c r="R43" t="n">
-        <v>6797251</v>
+        <v>6797239</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5382,7 +5364,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5392,7 +5374,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5407,22 +5389,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125014099</v>
+        <v>125014588</v>
       </c>
       <c r="B44" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5435,21 +5417,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5459,13 +5441,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385699</v>
+        <v>385586</v>
       </c>
       <c r="R44" t="n">
-        <v>6797223</v>
+        <v>6797244</v>
       </c>
       <c r="S44" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5494,7 +5476,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5504,7 +5486,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5519,22 +5506,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125008003</v>
+        <v>125008665</v>
       </c>
       <c r="B45" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5547,21 +5534,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5577,7 +5564,7 @@
         <v>6797194</v>
       </c>
       <c r="S45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5606,7 +5593,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5616,7 +5603,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5643,10 +5630,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125012816</v>
+        <v>125015273</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5659,21 +5646,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5683,13 +5670,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385738</v>
+        <v>385579</v>
       </c>
       <c r="R46" t="n">
-        <v>6797251</v>
+        <v>6797173</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5718,7 +5705,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5728,7 +5715,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5755,7 +5742,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125013977</v>
+        <v>125011588</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5795,13 +5782,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385623</v>
+        <v>385737</v>
       </c>
       <c r="R47" t="n">
-        <v>6797166</v>
+        <v>6797241</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5830,7 +5817,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5840,7 +5827,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5855,22 +5842,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125009359</v>
+        <v>125006076</v>
       </c>
       <c r="B48" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5883,21 +5870,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5907,13 +5894,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385862</v>
+        <v>385896</v>
       </c>
       <c r="R48" t="n">
-        <v>6797329</v>
+        <v>6797101</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5942,7 +5929,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5952,7 +5939,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5967,22 +5954,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125014700</v>
+        <v>125006190</v>
       </c>
       <c r="B49" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5991,25 +5978,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6019,10 +6006,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385567</v>
+        <v>385871</v>
       </c>
       <c r="R49" t="n">
-        <v>6797275</v>
+        <v>6797143</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6054,7 +6041,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6064,7 +6051,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6079,22 +6066,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125016157</v>
+        <v>125009952</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6107,21 +6094,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6131,13 +6118,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385706</v>
+        <v>385760</v>
       </c>
       <c r="R50" t="n">
-        <v>6797113</v>
+        <v>6797317</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6166,7 +6153,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6176,7 +6163,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6203,10 +6190,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125007590</v>
+        <v>125014685</v>
       </c>
       <c r="B51" t="n">
-        <v>78547</v>
+        <v>79892</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6219,21 +6206,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6243,13 +6230,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385922</v>
+        <v>385571</v>
       </c>
       <c r="R51" t="n">
-        <v>6797211</v>
+        <v>6797259</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6278,7 +6265,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6288,7 +6275,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6303,22 +6290,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125006076</v>
+        <v>125015572</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6331,21 +6318,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6355,13 +6342,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385896</v>
+        <v>385709</v>
       </c>
       <c r="R52" t="n">
-        <v>6797101</v>
+        <v>6797118</v>
       </c>
       <c r="S52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6390,7 +6377,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6400,7 +6387,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6415,22 +6402,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125014208</v>
+        <v>125014307</v>
       </c>
       <c r="B53" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6443,21 +6430,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6467,13 +6454,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385699</v>
+        <v>385616</v>
       </c>
       <c r="R53" t="n">
-        <v>6797223</v>
+        <v>6797214</v>
       </c>
       <c r="S53" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6502,7 +6489,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6512,7 +6499,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6527,22 +6514,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125015390</v>
+        <v>125014604</v>
       </c>
       <c r="B54" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6555,21 +6542,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6579,10 +6566,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385632</v>
+        <v>385586</v>
       </c>
       <c r="R54" t="n">
-        <v>6797173</v>
+        <v>6797242</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6614,7 +6601,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6624,7 +6611,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6639,22 +6626,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125010793</v>
+        <v>125015390</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6663,25 +6650,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6691,10 +6678,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385779</v>
+        <v>385632</v>
       </c>
       <c r="R55" t="n">
-        <v>6797286</v>
+        <v>6797173</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6726,7 +6713,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6736,7 +6723,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6751,22 +6738,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125016946</v>
+        <v>125009359</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6779,21 +6766,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6803,10 +6790,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385697</v>
+        <v>385862</v>
       </c>
       <c r="R56" t="n">
-        <v>6796899</v>
+        <v>6797329</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6838,7 +6825,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6848,7 +6835,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6875,10 +6862,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125010542</v>
+        <v>125014757</v>
       </c>
       <c r="B57" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6891,21 +6878,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6915,13 +6902,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385634</v>
+        <v>385618</v>
       </c>
       <c r="R57" t="n">
-        <v>6797413</v>
+        <v>6797202</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6950,7 +6937,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6960,7 +6947,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6975,19 +6962,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125015401</v>
+        <v>125009311</v>
       </c>
       <c r="B58" t="n">
         <v>78546</v>
@@ -7027,13 +7014,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385632</v>
+        <v>385900</v>
       </c>
       <c r="R58" t="n">
-        <v>6797173</v>
+        <v>6797194</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7062,7 +7049,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7072,7 +7059,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7087,22 +7074,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125014342</v>
+        <v>125015797</v>
       </c>
       <c r="B59" t="n">
-        <v>78547</v>
+        <v>79892</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7115,21 +7102,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7139,13 +7126,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385611</v>
+        <v>385690</v>
       </c>
       <c r="R59" t="n">
-        <v>6797222</v>
+        <v>6797129</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7174,7 +7161,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7184,7 +7171,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7199,19 +7186,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125014853</v>
+        <v>125016157</v>
       </c>
       <c r="B60" t="n">
         <v>79891</v>
@@ -7251,10 +7238,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385539</v>
+        <v>385706</v>
       </c>
       <c r="R60" t="n">
-        <v>6797252</v>
+        <v>6797113</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7286,7 +7273,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7296,7 +7283,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7323,10 +7310,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125014604</v>
+        <v>125015401</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7339,21 +7326,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7363,10 +7350,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385586</v>
+        <v>385632</v>
       </c>
       <c r="R61" t="n">
-        <v>6797242</v>
+        <v>6797173</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7398,7 +7385,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7408,7 +7395,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7423,22 +7410,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125014307</v>
+        <v>125014853</v>
       </c>
       <c r="B62" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7451,21 +7438,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7475,10 +7462,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385616</v>
+        <v>385539</v>
       </c>
       <c r="R62" t="n">
-        <v>6797214</v>
+        <v>6797252</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7510,7 +7497,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7520,7 +7507,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7547,7 +7534,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125008665</v>
+        <v>125015275</v>
       </c>
       <c r="B63" t="n">
         <v>78810</v>
@@ -7587,13 +7574,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385900</v>
+        <v>385609</v>
       </c>
       <c r="R63" t="n">
-        <v>6797194</v>
+        <v>6797178</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7622,7 +7609,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7632,7 +7619,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7647,19 +7634,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125006190</v>
+        <v>125015297</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7699,13 +7686,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385871</v>
+        <v>385569</v>
       </c>
       <c r="R64" t="n">
-        <v>6797143</v>
+        <v>6797152</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7734,7 +7721,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7744,7 +7731,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7759,22 +7746,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125008520</v>
+        <v>125013825</v>
       </c>
       <c r="B65" t="n">
-        <v>78547</v>
+        <v>79892</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7787,21 +7774,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7811,10 +7798,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385868</v>
+        <v>385689</v>
       </c>
       <c r="R65" t="n">
-        <v>6797226</v>
+        <v>6797243</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7846,7 +7833,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7856,7 +7843,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7871,19 +7858,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125008432</v>
+        <v>125016771</v>
       </c>
       <c r="B66" t="n">
         <v>78810</v>
@@ -7923,10 +7910,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385888</v>
+        <v>385674</v>
       </c>
       <c r="R66" t="n">
-        <v>6797224</v>
+        <v>6796981</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7958,7 +7945,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7968,7 +7955,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7983,22 +7970,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125014510</v>
+        <v>125014817</v>
       </c>
       <c r="B67" t="n">
-        <v>78547</v>
+        <v>79919</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8007,25 +7994,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8035,13 +8022,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385699</v>
+        <v>385541</v>
       </c>
       <c r="R67" t="n">
-        <v>6797223</v>
+        <v>6797264</v>
       </c>
       <c r="S67" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8070,7 +8057,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8080,7 +8067,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8095,22 +8087,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125015797</v>
+        <v>125014769</v>
       </c>
       <c r="B68" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8123,21 +8115,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8147,13 +8139,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385690</v>
+        <v>385552</v>
       </c>
       <c r="R68" t="n">
-        <v>6797129</v>
+        <v>6797252</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8182,7 +8174,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8192,7 +8184,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8207,22 +8204,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125009311</v>
+        <v>125006056</v>
       </c>
       <c r="B69" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8231,41 +8228,49 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385900</v>
+        <v>385924</v>
       </c>
       <c r="R69" t="n">
-        <v>6797194</v>
+        <v>6797115</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8294,7 +8299,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8304,7 +8309,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8319,22 +8324,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125014769</v>
+        <v>125014099</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>78842</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8347,21 +8352,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8371,13 +8376,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385552</v>
+        <v>385699</v>
       </c>
       <c r="R70" t="n">
-        <v>6797252</v>
+        <v>6797223</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8406,7 +8411,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8416,12 +8421,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Vid myr, källa?</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8436,12 +8436,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125004325</v>
+        <v>125004665</v>
       </c>
       <c r="B5" t="n">
-        <v>78834</v>
+        <v>79428</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385989</v>
+        <v>385935</v>
       </c>
       <c r="R5" t="n">
-        <v>6797025</v>
+        <v>6796995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,22 +1111,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125004665</v>
+        <v>125004587</v>
       </c>
       <c r="B6" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004587</v>
+        <v>125004345</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R7" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125004345</v>
+        <v>125004325</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>78834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>385975</v>
+        <v>385989</v>
       </c>
       <c r="R8" t="n">
-        <v>6797012</v>
+        <v>6797025</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,12 +1447,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1807,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125015299</v>
+        <v>125011580</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,21 +1823,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1847,13 +1847,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385588</v>
+        <v>385738</v>
       </c>
       <c r="R12" t="n">
-        <v>6797184</v>
+        <v>6797251</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,12 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,22 +1907,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125011580</v>
+        <v>125014812</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,21 +1935,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1964,13 +1959,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385738</v>
+        <v>385618</v>
       </c>
       <c r="R13" t="n">
-        <v>6797251</v>
+        <v>6797202</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1999,7 +1994,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2009,7 +2004,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,10 +2031,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125014812</v>
+        <v>125008543</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2052,21 +2047,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,13 +2071,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385618</v>
+        <v>385867</v>
       </c>
       <c r="R14" t="n">
-        <v>6797202</v>
+        <v>6797219</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2111,7 +2106,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2116,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,19 +2131,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125008543</v>
+        <v>125009430</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2188,10 +2183,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385867</v>
+        <v>385862</v>
       </c>
       <c r="R15" t="n">
-        <v>6797219</v>
+        <v>6797329</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2223,7 +2218,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2233,7 +2228,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,7 +2255,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125009430</v>
+        <v>125013949</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2300,10 +2295,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385862</v>
+        <v>385633</v>
       </c>
       <c r="R16" t="n">
-        <v>6797329</v>
+        <v>6797184</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2335,7 +2330,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,7 +2340,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,7 +2367,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125013949</v>
+        <v>125010594</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2415,7 +2410,7 @@
         <v>385633</v>
       </c>
       <c r="R17" t="n">
-        <v>6797184</v>
+        <v>6797363</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2447,7 +2442,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2452,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,7 +2479,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125010594</v>
+        <v>125016901</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2524,10 +2519,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385633</v>
+        <v>385697</v>
       </c>
       <c r="R18" t="n">
-        <v>6797363</v>
+        <v>6796929</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2559,7 +2554,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,7 +2564,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125015566</v>
+        <v>125014208</v>
       </c>
       <c r="B19" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2636,13 +2631,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385640</v>
+        <v>385699</v>
       </c>
       <c r="R19" t="n">
-        <v>6797141</v>
+        <v>6797223</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2671,7 +2666,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2676,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,19 +2691,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125016901</v>
+        <v>125015347</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2748,13 +2743,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385697</v>
+        <v>385592</v>
       </c>
       <c r="R20" t="n">
-        <v>6796929</v>
+        <v>6797161</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2783,7 +2778,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2793,7 +2788,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,22 +2803,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125014208</v>
+        <v>125012816</v>
       </c>
       <c r="B21" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2836,21 +2831,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2860,13 +2855,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385699</v>
+        <v>385738</v>
       </c>
       <c r="R21" t="n">
-        <v>6797223</v>
+        <v>6797251</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2895,7 +2890,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2905,7 +2900,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3268,10 +3263,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125015347</v>
+        <v>125009342</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3284,21 +3279,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3308,13 +3303,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385592</v>
+        <v>385861</v>
       </c>
       <c r="R25" t="n">
-        <v>6797161</v>
+        <v>6797324</v>
       </c>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3343,7 +3338,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3353,7 +3348,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3368,19 +3363,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125012816</v>
+        <v>125008432</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3420,13 +3415,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385738</v>
+        <v>385888</v>
       </c>
       <c r="R26" t="n">
-        <v>6797251</v>
+        <v>6797224</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3455,7 +3450,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3465,7 +3460,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3480,22 +3475,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014700</v>
+        <v>125014510</v>
       </c>
       <c r="B27" t="n">
-        <v>79919</v>
+        <v>78547</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3504,25 +3499,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3532,13 +3527,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385567</v>
+        <v>385699</v>
       </c>
       <c r="R27" t="n">
-        <v>6797275</v>
+        <v>6797223</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3567,7 +3562,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,7 +3572,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3592,22 +3587,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014342</v>
+        <v>125014035</v>
       </c>
       <c r="B28" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3620,21 +3615,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3644,10 +3639,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385611</v>
+        <v>385607</v>
       </c>
       <c r="R28" t="n">
-        <v>6797222</v>
+        <v>6797159</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3679,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3684,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3704,19 +3699,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125008506</v>
+        <v>125009781</v>
       </c>
       <c r="B29" t="n">
         <v>78546</v>
@@ -3756,10 +3751,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385867</v>
+        <v>385862</v>
       </c>
       <c r="R29" t="n">
-        <v>6797218</v>
+        <v>6797329</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3791,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3801,7 +3796,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3816,22 +3811,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125010560</v>
+        <v>125008003</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3844,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3868,13 +3863,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385763</v>
+        <v>385900</v>
       </c>
       <c r="R30" t="n">
-        <v>6797307</v>
+        <v>6797194</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3903,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3913,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3928,22 +3923,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125009342</v>
+        <v>125010553</v>
       </c>
       <c r="B31" t="n">
-        <v>79892</v>
+        <v>78547</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3956,21 +3951,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3980,13 +3975,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385861</v>
+        <v>385876</v>
       </c>
       <c r="R31" t="n">
-        <v>6797324</v>
+        <v>6797310</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4015,7 +4010,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4025,7 +4020,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,19 +4035,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125008432</v>
+        <v>125016946</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -4092,10 +4087,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385888</v>
+        <v>385697</v>
       </c>
       <c r="R32" t="n">
-        <v>6797224</v>
+        <v>6796899</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4127,7 +4122,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4137,7 +4132,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4164,10 +4159,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125010793</v>
+        <v>125013776</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4176,25 +4171,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4204,10 +4199,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385779</v>
+        <v>385692</v>
       </c>
       <c r="R33" t="n">
-        <v>6797286</v>
+        <v>6797239</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4239,7 +4234,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4249,7 +4244,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4264,22 +4259,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125014510</v>
+        <v>125008665</v>
       </c>
       <c r="B34" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4292,21 +4287,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4316,13 +4311,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385699</v>
+        <v>385900</v>
       </c>
       <c r="R34" t="n">
-        <v>6797223</v>
+        <v>6797194</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4351,7 +4346,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4361,7 +4356,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4388,10 +4383,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125014035</v>
+        <v>125015273</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4404,21 +4399,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4428,13 +4423,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385607</v>
+        <v>385579</v>
       </c>
       <c r="R35" t="n">
-        <v>6797159</v>
+        <v>6797173</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4463,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4473,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4488,22 +4483,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125010269</v>
+        <v>125006076</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4516,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4540,13 +4535,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385756</v>
+        <v>385896</v>
       </c>
       <c r="R36" t="n">
-        <v>6797314</v>
+        <v>6797101</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4575,7 +4570,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4585,12 +4580,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4605,22 +4595,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125009781</v>
+        <v>125006190</v>
       </c>
       <c r="B37" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4633,21 +4623,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4657,10 +4647,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385862</v>
+        <v>385871</v>
       </c>
       <c r="R37" t="n">
-        <v>6797329</v>
+        <v>6797143</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4692,7 +4682,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4702,7 +4692,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4729,10 +4719,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125014083</v>
+        <v>125015572</v>
       </c>
       <c r="B38" t="n">
-        <v>78842</v>
+        <v>79891</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4745,21 +4735,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4769,13 +4759,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385689</v>
+        <v>385709</v>
       </c>
       <c r="R38" t="n">
-        <v>6797223</v>
+        <v>6797118</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4804,7 +4794,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4814,7 +4804,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4829,22 +4819,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125008003</v>
+        <v>125015390</v>
       </c>
       <c r="B39" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4857,21 +4847,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4881,13 +4871,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385900</v>
+        <v>385632</v>
       </c>
       <c r="R39" t="n">
-        <v>6797194</v>
+        <v>6797173</v>
       </c>
       <c r="S39" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4916,7 +4906,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4926,7 +4916,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4941,22 +4931,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125010553</v>
+        <v>125009359</v>
       </c>
       <c r="B40" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4969,21 +4959,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4993,13 +4983,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385876</v>
+        <v>385862</v>
       </c>
       <c r="R40" t="n">
-        <v>6797310</v>
+        <v>6797329</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5028,7 +5018,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5038,7 +5028,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5053,22 +5043,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125008520</v>
+        <v>125015401</v>
       </c>
       <c r="B41" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5081,21 +5071,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5105,10 +5095,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385868</v>
+        <v>385632</v>
       </c>
       <c r="R41" t="n">
-        <v>6797226</v>
+        <v>6797173</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5140,7 +5130,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5150,7 +5140,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5165,19 +5155,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125016946</v>
+        <v>125014757</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -5217,13 +5207,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385697</v>
+        <v>385618</v>
       </c>
       <c r="R42" t="n">
-        <v>6796899</v>
+        <v>6797202</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5252,7 +5242,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5262,7 +5252,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5277,22 +5267,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125013776</v>
+        <v>125009311</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5305,21 +5295,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5329,13 +5319,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385692</v>
+        <v>385900</v>
       </c>
       <c r="R43" t="n">
-        <v>6797239</v>
+        <v>6797194</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5364,7 +5354,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5374,7 +5364,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5389,22 +5379,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125014588</v>
+        <v>125015797</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5417,21 +5407,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5441,13 +5431,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385586</v>
+        <v>385690</v>
       </c>
       <c r="R44" t="n">
-        <v>6797244</v>
+        <v>6797129</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5476,7 +5466,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5486,12 +5476,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5506,19 +5491,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125008665</v>
+        <v>125015275</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5558,13 +5543,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385900</v>
+        <v>385609</v>
       </c>
       <c r="R45" t="n">
-        <v>6797194</v>
+        <v>6797178</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5593,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5603,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5618,22 +5603,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125015273</v>
+        <v>125015297</v>
       </c>
       <c r="B46" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5646,21 +5631,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5670,13 +5655,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385579</v>
+        <v>385569</v>
       </c>
       <c r="R46" t="n">
-        <v>6797173</v>
+        <v>6797152</v>
       </c>
       <c r="S46" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5742,10 +5727,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125011588</v>
+        <v>125013825</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5758,21 +5743,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5782,13 +5767,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385737</v>
+        <v>385689</v>
       </c>
       <c r="R47" t="n">
-        <v>6797241</v>
+        <v>6797243</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5817,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5827,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5842,22 +5827,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125006076</v>
+        <v>125014099</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5870,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5894,13 +5879,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385896</v>
+        <v>385699</v>
       </c>
       <c r="R48" t="n">
-        <v>6797101</v>
+        <v>6797223</v>
       </c>
       <c r="S48" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5929,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5939,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5966,7 +5951,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125006190</v>
+        <v>125014604</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -6006,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385871</v>
+        <v>385586</v>
       </c>
       <c r="R49" t="n">
-        <v>6797143</v>
+        <v>6797242</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6041,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6051,7 +6036,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6066,22 +6051,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125009952</v>
+        <v>125014307</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6094,21 +6079,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6118,13 +6103,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385760</v>
+        <v>385616</v>
       </c>
       <c r="R50" t="n">
-        <v>6797317</v>
+        <v>6797214</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6153,7 +6138,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6163,7 +6148,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6183,17 +6168,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125014685</v>
+        <v>125014083</v>
       </c>
       <c r="B51" t="n">
-        <v>79892</v>
+        <v>78842</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6206,21 +6191,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6230,13 +6215,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385571</v>
+        <v>385689</v>
       </c>
       <c r="R51" t="n">
-        <v>6797259</v>
+        <v>6797223</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6265,7 +6250,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6275,7 +6260,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6295,17 +6280,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125015572</v>
+        <v>125015566</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6318,21 +6303,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6342,10 +6327,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385709</v>
+        <v>385640</v>
       </c>
       <c r="R52" t="n">
-        <v>6797118</v>
+        <v>6797141</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6402,22 +6387,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125014307</v>
+        <v>125016771</v>
       </c>
       <c r="B53" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6430,21 +6415,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6454,10 +6439,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385616</v>
+        <v>385674</v>
       </c>
       <c r="R53" t="n">
-        <v>6797214</v>
+        <v>6796981</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6489,7 +6474,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6499,7 +6484,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6519,17 +6504,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125014604</v>
+        <v>125014769</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6542,21 +6527,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6566,10 +6551,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385586</v>
+        <v>385552</v>
       </c>
       <c r="R54" t="n">
-        <v>6797242</v>
+        <v>6797252</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6601,7 +6586,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6611,7 +6596,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6631,17 +6621,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125015390</v>
+        <v>125014853</v>
       </c>
       <c r="B55" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6654,21 +6644,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6678,10 +6668,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385632</v>
+        <v>385539</v>
       </c>
       <c r="R55" t="n">
-        <v>6797173</v>
+        <v>6797252</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6713,7 +6703,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6723,7 +6713,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6738,22 +6728,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125009359</v>
+        <v>125010560</v>
       </c>
       <c r="B56" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6766,21 +6756,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6790,10 +6780,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385862</v>
+        <v>385763</v>
       </c>
       <c r="R56" t="n">
-        <v>6797329</v>
+        <v>6797307</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6825,7 +6815,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6835,7 +6825,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6850,22 +6840,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125014757</v>
+        <v>125014342</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6878,21 +6868,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6902,13 +6892,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385618</v>
+        <v>385611</v>
       </c>
       <c r="R57" t="n">
-        <v>6797202</v>
+        <v>6797222</v>
       </c>
       <c r="S57" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6937,7 +6927,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6947,7 +6937,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6962,22 +6952,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125009311</v>
+        <v>125009952</v>
       </c>
       <c r="B58" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6990,21 +6980,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7014,13 +7004,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385900</v>
+        <v>385760</v>
       </c>
       <c r="R58" t="n">
-        <v>6797194</v>
+        <v>6797317</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7049,7 +7039,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7059,7 +7049,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7074,22 +7064,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125015797</v>
+        <v>125014685</v>
       </c>
       <c r="B59" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7102,37 +7092,40 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385690</v>
+        <v>385571</v>
       </c>
       <c r="R59" t="n">
-        <v>6797129</v>
+        <v>6797259</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7161,7 +7154,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7171,7 +7164,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7180,18 +7173,19 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7303,17 +7297,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125015401</v>
+        <v>125074279</v>
       </c>
       <c r="B61" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7322,38 +7316,42 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385632</v>
+        <v>385755</v>
       </c>
       <c r="R61" t="n">
-        <v>6797173</v>
+        <v>6797321</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7383,49 +7381,40 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125014853</v>
+        <v>125006056</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7434,41 +7423,49 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385539</v>
+        <v>385924</v>
       </c>
       <c r="R62" t="n">
-        <v>6797252</v>
+        <v>6797115</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7497,7 +7494,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7507,7 +7504,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7527,17 +7524,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125015275</v>
+        <v>125010793</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7546,25 +7543,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7574,10 +7571,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385609</v>
+        <v>385779</v>
       </c>
       <c r="R63" t="n">
-        <v>6797178</v>
+        <v>6797286</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7609,7 +7606,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7619,7 +7616,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7634,22 +7631,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125015297</v>
+        <v>125014700</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7658,25 +7655,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7686,13 +7683,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385569</v>
+        <v>385567</v>
       </c>
       <c r="R64" t="n">
-        <v>6797152</v>
+        <v>6797275</v>
       </c>
       <c r="S64" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7721,7 +7718,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7731,7 +7728,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7746,22 +7743,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125013825</v>
+        <v>125008506</v>
       </c>
       <c r="B65" t="n">
-        <v>79892</v>
+        <v>78546</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7774,21 +7771,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7798,10 +7795,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385689</v>
+        <v>385867</v>
       </c>
       <c r="R65" t="n">
-        <v>6797243</v>
+        <v>6797218</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7833,7 +7830,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7843,7 +7840,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7858,19 +7855,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125016771</v>
+        <v>125015299</v>
       </c>
       <c r="B66" t="n">
         <v>78810</v>
@@ -7910,10 +7907,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385674</v>
+        <v>385588</v>
       </c>
       <c r="R66" t="n">
-        <v>6796981</v>
+        <v>6797184</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7945,7 +7942,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7955,7 +7952,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7975,7 +7977,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8092,14 +8094,14 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014769</v>
+        <v>125010269</v>
       </c>
       <c r="B68" t="n">
         <v>79891</v>
@@ -8139,13 +8141,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385552</v>
+        <v>385756</v>
       </c>
       <c r="R68" t="n">
-        <v>6797252</v>
+        <v>6797314</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8174,7 +8176,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8184,12 +8186,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Vid myr, källa?</t>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8209,17 +8211,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125006056</v>
+        <v>125011588</v>
       </c>
       <c r="B69" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8228,46 +8230,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385924</v>
+        <v>385737</v>
       </c>
       <c r="R69" t="n">
-        <v>6797115</v>
+        <v>6797241</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8299,7 +8293,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8309,7 +8303,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8329,17 +8323,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125014099</v>
+        <v>125014588</v>
       </c>
       <c r="B70" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8352,21 +8346,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8376,13 +8370,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385699</v>
+        <v>385586</v>
       </c>
       <c r="R70" t="n">
-        <v>6797223</v>
+        <v>6797244</v>
       </c>
       <c r="S70" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8411,7 +8405,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8421,7 +8415,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8436,22 +8435,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>77940137</v>
+        <v>125008520</v>
       </c>
       <c r="B71" t="n">
-        <v>78570</v>
+        <v>78547</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8464,37 +8463,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Grunnfossgnollen, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385032.0330319937</v>
+        <v>385868</v>
       </c>
       <c r="R71" t="n">
-        <v>6796918.812237687</v>
+        <v>6797226</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8518,22 +8517,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2019-05-06</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2019-05-06</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8544,34 +8543,146 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>77940137</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78570</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Grunnfossgnollen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>385032.0330319937</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6796918.812237687</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2019-05-06</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2019-05-06</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
           <t>Andreas Öster</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
+      <c r="AX72" t="inlineStr">
         <is>
           <t>Andreas Öster</t>
         </is>
       </c>
-      <c r="AY71" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125004324</v>
+        <v>125004345</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125004366</v>
+        <v>125004576</v>
       </c>
       <c r="B3" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R3" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125004576</v>
+        <v>125004366</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R4" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125004665</v>
+        <v>125004324</v>
       </c>
       <c r="B5" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R5" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125004587</v>
+        <v>125004665</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004345</v>
+        <v>125004587</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R7" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125007590</v>
+        <v>125010553</v>
       </c>
       <c r="B9" t="n">
         <v>78547</v>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385922</v>
+        <v>385876</v>
       </c>
       <c r="R9" t="n">
-        <v>6797211</v>
+        <v>6797310</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125014011</v>
+        <v>125015275</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,50 +1583,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385610</v>
+        <v>385609</v>
       </c>
       <c r="R10" t="n">
-        <v>6797160</v>
+        <v>6797178</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1658,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125010000</v>
+        <v>125008614</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1735,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385749</v>
+        <v>385867</v>
       </c>
       <c r="R11" t="n">
-        <v>6797429</v>
+        <v>6797219</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1770,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125011580</v>
+        <v>125006076</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1847,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385738</v>
+        <v>385896</v>
       </c>
       <c r="R12" t="n">
-        <v>6797251</v>
+        <v>6797101</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1882,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125014812</v>
+        <v>125009359</v>
       </c>
       <c r="B13" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1959,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385618</v>
+        <v>385862</v>
       </c>
       <c r="R13" t="n">
-        <v>6797202</v>
+        <v>6797329</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2004,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,22 +2007,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125008543</v>
+        <v>125008003</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2047,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385867</v>
+        <v>385900</v>
       </c>
       <c r="R14" t="n">
-        <v>6797219</v>
+        <v>6797194</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2106,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2116,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,22 +2119,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125009430</v>
+        <v>125014812</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2159,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385862</v>
+        <v>385618</v>
       </c>
       <c r="R15" t="n">
-        <v>6797329</v>
+        <v>6797202</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2218,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2228,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,22 +2231,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125013949</v>
+        <v>125014510</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2271,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2295,13 +2283,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385633</v>
+        <v>385699</v>
       </c>
       <c r="R16" t="n">
-        <v>6797184</v>
+        <v>6797223</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2330,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2340,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,19 +2343,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125010594</v>
+        <v>125015297</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2407,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385633</v>
+        <v>385569</v>
       </c>
       <c r="R17" t="n">
-        <v>6797363</v>
+        <v>6797152</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2442,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2452,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,22 +2455,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125016901</v>
+        <v>125015390</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2495,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2519,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385697</v>
+        <v>385632</v>
       </c>
       <c r="R18" t="n">
-        <v>6796929</v>
+        <v>6797173</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2554,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2564,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125014208</v>
+        <v>125010031</v>
       </c>
       <c r="B19" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,13 +2619,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385699</v>
+        <v>385750</v>
       </c>
       <c r="R19" t="n">
-        <v>6797223</v>
+        <v>6797429</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2666,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2676,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,22 +2679,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125015347</v>
+        <v>125015797</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2719,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2743,13 +2731,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385592</v>
+        <v>385690</v>
       </c>
       <c r="R20" t="n">
-        <v>6797161</v>
+        <v>6797129</v>
       </c>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2778,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2788,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2815,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125012816</v>
+        <v>125013825</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2831,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2855,13 +2843,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385738</v>
+        <v>385689</v>
       </c>
       <c r="R21" t="n">
-        <v>6797251</v>
+        <v>6797243</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2890,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2900,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,22 +2903,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125010542</v>
+        <v>125014757</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2943,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2967,13 +2955,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385634</v>
+        <v>385618</v>
       </c>
       <c r="R22" t="n">
-        <v>6797413</v>
+        <v>6797202</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3002,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3012,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,19 +3015,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125013977</v>
+        <v>125012816</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3079,13 +3067,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385623</v>
+        <v>385738</v>
       </c>
       <c r="R23" t="n">
-        <v>6797166</v>
+        <v>6797251</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3114,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3124,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,22 +3127,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125010031</v>
+        <v>125013776</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3167,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3191,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385750</v>
+        <v>385692</v>
       </c>
       <c r="R24" t="n">
-        <v>6797429</v>
+        <v>6797239</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3226,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3263,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125009342</v>
+        <v>125015347</v>
       </c>
       <c r="B25" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3279,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3303,13 +3291,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385861</v>
+        <v>385592</v>
       </c>
       <c r="R25" t="n">
-        <v>6797324</v>
+        <v>6797161</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3338,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3348,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,12 +3351,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3487,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014510</v>
+        <v>125013977</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3503,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3527,13 +3515,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385699</v>
+        <v>385623</v>
       </c>
       <c r="R27" t="n">
-        <v>6797223</v>
+        <v>6797166</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3562,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3572,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,19 +3575,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125014035</v>
+        <v>125016913</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3639,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385607</v>
+        <v>385697</v>
       </c>
       <c r="R28" t="n">
-        <v>6797159</v>
+        <v>6796929</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3674,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3711,10 +3699,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125009781</v>
+        <v>125014035</v>
       </c>
       <c r="B29" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3727,21 +3715,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3751,10 +3739,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385862</v>
+        <v>385607</v>
       </c>
       <c r="R29" t="n">
-        <v>6797329</v>
+        <v>6797159</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3786,7 +3774,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,7 +3784,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3823,10 +3811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125008003</v>
+        <v>125014011</v>
       </c>
       <c r="B30" t="n">
-        <v>79399</v>
+        <v>56722</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3835,41 +3823,53 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385900</v>
+        <v>385610</v>
       </c>
       <c r="R30" t="n">
-        <v>6797194</v>
+        <v>6797160</v>
       </c>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3923,22 +3923,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125010553</v>
+        <v>125010594</v>
       </c>
       <c r="B31" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3975,13 +3975,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385876</v>
+        <v>385633</v>
       </c>
       <c r="R31" t="n">
-        <v>6797310</v>
+        <v>6797363</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,22 +4035,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125016946</v>
+        <v>125010542</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385697</v>
+        <v>385634</v>
       </c>
       <c r="R32" t="n">
-        <v>6796899</v>
+        <v>6797413</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4159,10 +4159,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125013776</v>
+        <v>125009342</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4175,21 +4175,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385692</v>
+        <v>385861</v>
       </c>
       <c r="R33" t="n">
-        <v>6797239</v>
+        <v>6797324</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4271,10 +4271,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125008665</v>
+        <v>125015572</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385900</v>
+        <v>385709</v>
       </c>
       <c r="R34" t="n">
-        <v>6797194</v>
+        <v>6797118</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,22 +4371,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125015273</v>
+        <v>125006190</v>
       </c>
       <c r="B35" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4399,21 +4399,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385579</v>
+        <v>385871</v>
       </c>
       <c r="R35" t="n">
-        <v>6797173</v>
+        <v>6797143</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,22 +4483,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125006076</v>
+        <v>125014099</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385896</v>
+        <v>385699</v>
       </c>
       <c r="R36" t="n">
-        <v>6797101</v>
+        <v>6797223</v>
       </c>
       <c r="S36" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,7 +4607,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125006190</v>
+        <v>125010000</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385871</v>
+        <v>385749</v>
       </c>
       <c r="R37" t="n">
-        <v>6797143</v>
+        <v>6797429</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4719,10 +4719,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125015572</v>
+        <v>125015273</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4735,21 +4735,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385709</v>
+        <v>385579</v>
       </c>
       <c r="R38" t="n">
-        <v>6797118</v>
+        <v>6797173</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,22 +4819,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125015390</v>
+        <v>125016946</v>
       </c>
       <c r="B39" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385632</v>
+        <v>385697</v>
       </c>
       <c r="R39" t="n">
-        <v>6797173</v>
+        <v>6796899</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4943,10 +4943,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125009359</v>
+        <v>125009430</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5055,10 +5055,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125015401</v>
+        <v>125011580</v>
       </c>
       <c r="B41" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385632</v>
+        <v>385738</v>
       </c>
       <c r="R41" t="n">
-        <v>6797173</v>
+        <v>6797251</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,22 +5155,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125014757</v>
+        <v>125007590</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5183,21 +5183,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385618</v>
+        <v>385922</v>
       </c>
       <c r="R42" t="n">
-        <v>6797202</v>
+        <v>6797211</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5391,10 +5391,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125015797</v>
+        <v>125009781</v>
       </c>
       <c r="B44" t="n">
-        <v>79892</v>
+        <v>78546</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385690</v>
+        <v>385862</v>
       </c>
       <c r="R44" t="n">
-        <v>6797129</v>
+        <v>6797329</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5491,19 +5491,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125015275</v>
+        <v>125008665</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5543,13 +5543,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385609</v>
+        <v>385900</v>
       </c>
       <c r="R45" t="n">
-        <v>6797178</v>
+        <v>6797194</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5603,22 +5603,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125015297</v>
+        <v>125014208</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385569</v>
+        <v>385699</v>
       </c>
       <c r="R46" t="n">
-        <v>6797152</v>
+        <v>6797223</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5727,10 +5727,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125013825</v>
+        <v>125013949</v>
       </c>
       <c r="B47" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5743,21 +5743,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385689</v>
+        <v>385633</v>
       </c>
       <c r="R47" t="n">
-        <v>6797243</v>
+        <v>6797184</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125014099</v>
+        <v>125015401</v>
       </c>
       <c r="B48" t="n">
-        <v>78842</v>
+        <v>78546</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,13 +5879,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385699</v>
+        <v>385632</v>
       </c>
       <c r="R48" t="n">
-        <v>6797223</v>
+        <v>6797173</v>
       </c>
       <c r="S48" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5939,22 +5939,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125014604</v>
+        <v>125014853</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385586</v>
+        <v>385539</v>
       </c>
       <c r="R49" t="n">
-        <v>6797242</v>
+        <v>6797252</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6063,10 +6063,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125014307</v>
+        <v>125014685</v>
       </c>
       <c r="B50" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6079,34 +6079,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385616</v>
+        <v>385571</v>
       </c>
       <c r="R50" t="n">
-        <v>6797214</v>
+        <v>6797259</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6138,7 +6141,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6148,7 +6151,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6157,6 +6160,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6175,10 +6179,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125014083</v>
+        <v>125016157</v>
       </c>
       <c r="B51" t="n">
-        <v>78842</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6191,21 +6195,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6215,13 +6219,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385689</v>
+        <v>385706</v>
       </c>
       <c r="R51" t="n">
-        <v>6797223</v>
+        <v>6797113</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6250,7 +6254,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6260,7 +6264,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6287,10 +6291,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125015566</v>
+        <v>125014083</v>
       </c>
       <c r="B52" t="n">
-        <v>78546</v>
+        <v>78842</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6303,21 +6307,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6327,13 +6331,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385640</v>
+        <v>385689</v>
       </c>
       <c r="R52" t="n">
-        <v>6797141</v>
+        <v>6797223</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6362,7 +6366,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6372,7 +6376,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6399,10 +6403,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125016771</v>
+        <v>125074279</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6411,38 +6415,42 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385674</v>
+        <v>385755</v>
       </c>
       <c r="R53" t="n">
-        <v>6796981</v>
+        <v>6797321</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6472,27 +6480,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6504,17 +6503,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125014769</v>
+        <v>125015566</v>
       </c>
       <c r="B54" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6527,21 +6526,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6551,10 +6550,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385552</v>
+        <v>385640</v>
       </c>
       <c r="R54" t="n">
-        <v>6797252</v>
+        <v>6797141</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6586,7 +6585,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6596,12 +6595,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Vid myr, källa?</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6628,10 +6622,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125014853</v>
+        <v>125008506</v>
       </c>
       <c r="B55" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6644,21 +6638,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6668,10 +6662,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385539</v>
+        <v>385867</v>
       </c>
       <c r="R55" t="n">
-        <v>6797252</v>
+        <v>6797218</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6703,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6713,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6740,7 +6734,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125010560</v>
+        <v>125015299</v>
       </c>
       <c r="B56" t="n">
         <v>78810</v>
@@ -6780,10 +6774,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385763</v>
+        <v>385588</v>
       </c>
       <c r="R56" t="n">
-        <v>6797307</v>
+        <v>6797184</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6815,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6825,7 +6819,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6852,10 +6851,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125014342</v>
+        <v>125014700</v>
       </c>
       <c r="B57" t="n">
-        <v>78547</v>
+        <v>79919</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6864,25 +6863,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6892,10 +6891,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385611</v>
+        <v>385567</v>
       </c>
       <c r="R57" t="n">
-        <v>6797222</v>
+        <v>6797275</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6927,7 +6926,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6937,7 +6936,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6964,7 +6963,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125009952</v>
+        <v>125016771</v>
       </c>
       <c r="B58" t="n">
         <v>78810</v>
@@ -7004,13 +7003,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385760</v>
+        <v>385674</v>
       </c>
       <c r="R58" t="n">
-        <v>6797317</v>
+        <v>6796981</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7039,7 +7038,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7049,7 +7048,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7076,7 +7075,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125014685</v>
+        <v>125010269</v>
       </c>
       <c r="B59" t="n">
         <v>79891</v>
@@ -7110,22 +7109,19 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385571</v>
+        <v>385756</v>
       </c>
       <c r="R59" t="n">
-        <v>6797259</v>
+        <v>6797314</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7154,7 +7150,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7164,7 +7160,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7173,7 +7174,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7192,10 +7192,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125016157</v>
+        <v>125011588</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7208,21 +7208,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7232,13 +7232,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385706</v>
+        <v>385737</v>
       </c>
       <c r="R60" t="n">
-        <v>6797113</v>
+        <v>6797241</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7304,10 +7304,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125074279</v>
+        <v>125014342</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7316,42 +7316,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sätern, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385755</v>
+        <v>385611</v>
       </c>
       <c r="R61" t="n">
-        <v>6797321</v>
+        <v>6797222</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7381,18 +7377,27 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7404,17 +7409,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125006056</v>
+        <v>125010560</v>
       </c>
       <c r="B62" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7423,49 +7428,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385924</v>
+        <v>385763</v>
       </c>
       <c r="R62" t="n">
-        <v>6797115</v>
+        <v>6797307</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7494,7 +7491,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7504,7 +7501,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7643,7 +7640,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125014700</v>
+        <v>125014817</v>
       </c>
       <c r="B64" t="n">
         <v>79919</v>
@@ -7683,10 +7680,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385567</v>
+        <v>385541</v>
       </c>
       <c r="R64" t="n">
-        <v>6797275</v>
+        <v>6797264</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7718,7 +7715,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7728,7 +7725,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7755,10 +7757,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125008506</v>
+        <v>125014604</v>
       </c>
       <c r="B65" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7771,21 +7773,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7795,10 +7797,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385867</v>
+        <v>385586</v>
       </c>
       <c r="R65" t="n">
-        <v>6797218</v>
+        <v>6797242</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7830,7 +7832,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7840,7 +7842,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7867,10 +7869,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125015299</v>
+        <v>125014307</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7883,21 +7885,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7907,10 +7909,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385588</v>
+        <v>385616</v>
       </c>
       <c r="R66" t="n">
-        <v>6797184</v>
+        <v>6797214</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7942,7 +7944,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7952,12 +7954,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7984,10 +7981,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125014817</v>
+        <v>125009952</v>
       </c>
       <c r="B67" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7996,25 +7993,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8024,13 +8021,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385541</v>
+        <v>385760</v>
       </c>
       <c r="R67" t="n">
-        <v>6797264</v>
+        <v>6797317</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8059,7 +8056,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8069,12 +8066,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Vid myr, tjärn</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8101,7 +8093,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125010269</v>
+        <v>125014769</v>
       </c>
       <c r="B68" t="n">
         <v>79891</v>
@@ -8141,13 +8133,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385756</v>
+        <v>385552</v>
       </c>
       <c r="R68" t="n">
-        <v>6797314</v>
+        <v>6797252</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8176,7 +8168,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8186,12 +8178,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8218,10 +8210,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125011588</v>
+        <v>125006056</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8230,38 +8222,46 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385737</v>
+        <v>385924</v>
       </c>
       <c r="R69" t="n">
-        <v>6797241</v>
+        <v>6797115</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8330,10 +8330,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125014588</v>
+        <v>125008520</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8346,21 +8346,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385586</v>
+        <v>385868</v>
       </c>
       <c r="R70" t="n">
-        <v>6797244</v>
+        <v>6797226</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8415,12 +8415,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8447,10 +8442,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125008520</v>
+        <v>125014588</v>
       </c>
       <c r="B71" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8463,21 +8458,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8487,10 +8482,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385868</v>
+        <v>385586</v>
       </c>
       <c r="R71" t="n">
-        <v>6797226</v>
+        <v>6797244</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8522,7 +8517,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8532,7 +8527,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125010553</v>
+        <v>125015275</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385876</v>
+        <v>385609</v>
       </c>
       <c r="R9" t="n">
-        <v>6797310</v>
+        <v>6797178</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,19 +1559,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125015275</v>
+        <v>125008614</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385609</v>
+        <v>385867</v>
       </c>
       <c r="R10" t="n">
-        <v>6797178</v>
+        <v>6797219</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125008614</v>
+        <v>125006076</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385867</v>
+        <v>385896</v>
       </c>
       <c r="R11" t="n">
-        <v>6797219</v>
+        <v>6797101</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125006076</v>
+        <v>125010553</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385896</v>
+        <v>385876</v>
       </c>
       <c r="R12" t="n">
-        <v>6797101</v>
+        <v>6797310</v>
       </c>
       <c r="S12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125013776</v>
+        <v>125015347</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385692</v>
+        <v>385592</v>
       </c>
       <c r="R24" t="n">
-        <v>6797239</v>
+        <v>6797161</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3239,19 +3239,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125015347</v>
+        <v>125008432</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3291,13 +3291,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385592</v>
+        <v>385888</v>
       </c>
       <c r="R25" t="n">
-        <v>6797161</v>
+        <v>6797224</v>
       </c>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3351,19 +3351,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125008432</v>
+        <v>125013977</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385888</v>
+        <v>385623</v>
       </c>
       <c r="R26" t="n">
-        <v>6797224</v>
+        <v>6797166</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,7 +3475,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125013977</v>
+        <v>125016913</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385623</v>
+        <v>385697</v>
       </c>
       <c r="R27" t="n">
-        <v>6797166</v>
+        <v>6796929</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125016913</v>
+        <v>125013776</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385697</v>
+        <v>385692</v>
       </c>
       <c r="R28" t="n">
-        <v>6796929</v>
+        <v>6797239</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125014035</v>
+        <v>125014011</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3711,38 +3711,50 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385607</v>
+        <v>385610</v>
       </c>
       <c r="R29" t="n">
-        <v>6797159</v>
+        <v>6797160</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3811,10 +3823,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125014011</v>
+        <v>125014035</v>
       </c>
       <c r="B30" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3823,50 +3835,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385610</v>
+        <v>385607</v>
       </c>
       <c r="R30" t="n">
-        <v>6797160</v>
+        <v>6797159</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125004345</v>
+        <v>125004665</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R2" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125004366</v>
+        <v>125004345</v>
       </c>
       <c r="B4" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125004665</v>
+        <v>125004587</v>
       </c>
       <c r="B6" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004587</v>
+        <v>125004366</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R7" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125015275</v>
+        <v>125008543</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385609</v>
+        <v>385867</v>
       </c>
       <c r="R9" t="n">
-        <v>6797178</v>
+        <v>6797219</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125008614</v>
+        <v>125008432</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385867</v>
+        <v>385888</v>
       </c>
       <c r="R10" t="n">
-        <v>6797219</v>
+        <v>6797224</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125006076</v>
+        <v>125015275</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385896</v>
+        <v>385609</v>
       </c>
       <c r="R11" t="n">
-        <v>6797101</v>
+        <v>6797178</v>
       </c>
       <c r="S11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125010553</v>
+        <v>125014208</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385876</v>
+        <v>385699</v>
       </c>
       <c r="R12" t="n">
-        <v>6797310</v>
+        <v>6797223</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125009359</v>
+        <v>125014035</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385862</v>
+        <v>385607</v>
       </c>
       <c r="R13" t="n">
-        <v>6797329</v>
+        <v>6797159</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125008003</v>
+        <v>125015401</v>
       </c>
       <c r="B14" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385900</v>
+        <v>385632</v>
       </c>
       <c r="R14" t="n">
-        <v>6797194</v>
+        <v>6797173</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,19 +2119,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125014812</v>
+        <v>125010553</v>
       </c>
       <c r="B15" t="n">
         <v>78547</v>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385618</v>
+        <v>385876</v>
       </c>
       <c r="R15" t="n">
-        <v>6797202</v>
+        <v>6797310</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,7 +2243,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125014510</v>
+        <v>125015390</v>
       </c>
       <c r="B16" t="n">
         <v>78547</v>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385699</v>
+        <v>385632</v>
       </c>
       <c r="R16" t="n">
-        <v>6797223</v>
+        <v>6797173</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,22 +2343,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125015297</v>
+        <v>125013825</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385569</v>
+        <v>385689</v>
       </c>
       <c r="R17" t="n">
-        <v>6797152</v>
+        <v>6797243</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,22 +2455,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125015390</v>
+        <v>125010604</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385632</v>
+        <v>385633</v>
       </c>
       <c r="R18" t="n">
-        <v>6797173</v>
+        <v>6797363</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125010031</v>
+        <v>125013977</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385750</v>
+        <v>385623</v>
       </c>
       <c r="R19" t="n">
-        <v>6797429</v>
+        <v>6797166</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125015797</v>
+        <v>125008665</v>
       </c>
       <c r="B20" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385690</v>
+        <v>385900</v>
       </c>
       <c r="R20" t="n">
-        <v>6797129</v>
+        <v>6797194</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125013825</v>
+        <v>125013776</v>
       </c>
       <c r="B21" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385689</v>
+        <v>385692</v>
       </c>
       <c r="R21" t="n">
-        <v>6797243</v>
+        <v>6797239</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125014757</v>
+        <v>125009311</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385618</v>
+        <v>385900</v>
       </c>
       <c r="R22" t="n">
-        <v>6797202</v>
+        <v>6797194</v>
       </c>
       <c r="S22" t="n">
         <v>9</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125012816</v>
+        <v>125008003</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385738</v>
+        <v>385900</v>
       </c>
       <c r="R23" t="n">
-        <v>6797251</v>
+        <v>6797194</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,7 +3139,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125015347</v>
+        <v>125010000</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385592</v>
+        <v>385749</v>
       </c>
       <c r="R24" t="n">
-        <v>6797161</v>
+        <v>6797429</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3239,19 +3239,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125008432</v>
+        <v>125006076</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3291,13 +3291,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385888</v>
+        <v>385896</v>
       </c>
       <c r="R25" t="n">
-        <v>6797224</v>
+        <v>6797101</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3351,22 +3351,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125013977</v>
+        <v>125015572</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385623</v>
+        <v>385709</v>
       </c>
       <c r="R26" t="n">
-        <v>6797166</v>
+        <v>6797118</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125016913</v>
+        <v>125011580</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385697</v>
+        <v>385738</v>
       </c>
       <c r="R27" t="n">
-        <v>6796929</v>
+        <v>6797251</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3575,22 +3575,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125013776</v>
+        <v>125016901</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385692</v>
+        <v>385697</v>
       </c>
       <c r="R28" t="n">
-        <v>6797239</v>
+        <v>6796929</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125014011</v>
+        <v>125015347</v>
       </c>
       <c r="B29" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3711,53 +3711,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385610</v>
+        <v>385592</v>
       </c>
       <c r="R29" t="n">
-        <v>6797160</v>
+        <v>6797161</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3786,7 +3774,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,7 +3784,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,19 +3799,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125014035</v>
+        <v>125013949</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3863,10 +3851,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385607</v>
+        <v>385633</v>
       </c>
       <c r="R30" t="n">
-        <v>6797159</v>
+        <v>6797184</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3898,7 +3886,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3896,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,10 +3923,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125010594</v>
+        <v>125014510</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3951,21 +3939,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3975,13 +3963,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385633</v>
+        <v>385699</v>
       </c>
       <c r="R31" t="n">
-        <v>6797363</v>
+        <v>6797223</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,7 +3998,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4020,7 +4008,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,22 +4023,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125010542</v>
+        <v>125012816</v>
       </c>
       <c r="B32" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4063,21 +4051,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4087,13 +4075,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385634</v>
+        <v>385738</v>
       </c>
       <c r="R32" t="n">
-        <v>6797413</v>
+        <v>6797251</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4122,7 +4110,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4132,7 +4120,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,22 +4135,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125009342</v>
+        <v>125009359</v>
       </c>
       <c r="B33" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4175,21 +4163,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4199,10 +4187,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385861</v>
+        <v>385862</v>
       </c>
       <c r="R33" t="n">
-        <v>6797324</v>
+        <v>6797329</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4271,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125015572</v>
+        <v>125014757</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4287,21 +4275,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4311,13 +4299,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385709</v>
+        <v>385618</v>
       </c>
       <c r="R34" t="n">
-        <v>6797118</v>
+        <v>6797202</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4346,7 +4334,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4356,7 +4344,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,19 +4359,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125006190</v>
+        <v>125016946</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4423,10 +4411,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385871</v>
+        <v>385697</v>
       </c>
       <c r="R35" t="n">
-        <v>6797143</v>
+        <v>6796899</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4458,7 +4446,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4468,7 +4456,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,10 +4483,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125014099</v>
+        <v>125015797</v>
       </c>
       <c r="B36" t="n">
-        <v>78842</v>
+        <v>79892</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,21 +4499,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,13 +4523,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385699</v>
+        <v>385690</v>
       </c>
       <c r="R36" t="n">
-        <v>6797223</v>
+        <v>6797129</v>
       </c>
       <c r="S36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4580,7 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,7 +4595,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125010000</v>
+        <v>125006190</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4647,10 +4635,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385749</v>
+        <v>385871</v>
       </c>
       <c r="R37" t="n">
-        <v>6797429</v>
+        <v>6797143</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4682,7 +4670,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4692,7 +4680,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4719,10 +4707,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125015273</v>
+        <v>125010031</v>
       </c>
       <c r="B38" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4735,21 +4723,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,13 +4747,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385579</v>
+        <v>385750</v>
       </c>
       <c r="R38" t="n">
-        <v>6797173</v>
+        <v>6797429</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4794,7 +4782,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4804,7 +4792,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,22 +4807,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125016946</v>
+        <v>125014011</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4843,38 +4831,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385697</v>
+        <v>385610</v>
       </c>
       <c r="R39" t="n">
-        <v>6796899</v>
+        <v>6797160</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4943,10 +4943,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125009430</v>
+        <v>125007590</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385862</v>
+        <v>385922</v>
       </c>
       <c r="R40" t="n">
-        <v>6797329</v>
+        <v>6797211</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,22 +5043,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125011580</v>
+        <v>125010542</v>
       </c>
       <c r="B41" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385738</v>
+        <v>385634</v>
       </c>
       <c r="R41" t="n">
-        <v>6797251</v>
+        <v>6797413</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,22 +5155,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125007590</v>
+        <v>125009342</v>
       </c>
       <c r="B42" t="n">
-        <v>78547</v>
+        <v>79892</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5183,21 +5183,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385922</v>
+        <v>385861</v>
       </c>
       <c r="R42" t="n">
-        <v>6797211</v>
+        <v>6797324</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5267,22 +5267,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125009311</v>
+        <v>125009430</v>
       </c>
       <c r="B43" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5295,21 +5295,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5319,13 +5319,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385900</v>
+        <v>385862</v>
       </c>
       <c r="R43" t="n">
-        <v>6797194</v>
+        <v>6797329</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5379,22 +5379,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125009781</v>
+        <v>125014812</v>
       </c>
       <c r="B44" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385862</v>
+        <v>385618</v>
       </c>
       <c r="R44" t="n">
-        <v>6797329</v>
+        <v>6797202</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5491,22 +5491,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125008665</v>
+        <v>125009781</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5519,21 +5519,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5543,13 +5543,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385900</v>
+        <v>385862</v>
       </c>
       <c r="R45" t="n">
-        <v>6797194</v>
+        <v>6797329</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5603,22 +5603,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125014208</v>
+        <v>125015297</v>
       </c>
       <c r="B46" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385699</v>
+        <v>385569</v>
       </c>
       <c r="R46" t="n">
-        <v>6797223</v>
+        <v>6797152</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5727,10 +5727,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125013949</v>
+        <v>125014099</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5743,21 +5743,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5767,13 +5767,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385633</v>
+        <v>385699</v>
       </c>
       <c r="R47" t="n">
-        <v>6797184</v>
+        <v>6797223</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5827,22 +5827,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125015401</v>
+        <v>125015273</v>
       </c>
       <c r="B48" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,13 +5879,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385632</v>
+        <v>385579</v>
       </c>
       <c r="R48" t="n">
         <v>6797173</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5939,22 +5939,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125014853</v>
+        <v>125008506</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385539</v>
+        <v>385867</v>
       </c>
       <c r="R49" t="n">
-        <v>6797252</v>
+        <v>6797218</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6179,10 +6179,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125016157</v>
+        <v>125014307</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6195,21 +6195,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385706</v>
+        <v>385616</v>
       </c>
       <c r="R51" t="n">
-        <v>6797113</v>
+        <v>6797214</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6291,10 +6291,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125014083</v>
+        <v>125016157</v>
       </c>
       <c r="B52" t="n">
-        <v>78842</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6307,21 +6307,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6331,13 +6331,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385689</v>
+        <v>385706</v>
       </c>
       <c r="R52" t="n">
-        <v>6797223</v>
+        <v>6797113</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6403,10 +6403,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125074279</v>
+        <v>125011588</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6415,45 +6415,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sätern, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385755</v>
+        <v>385737</v>
       </c>
       <c r="R53" t="n">
-        <v>6797321</v>
+        <v>6797241</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6480,18 +6476,27 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6503,17 +6508,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125015566</v>
+        <v>125074279</v>
       </c>
       <c r="B54" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6522,38 +6527,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385640</v>
+        <v>385755</v>
       </c>
       <c r="R54" t="n">
-        <v>6797141</v>
+        <v>6797321</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6583,27 +6592,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6615,14 +6615,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125008506</v>
+        <v>125015566</v>
       </c>
       <c r="B55" t="n">
         <v>78546</v>
@@ -6662,10 +6662,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385867</v>
+        <v>385640</v>
       </c>
       <c r="R55" t="n">
-        <v>6797218</v>
+        <v>6797141</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6734,7 +6734,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125015299</v>
+        <v>125014588</v>
       </c>
       <c r="B56" t="n">
         <v>78810</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385588</v>
+        <v>385586</v>
       </c>
       <c r="R56" t="n">
-        <v>6797184</v>
+        <v>6797244</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6851,10 +6851,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125014700</v>
+        <v>125010793</v>
       </c>
       <c r="B57" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6863,25 +6863,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385567</v>
+        <v>385779</v>
       </c>
       <c r="R57" t="n">
-        <v>6797275</v>
+        <v>6797286</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6963,10 +6963,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125016771</v>
+        <v>125008520</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6979,21 +6979,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7003,10 +7003,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385674</v>
+        <v>385868</v>
       </c>
       <c r="R58" t="n">
-        <v>6796981</v>
+        <v>6797226</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7075,10 +7075,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125010269</v>
+        <v>125014083</v>
       </c>
       <c r="B59" t="n">
-        <v>79891</v>
+        <v>78842</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7091,21 +7091,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385756</v>
+        <v>385689</v>
       </c>
       <c r="R59" t="n">
-        <v>6797314</v>
+        <v>6797223</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7150,7 +7150,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7160,12 +7160,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7192,10 +7187,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125011588</v>
+        <v>125014853</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7208,21 +7203,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7232,13 +7227,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385737</v>
+        <v>385539</v>
       </c>
       <c r="R60" t="n">
-        <v>6797241</v>
+        <v>6797252</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7267,7 +7262,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7277,7 +7272,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7304,10 +7299,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125014342</v>
+        <v>125014769</v>
       </c>
       <c r="B61" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7320,21 +7315,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7344,10 +7339,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385611</v>
+        <v>385552</v>
       </c>
       <c r="R61" t="n">
-        <v>6797222</v>
+        <v>6797252</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7379,7 +7374,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7389,7 +7384,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7416,7 +7416,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125010560</v>
+        <v>125009952</v>
       </c>
       <c r="B62" t="n">
         <v>78810</v>
@@ -7456,13 +7456,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385763</v>
+        <v>385760</v>
       </c>
       <c r="R62" t="n">
-        <v>6797307</v>
+        <v>6797317</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7528,10 +7528,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125010793</v>
+        <v>125015299</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7540,25 +7540,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385779</v>
+        <v>385588</v>
       </c>
       <c r="R63" t="n">
-        <v>6797286</v>
+        <v>6797184</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7613,7 +7613,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7640,10 +7645,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125014817</v>
+        <v>125016771</v>
       </c>
       <c r="B64" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7652,25 +7657,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7680,10 +7685,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385541</v>
+        <v>385674</v>
       </c>
       <c r="R64" t="n">
-        <v>6797264</v>
+        <v>6796981</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7715,7 +7720,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7725,12 +7730,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Vid myr, tjärn</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7757,7 +7757,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125014604</v>
+        <v>125010560</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385586</v>
+        <v>385763</v>
       </c>
       <c r="R65" t="n">
-        <v>6797242</v>
+        <v>6797307</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7869,10 +7869,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125014307</v>
+        <v>125014604</v>
       </c>
       <c r="B66" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7885,21 +7885,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7909,10 +7909,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385616</v>
+        <v>385586</v>
       </c>
       <c r="R66" t="n">
-        <v>6797214</v>
+        <v>6797242</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7981,10 +7981,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125009952</v>
+        <v>125014817</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7993,25 +7993,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385760</v>
+        <v>385541</v>
       </c>
       <c r="R67" t="n">
-        <v>6797317</v>
+        <v>6797264</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8066,7 +8066,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8093,10 +8098,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014769</v>
+        <v>125014342</v>
       </c>
       <c r="B68" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8109,21 +8114,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8133,10 +8138,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385552</v>
+        <v>385611</v>
       </c>
       <c r="R68" t="n">
-        <v>6797252</v>
+        <v>6797222</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8168,7 +8173,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8178,12 +8183,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Vid myr, källa?</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8210,10 +8210,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125006056</v>
+        <v>125014700</v>
       </c>
       <c r="B69" t="n">
-        <v>56722</v>
+        <v>79919</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8226,45 +8226,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385924</v>
+        <v>385567</v>
       </c>
       <c r="R69" t="n">
-        <v>6797115</v>
+        <v>6797275</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8293,7 +8285,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8303,7 +8295,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8330,10 +8322,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125008520</v>
+        <v>125010269</v>
       </c>
       <c r="B70" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8346,21 +8338,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8370,13 +8362,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385868</v>
+        <v>385756</v>
       </c>
       <c r="R70" t="n">
-        <v>6797226</v>
+        <v>6797314</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8405,7 +8397,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8415,7 +8407,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8442,10 +8439,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125014588</v>
+        <v>125006056</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8454,41 +8451,49 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385586</v>
+        <v>385924</v>
       </c>
       <c r="R71" t="n">
-        <v>6797244</v>
+        <v>6797115</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8517,7 +8522,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8527,12 +8532,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125004576</v>
+        <v>125004366</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R3" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125004345</v>
+        <v>125004324</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125004324</v>
+        <v>125004587</v>
       </c>
       <c r="B5" t="n">
         <v>78546</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R5" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125004587</v>
+        <v>125004345</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R6" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004366</v>
+        <v>125004576</v>
       </c>
       <c r="B7" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R7" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125008543</v>
+        <v>125014057</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385867</v>
+        <v>385607</v>
       </c>
       <c r="R9" t="n">
-        <v>6797219</v>
+        <v>6797159</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125008432</v>
+        <v>125015390</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385888</v>
+        <v>385632</v>
       </c>
       <c r="R10" t="n">
-        <v>6797224</v>
+        <v>6797173</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125015275</v>
+        <v>125014208</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385609</v>
+        <v>385699</v>
       </c>
       <c r="R11" t="n">
-        <v>6797178</v>
+        <v>6797223</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125014208</v>
+        <v>125009359</v>
       </c>
       <c r="B12" t="n">
-        <v>79399</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385699</v>
+        <v>385862</v>
       </c>
       <c r="R12" t="n">
-        <v>6797223</v>
+        <v>6797329</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,19 +1895,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125014035</v>
+        <v>125015347</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385607</v>
+        <v>385592</v>
       </c>
       <c r="R13" t="n">
-        <v>6797159</v>
+        <v>6797161</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,22 +2007,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125015401</v>
+        <v>125009430</v>
       </c>
       <c r="B14" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385632</v>
+        <v>385862</v>
       </c>
       <c r="R14" t="n">
-        <v>6797173</v>
+        <v>6797329</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125010553</v>
+        <v>125014757</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385876</v>
+        <v>385618</v>
       </c>
       <c r="R15" t="n">
-        <v>6797310</v>
+        <v>6797202</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125015390</v>
+        <v>125009342</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>79892</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385632</v>
+        <v>385861</v>
       </c>
       <c r="R16" t="n">
-        <v>6797173</v>
+        <v>6797324</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125013825</v>
+        <v>125008003</v>
       </c>
       <c r="B17" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385689</v>
+        <v>385900</v>
       </c>
       <c r="R17" t="n">
-        <v>6797243</v>
+        <v>6797194</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,19 +2455,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125010604</v>
+        <v>125013949</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2510,7 +2510,7 @@
         <v>385633</v>
       </c>
       <c r="R18" t="n">
-        <v>6797363</v>
+        <v>6797184</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125013977</v>
+        <v>125010031</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385623</v>
+        <v>385750</v>
       </c>
       <c r="R19" t="n">
-        <v>6797166</v>
+        <v>6797429</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125008665</v>
+        <v>125008604</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385900</v>
+        <v>385867</v>
       </c>
       <c r="R20" t="n">
-        <v>6797194</v>
+        <v>6797219</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,22 +2791,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125013776</v>
+        <v>125010542</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385692</v>
+        <v>385634</v>
       </c>
       <c r="R21" t="n">
-        <v>6797239</v>
+        <v>6797413</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125008003</v>
+        <v>125013825</v>
       </c>
       <c r="B23" t="n">
-        <v>79399</v>
+        <v>79892</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385900</v>
+        <v>385689</v>
       </c>
       <c r="R23" t="n">
-        <v>6797194</v>
+        <v>6797243</v>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,12 +3127,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3251,7 +3251,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125006076</v>
+        <v>125008432</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3291,13 +3291,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385896</v>
+        <v>385888</v>
       </c>
       <c r="R25" t="n">
-        <v>6797101</v>
+        <v>6797224</v>
       </c>
       <c r="S25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3351,22 +3351,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125015572</v>
+        <v>125014011</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,38 +3375,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385709</v>
+        <v>385610</v>
       </c>
       <c r="R26" t="n">
-        <v>6797118</v>
+        <v>6797160</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3438,7 +3450,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3460,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,10 +3487,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125011580</v>
+        <v>125010553</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3503,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,13 +3527,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385738</v>
+        <v>385876</v>
       </c>
       <c r="R27" t="n">
-        <v>6797251</v>
+        <v>6797310</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3550,7 +3562,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3572,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,7 +3599,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125016901</v>
+        <v>125010604</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3627,10 +3639,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385697</v>
+        <v>385633</v>
       </c>
       <c r="R28" t="n">
-        <v>6796929</v>
+        <v>6797363</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3662,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3684,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,10 +3711,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125015347</v>
+        <v>125011580</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3715,21 +3727,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3739,13 +3751,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385592</v>
+        <v>385738</v>
       </c>
       <c r="R29" t="n">
-        <v>6797161</v>
+        <v>6797251</v>
       </c>
       <c r="S29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3774,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3784,7 +3796,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,10 +3823,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125013949</v>
+        <v>125015797</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3827,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3851,13 +3863,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385633</v>
+        <v>385690</v>
       </c>
       <c r="R30" t="n">
-        <v>6797184</v>
+        <v>6797129</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3886,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3896,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3911,22 +3923,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125014510</v>
+        <v>125008665</v>
       </c>
       <c r="B31" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3939,21 +3951,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3963,13 +3975,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385699</v>
+        <v>385900</v>
       </c>
       <c r="R31" t="n">
-        <v>6797223</v>
+        <v>6797194</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3998,7 +4010,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4008,7 +4020,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,10 +4047,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125012816</v>
+        <v>125014510</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,21 +4063,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4075,13 +4087,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385738</v>
+        <v>385699</v>
       </c>
       <c r="R32" t="n">
-        <v>6797251</v>
+        <v>6797223</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4110,7 +4122,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4120,7 +4132,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,10 +4159,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125009359</v>
+        <v>125009781</v>
       </c>
       <c r="B33" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4163,21 +4175,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4222,7 +4234,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4232,7 +4244,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,10 +4271,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125014757</v>
+        <v>125014812</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4275,21 +4287,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4334,7 +4346,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4344,7 +4356,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,10 +4383,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125016946</v>
+        <v>125007590</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4387,21 +4399,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4411,13 +4423,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385697</v>
+        <v>385922</v>
       </c>
       <c r="R35" t="n">
-        <v>6796899</v>
+        <v>6797211</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4446,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4456,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4471,22 +4483,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125015797</v>
+        <v>125016913</v>
       </c>
       <c r="B36" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4499,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,13 +4535,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385690</v>
+        <v>385697</v>
       </c>
       <c r="R36" t="n">
-        <v>6797129</v>
+        <v>6796929</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4558,7 +4570,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4580,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,19 +4595,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125006190</v>
+        <v>125006076</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4635,13 +4647,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385871</v>
+        <v>385896</v>
       </c>
       <c r="R37" t="n">
-        <v>6797143</v>
+        <v>6797101</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4670,7 +4682,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4680,7 +4692,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4695,19 +4707,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125010031</v>
+        <v>125006190</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4747,10 +4759,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385750</v>
+        <v>385871</v>
       </c>
       <c r="R38" t="n">
-        <v>6797429</v>
+        <v>6797143</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4782,7 +4794,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4792,7 +4804,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,10 +4831,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125014011</v>
+        <v>125015401</v>
       </c>
       <c r="B39" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4831,50 +4843,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385610</v>
+        <v>385632</v>
       </c>
       <c r="R39" t="n">
-        <v>6797160</v>
+        <v>6797173</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4943,7 +4943,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125007590</v>
+        <v>125015273</v>
       </c>
       <c r="B40" t="n">
         <v>78547</v>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385922</v>
+        <v>385579</v>
       </c>
       <c r="R40" t="n">
-        <v>6797211</v>
+        <v>6797173</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5055,10 +5055,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125010542</v>
+        <v>125012816</v>
       </c>
       <c r="B41" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385634</v>
+        <v>385738</v>
       </c>
       <c r="R41" t="n">
-        <v>6797413</v>
+        <v>6797251</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,22 +5155,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125009342</v>
+        <v>125015297</v>
       </c>
       <c r="B42" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5183,21 +5183,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385861</v>
+        <v>385569</v>
       </c>
       <c r="R42" t="n">
-        <v>6797324</v>
+        <v>6797152</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5267,22 +5267,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125009430</v>
+        <v>125013776</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5295,21 +5295,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385862</v>
+        <v>385692</v>
       </c>
       <c r="R43" t="n">
-        <v>6797329</v>
+        <v>6797239</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5391,10 +5391,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125014812</v>
+        <v>125015572</v>
       </c>
       <c r="B44" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385618</v>
+        <v>385709</v>
       </c>
       <c r="R44" t="n">
-        <v>6797202</v>
+        <v>6797118</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5491,22 +5491,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125009781</v>
+        <v>125013977</v>
       </c>
       <c r="B45" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5519,21 +5519,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5543,10 +5543,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385862</v>
+        <v>385623</v>
       </c>
       <c r="R45" t="n">
-        <v>6797329</v>
+        <v>6797166</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5615,10 +5615,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125015297</v>
+        <v>125014099</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385569</v>
+        <v>385699</v>
       </c>
       <c r="R46" t="n">
-        <v>6797152</v>
+        <v>6797223</v>
       </c>
       <c r="S46" t="n">
         <v>11</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5727,10 +5727,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125014099</v>
+        <v>125015275</v>
       </c>
       <c r="B47" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5743,21 +5743,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5767,13 +5767,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385699</v>
+        <v>385609</v>
       </c>
       <c r="R47" t="n">
-        <v>6797223</v>
+        <v>6797178</v>
       </c>
       <c r="S47" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5827,22 +5827,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125015273</v>
+        <v>125016946</v>
       </c>
       <c r="B48" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,13 +5879,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385579</v>
+        <v>385697</v>
       </c>
       <c r="R48" t="n">
-        <v>6797173</v>
+        <v>6796899</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5939,22 +5939,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125008506</v>
+        <v>125014700</v>
       </c>
       <c r="B49" t="n">
-        <v>78546</v>
+        <v>79919</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5963,25 +5963,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385867</v>
+        <v>385567</v>
       </c>
       <c r="R49" t="n">
-        <v>6797218</v>
+        <v>6797275</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6063,10 +6063,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125014685</v>
+        <v>125014604</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6079,37 +6079,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385571</v>
+        <v>385586</v>
       </c>
       <c r="R50" t="n">
-        <v>6797259</v>
+        <v>6797242</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6141,7 +6138,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6151,7 +6148,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6160,7 +6157,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6179,10 +6175,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125014307</v>
+        <v>125009952</v>
       </c>
       <c r="B51" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6195,21 +6191,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6219,13 +6215,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385616</v>
+        <v>385760</v>
       </c>
       <c r="R51" t="n">
-        <v>6797214</v>
+        <v>6797317</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6254,7 +6250,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6264,7 +6260,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6291,10 +6287,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125016157</v>
+        <v>125015299</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6307,21 +6303,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6331,10 +6327,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385706</v>
+        <v>385588</v>
       </c>
       <c r="R52" t="n">
-        <v>6797113</v>
+        <v>6797184</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6366,7 +6362,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6376,7 +6372,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6403,10 +6404,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125011588</v>
+        <v>125074279</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6415,41 +6416,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385737</v>
+        <v>385755</v>
       </c>
       <c r="R53" t="n">
-        <v>6797241</v>
+        <v>6797321</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6476,27 +6481,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6508,17 +6504,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125074279</v>
+        <v>125014307</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6527,42 +6523,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sätern, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385755</v>
+        <v>385616</v>
       </c>
       <c r="R54" t="n">
-        <v>6797321</v>
+        <v>6797214</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6592,18 +6584,27 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6615,14 +6616,14 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125015566</v>
+        <v>125008506</v>
       </c>
       <c r="B55" t="n">
         <v>78546</v>
@@ -6662,10 +6663,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385640</v>
+        <v>385867</v>
       </c>
       <c r="R55" t="n">
-        <v>6797141</v>
+        <v>6797218</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6697,7 +6698,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6707,7 +6708,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6851,10 +6852,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125010793</v>
+        <v>125016157</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6863,25 +6864,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6891,10 +6892,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385779</v>
+        <v>385706</v>
       </c>
       <c r="R57" t="n">
-        <v>6797286</v>
+        <v>6797113</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6926,7 +6927,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6936,7 +6937,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6963,10 +6964,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125008520</v>
+        <v>125014853</v>
       </c>
       <c r="B58" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6979,21 +6980,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7003,10 +7004,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385868</v>
+        <v>385539</v>
       </c>
       <c r="R58" t="n">
-        <v>6797226</v>
+        <v>6797252</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7038,7 +7039,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7048,7 +7049,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7075,10 +7076,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125014083</v>
+        <v>125016771</v>
       </c>
       <c r="B59" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7091,21 +7092,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7115,13 +7116,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385689</v>
+        <v>385674</v>
       </c>
       <c r="R59" t="n">
-        <v>6797223</v>
+        <v>6796981</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7150,7 +7151,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7160,7 +7161,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7187,7 +7188,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125014853</v>
+        <v>125014685</v>
       </c>
       <c r="B60" t="n">
         <v>79891</v>
@@ -7221,16 +7222,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385539</v>
+        <v>385571</v>
       </c>
       <c r="R60" t="n">
-        <v>6797252</v>
+        <v>6797259</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7262,7 +7266,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7272,7 +7276,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7281,6 +7285,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7299,10 +7304,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125014769</v>
+        <v>125014342</v>
       </c>
       <c r="B61" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7315,21 +7320,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7339,10 +7344,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385552</v>
+        <v>385611</v>
       </c>
       <c r="R61" t="n">
-        <v>6797252</v>
+        <v>6797222</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7374,7 +7379,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7384,12 +7389,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Vid myr, källa?</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7416,10 +7416,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125009952</v>
+        <v>125014083</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7432,21 +7432,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385760</v>
+        <v>385689</v>
       </c>
       <c r="R62" t="n">
-        <v>6797317</v>
+        <v>6797223</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7528,10 +7528,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125015299</v>
+        <v>125008520</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7544,21 +7544,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385588</v>
+        <v>385868</v>
       </c>
       <c r="R63" t="n">
-        <v>6797184</v>
+        <v>6797226</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7613,12 +7613,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7645,7 +7640,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125016771</v>
+        <v>125010560</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7685,10 +7680,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385674</v>
+        <v>385763</v>
       </c>
       <c r="R64" t="n">
-        <v>6796981</v>
+        <v>6797307</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7720,7 +7715,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7730,7 +7725,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7757,10 +7752,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125010560</v>
+        <v>125006056</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7769,41 +7764,49 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385763</v>
+        <v>385924</v>
       </c>
       <c r="R65" t="n">
-        <v>6797307</v>
+        <v>6797115</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7832,7 +7835,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7842,7 +7845,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7869,10 +7872,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125014604</v>
+        <v>125010793</v>
       </c>
       <c r="B66" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7881,25 +7884,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7909,10 +7912,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385586</v>
+        <v>385779</v>
       </c>
       <c r="R66" t="n">
-        <v>6797242</v>
+        <v>6797286</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7944,7 +7947,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7954,7 +7957,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7981,10 +7984,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125014817</v>
+        <v>125014769</v>
       </c>
       <c r="B67" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7993,25 +7996,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8021,10 +8024,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385541</v>
+        <v>385552</v>
       </c>
       <c r="R67" t="n">
-        <v>6797264</v>
+        <v>6797252</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8056,7 +8059,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8066,12 +8069,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Vid myr, tjärn</t>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8098,10 +8101,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014342</v>
+        <v>125011588</v>
       </c>
       <c r="B68" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8114,21 +8117,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8138,13 +8141,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385611</v>
+        <v>385737</v>
       </c>
       <c r="R68" t="n">
-        <v>6797222</v>
+        <v>6797241</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8173,7 +8176,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8183,7 +8186,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8210,7 +8213,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014700</v>
+        <v>125014817</v>
       </c>
       <c r="B69" t="n">
         <v>79919</v>
@@ -8250,10 +8253,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385567</v>
+        <v>385541</v>
       </c>
       <c r="R69" t="n">
-        <v>6797275</v>
+        <v>6797264</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8285,7 +8288,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8295,7 +8298,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8439,10 +8447,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125006056</v>
+        <v>125015566</v>
       </c>
       <c r="B71" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8451,49 +8459,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385924</v>
+        <v>385640</v>
       </c>
       <c r="R71" t="n">
-        <v>6797115</v>
+        <v>6797141</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125009359</v>
+        <v>125015347</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385862</v>
+        <v>385592</v>
       </c>
       <c r="R12" t="n">
-        <v>6797329</v>
+        <v>6797161</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,19 +1895,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125015347</v>
+        <v>125009430</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385592</v>
+        <v>385862</v>
       </c>
       <c r="R13" t="n">
-        <v>6797161</v>
+        <v>6797329</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,22 +2007,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125009430</v>
+        <v>125009359</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125014757</v>
+        <v>125008003</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385618</v>
+        <v>385900</v>
       </c>
       <c r="R15" t="n">
-        <v>6797202</v>
+        <v>6797194</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125009342</v>
+        <v>125014757</v>
       </c>
       <c r="B16" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385861</v>
+        <v>385618</v>
       </c>
       <c r="R16" t="n">
-        <v>6797324</v>
+        <v>6797202</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,22 +2343,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125008003</v>
+        <v>125009342</v>
       </c>
       <c r="B17" t="n">
-        <v>79399</v>
+        <v>79892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385900</v>
+        <v>385861</v>
       </c>
       <c r="R17" t="n">
-        <v>6797194</v>
+        <v>6797324</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,12 +2455,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125013825</v>
+        <v>125010000</v>
       </c>
       <c r="B23" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385689</v>
+        <v>385749</v>
       </c>
       <c r="R23" t="n">
-        <v>6797243</v>
+        <v>6797429</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,7 +3139,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125010000</v>
+        <v>125008432</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385749</v>
+        <v>385888</v>
       </c>
       <c r="R24" t="n">
-        <v>6797429</v>
+        <v>6797224</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125008432</v>
+        <v>125014011</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,38 +3263,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385888</v>
+        <v>385610</v>
       </c>
       <c r="R25" t="n">
-        <v>6797224</v>
+        <v>6797160</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3326,7 +3338,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3348,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125014011</v>
+        <v>125013825</v>
       </c>
       <c r="B26" t="n">
-        <v>56722</v>
+        <v>79892</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,50 +3387,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385610</v>
+        <v>385689</v>
       </c>
       <c r="R26" t="n">
-        <v>6797160</v>
+        <v>6797243</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3823,10 +3823,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125015797</v>
+        <v>125008665</v>
       </c>
       <c r="B30" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3839,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385690</v>
+        <v>385900</v>
       </c>
       <c r="R30" t="n">
-        <v>6797129</v>
+        <v>6797194</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125008665</v>
+        <v>125015797</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3975,13 +3975,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385900</v>
+        <v>385690</v>
       </c>
       <c r="R31" t="n">
-        <v>6797194</v>
+        <v>6797129</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -6511,7 +6511,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125014307</v>
+        <v>125008506</v>
       </c>
       <c r="B54" t="n">
         <v>78546</v>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385616</v>
+        <v>385867</v>
       </c>
       <c r="R54" t="n">
-        <v>6797214</v>
+        <v>6797218</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6623,10 +6623,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125008506</v>
+        <v>125014588</v>
       </c>
       <c r="B55" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6639,21 +6639,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385867</v>
+        <v>385586</v>
       </c>
       <c r="R55" t="n">
-        <v>6797218</v>
+        <v>6797244</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6708,7 +6708,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6735,10 +6740,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125014588</v>
+        <v>125014307</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6751,21 +6756,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6775,10 +6780,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385586</v>
+        <v>385616</v>
       </c>
       <c r="R56" t="n">
-        <v>6797244</v>
+        <v>6797214</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6810,7 +6815,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6820,12 +6825,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7076,10 +7076,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125016771</v>
+        <v>125014342</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7092,21 +7092,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7116,10 +7116,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385674</v>
+        <v>385611</v>
       </c>
       <c r="R59" t="n">
-        <v>6796981</v>
+        <v>6797222</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7188,10 +7188,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125014685</v>
+        <v>125016771</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7204,37 +7204,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385571</v>
+        <v>385674</v>
       </c>
       <c r="R60" t="n">
-        <v>6797259</v>
+        <v>6796981</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7266,7 +7263,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7276,7 +7273,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7285,7 +7282,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7304,10 +7300,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125014342</v>
+        <v>125014685</v>
       </c>
       <c r="B61" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7320,34 +7316,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385611</v>
+        <v>385571</v>
       </c>
       <c r="R61" t="n">
-        <v>6797222</v>
+        <v>6797259</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7379,7 +7378,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7389,7 +7388,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7398,6 +7397,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7752,10 +7752,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125006056</v>
+        <v>125010793</v>
       </c>
       <c r="B65" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7764,49 +7764,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385924</v>
+        <v>385779</v>
       </c>
       <c r="R65" t="n">
-        <v>6797115</v>
+        <v>6797286</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7835,7 +7827,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7845,7 +7837,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7872,10 +7864,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125010793</v>
+        <v>125006056</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7884,41 +7876,49 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385779</v>
+        <v>385924</v>
       </c>
       <c r="R66" t="n">
-        <v>6797286</v>
+        <v>6797115</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7957,7 +7957,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8330,10 +8330,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125010269</v>
+        <v>125015566</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8346,21 +8346,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8370,13 +8370,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385756</v>
+        <v>385640</v>
       </c>
       <c r="R70" t="n">
-        <v>6797314</v>
+        <v>6797141</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8415,12 +8415,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8447,10 +8442,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125015566</v>
+        <v>125010269</v>
       </c>
       <c r="B71" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8463,21 +8458,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8487,13 +8482,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385640</v>
+        <v>385756</v>
       </c>
       <c r="R71" t="n">
-        <v>6797141</v>
+        <v>6797314</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8522,7 +8517,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8532,7 +8527,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125015347</v>
+        <v>125009359</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385592</v>
+        <v>385862</v>
       </c>
       <c r="R12" t="n">
-        <v>6797161</v>
+        <v>6797329</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,19 +1895,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125009430</v>
+        <v>125015347</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385862</v>
+        <v>385592</v>
       </c>
       <c r="R13" t="n">
-        <v>6797329</v>
+        <v>6797161</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,22 +2007,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125009359</v>
+        <v>125009430</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125008003</v>
+        <v>125009342</v>
       </c>
       <c r="B15" t="n">
-        <v>79399</v>
+        <v>79892</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385900</v>
+        <v>385861</v>
       </c>
       <c r="R15" t="n">
-        <v>6797194</v>
+        <v>6797324</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,12 +2231,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125009342</v>
+        <v>125008003</v>
       </c>
       <c r="B17" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385861</v>
+        <v>385900</v>
       </c>
       <c r="R17" t="n">
-        <v>6797324</v>
+        <v>6797194</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,12 +2455,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125010604</v>
+        <v>125011580</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3615,21 +3615,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3639,13 +3639,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385633</v>
+        <v>385738</v>
       </c>
       <c r="R28" t="n">
-        <v>6797363</v>
+        <v>6797251</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,22 +3699,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125011580</v>
+        <v>125010604</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3727,21 +3727,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3751,13 +3751,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385738</v>
+        <v>385633</v>
       </c>
       <c r="R29" t="n">
-        <v>6797251</v>
+        <v>6797363</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,12 +3811,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4047,10 +4047,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125014510</v>
+        <v>125009781</v>
       </c>
       <c r="B32" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4087,13 +4087,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385699</v>
+        <v>385862</v>
       </c>
       <c r="R32" t="n">
-        <v>6797223</v>
+        <v>6797329</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,22 +4147,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125009781</v>
+        <v>125014510</v>
       </c>
       <c r="B33" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4175,21 +4175,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4199,13 +4199,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385862</v>
+        <v>385699</v>
       </c>
       <c r="R33" t="n">
-        <v>6797329</v>
+        <v>6797223</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,22 +4259,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125014812</v>
+        <v>125016913</v>
       </c>
       <c r="B34" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385618</v>
+        <v>385697</v>
       </c>
       <c r="R34" t="n">
-        <v>6797202</v>
+        <v>6796929</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,19 +4371,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125007590</v>
+        <v>125014812</v>
       </c>
       <c r="B35" t="n">
         <v>78547</v>
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385922</v>
+        <v>385618</v>
       </c>
       <c r="R35" t="n">
-        <v>6797211</v>
+        <v>6797202</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,10 +4495,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125016913</v>
+        <v>125007590</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385697</v>
+        <v>385922</v>
       </c>
       <c r="R36" t="n">
-        <v>6796929</v>
+        <v>6797211</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4595,12 +4595,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125006190</v>
+        <v>125015273</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4735,21 +4735,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385871</v>
+        <v>385579</v>
       </c>
       <c r="R38" t="n">
-        <v>6797143</v>
+        <v>6797173</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,22 +4819,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125015401</v>
+        <v>125006190</v>
       </c>
       <c r="B39" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385632</v>
+        <v>385871</v>
       </c>
       <c r="R39" t="n">
-        <v>6797173</v>
+        <v>6797143</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4943,10 +4943,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125015273</v>
+        <v>125015401</v>
       </c>
       <c r="B40" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385579</v>
+        <v>385632</v>
       </c>
       <c r="R40" t="n">
         <v>6797173</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,12 +5043,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5951,10 +5951,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125014700</v>
+        <v>125014604</v>
       </c>
       <c r="B49" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5963,25 +5963,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385567</v>
+        <v>385586</v>
       </c>
       <c r="R49" t="n">
-        <v>6797275</v>
+        <v>6797242</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6063,10 +6063,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125014604</v>
+        <v>125014700</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6075,25 +6075,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6103,10 +6103,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385586</v>
+        <v>385567</v>
       </c>
       <c r="R50" t="n">
-        <v>6797242</v>
+        <v>6797275</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -8330,10 +8330,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125015566</v>
+        <v>125010269</v>
       </c>
       <c r="B70" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8346,21 +8346,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8370,13 +8370,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385640</v>
+        <v>385756</v>
       </c>
       <c r="R70" t="n">
-        <v>6797141</v>
+        <v>6797314</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8415,7 +8415,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8442,10 +8447,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125010269</v>
+        <v>125015566</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8458,21 +8463,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8482,13 +8487,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385756</v>
+        <v>385640</v>
       </c>
       <c r="R71" t="n">
-        <v>6797314</v>
+        <v>6797141</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8517,7 +8522,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8527,12 +8532,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125004665</v>
+        <v>125004576</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125004366</v>
+        <v>125004665</v>
       </c>
       <c r="B3" t="n">
-        <v>79399</v>
+        <v>79428</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R3" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125004324</v>
+        <v>125004345</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125004345</v>
+        <v>125004324</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004576</v>
+        <v>125004366</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>79399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R7" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125014057</v>
+        <v>125011580</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385607</v>
+        <v>385738</v>
       </c>
       <c r="R9" t="n">
-        <v>6797159</v>
+        <v>6797251</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,22 +1559,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125015390</v>
+        <v>125013977</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385632</v>
+        <v>385623</v>
       </c>
       <c r="R10" t="n">
-        <v>6797173</v>
+        <v>6797166</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125014208</v>
+        <v>125015297</v>
       </c>
       <c r="B11" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385699</v>
+        <v>385569</v>
       </c>
       <c r="R11" t="n">
-        <v>6797223</v>
+        <v>6797152</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125009359</v>
+        <v>125015273</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385862</v>
+        <v>385579</v>
       </c>
       <c r="R12" t="n">
-        <v>6797329</v>
+        <v>6797173</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,22 +1895,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125015347</v>
+        <v>125010553</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385592</v>
+        <v>385876</v>
       </c>
       <c r="R13" t="n">
-        <v>6797161</v>
+        <v>6797310</v>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125009430</v>
+        <v>125008585</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385862</v>
+        <v>385867</v>
       </c>
       <c r="R14" t="n">
-        <v>6797329</v>
+        <v>6797219</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125009342</v>
+        <v>125008003</v>
       </c>
       <c r="B15" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385861</v>
+        <v>385900</v>
       </c>
       <c r="R15" t="n">
-        <v>6797324</v>
+        <v>6797194</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,22 +2231,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125014757</v>
+        <v>125007590</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385618</v>
+        <v>385922</v>
       </c>
       <c r="R16" t="n">
-        <v>6797202</v>
+        <v>6797211</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125008003</v>
+        <v>125014208</v>
       </c>
       <c r="B17" t="n">
         <v>79399</v>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385900</v>
+        <v>385699</v>
       </c>
       <c r="R17" t="n">
-        <v>6797194</v>
+        <v>6797223</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,7 +2467,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125013949</v>
+        <v>125008665</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385633</v>
+        <v>385900</v>
       </c>
       <c r="R18" t="n">
-        <v>6797184</v>
+        <v>6797194</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,22 +2567,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125010031</v>
+        <v>125009359</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385750</v>
+        <v>385862</v>
       </c>
       <c r="R19" t="n">
-        <v>6797429</v>
+        <v>6797329</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125008604</v>
+        <v>125006190</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385867</v>
+        <v>385871</v>
       </c>
       <c r="R20" t="n">
-        <v>6797219</v>
+        <v>6797143</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125010542</v>
+        <v>125015572</v>
       </c>
       <c r="B21" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385634</v>
+        <v>385709</v>
       </c>
       <c r="R21" t="n">
-        <v>6797413</v>
+        <v>6797118</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125009311</v>
+        <v>125016913</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385900</v>
+        <v>385697</v>
       </c>
       <c r="R22" t="n">
-        <v>6797194</v>
+        <v>6796929</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,19 +3015,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125010000</v>
+        <v>125012816</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385749</v>
+        <v>385738</v>
       </c>
       <c r="R23" t="n">
-        <v>6797429</v>
+        <v>6797251</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,22 +3127,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125008432</v>
+        <v>125013825</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385888</v>
+        <v>385689</v>
       </c>
       <c r="R24" t="n">
-        <v>6797224</v>
+        <v>6797243</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014011</v>
+        <v>125010542</v>
       </c>
       <c r="B25" t="n">
-        <v>56722</v>
+        <v>78546</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,50 +3263,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385610</v>
+        <v>385634</v>
       </c>
       <c r="R25" t="n">
-        <v>6797160</v>
+        <v>6797413</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3338,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3348,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3375,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125013825</v>
+        <v>125015347</v>
       </c>
       <c r="B26" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3391,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3415,13 +3403,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385689</v>
+        <v>385592</v>
       </c>
       <c r="R26" t="n">
-        <v>6797243</v>
+        <v>6797161</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3450,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3460,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,22 +3463,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125010553</v>
+        <v>125009342</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>79892</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3503,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3527,13 +3515,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385876</v>
+        <v>385861</v>
       </c>
       <c r="R27" t="n">
-        <v>6797310</v>
+        <v>6797324</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3562,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3572,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,19 +3575,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125011580</v>
+        <v>125013776</v>
       </c>
       <c r="B28" t="n">
         <v>79891</v>
@@ -3639,13 +3627,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385738</v>
+        <v>385692</v>
       </c>
       <c r="R28" t="n">
-        <v>6797251</v>
+        <v>6797239</v>
       </c>
       <c r="S28" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3674,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,19 +3687,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125010604</v>
+        <v>125015275</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3751,10 +3739,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385633</v>
+        <v>385609</v>
       </c>
       <c r="R29" t="n">
-        <v>6797363</v>
+        <v>6797178</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3786,7 +3774,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,7 +3784,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3823,7 +3811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125008665</v>
+        <v>125014757</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3863,13 +3851,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385900</v>
+        <v>385618</v>
       </c>
       <c r="R30" t="n">
-        <v>6797194</v>
+        <v>6797202</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,7 +3886,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3896,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,10 +3923,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125015797</v>
+        <v>125014057</v>
       </c>
       <c r="B31" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3951,21 +3939,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3975,13 +3963,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385690</v>
+        <v>385607</v>
       </c>
       <c r="R31" t="n">
-        <v>6797129</v>
+        <v>6797159</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,7 +3998,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4020,7 +4008,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,22 +4023,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125009781</v>
+        <v>125014011</v>
       </c>
       <c r="B32" t="n">
-        <v>78546</v>
+        <v>56722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4059,38 +4047,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385862</v>
+        <v>385610</v>
       </c>
       <c r="R32" t="n">
-        <v>6797329</v>
+        <v>6797160</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4271,7 +4271,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125016913</v>
+        <v>125009430</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385697</v>
+        <v>385862</v>
       </c>
       <c r="R34" t="n">
-        <v>6796929</v>
+        <v>6797329</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4383,10 +4383,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125014812</v>
+        <v>125010031</v>
       </c>
       <c r="B35" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4399,21 +4399,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385618</v>
+        <v>385750</v>
       </c>
       <c r="R35" t="n">
-        <v>6797202</v>
+        <v>6797429</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,22 +4483,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125007590</v>
+        <v>125006076</v>
       </c>
       <c r="B36" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385922</v>
+        <v>385896</v>
       </c>
       <c r="R36" t="n">
-        <v>6797211</v>
+        <v>6797101</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,7 +4607,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125006076</v>
+        <v>125016946</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4647,13 +4647,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385896</v>
+        <v>385697</v>
       </c>
       <c r="R37" t="n">
-        <v>6797101</v>
+        <v>6796899</v>
       </c>
       <c r="S37" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4707,22 +4707,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125015273</v>
+        <v>125009311</v>
       </c>
       <c r="B38" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4735,21 +4735,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385579</v>
+        <v>385900</v>
       </c>
       <c r="R38" t="n">
-        <v>6797173</v>
+        <v>6797194</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4831,10 +4831,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125006190</v>
+        <v>125014812</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385871</v>
+        <v>385618</v>
       </c>
       <c r="R39" t="n">
-        <v>6797143</v>
+        <v>6797202</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4931,19 +4931,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125015401</v>
+        <v>125009781</v>
       </c>
       <c r="B40" t="n">
         <v>78546</v>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385632</v>
+        <v>385862</v>
       </c>
       <c r="R40" t="n">
-        <v>6797173</v>
+        <v>6797329</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5055,10 +5055,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125012816</v>
+        <v>125015390</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385738</v>
+        <v>385632</v>
       </c>
       <c r="R41" t="n">
-        <v>6797251</v>
+        <v>6797173</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,22 +5155,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125015297</v>
+        <v>125014099</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5183,21 +5183,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5207,10 +5207,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385569</v>
+        <v>385699</v>
       </c>
       <c r="R42" t="n">
-        <v>6797152</v>
+        <v>6797223</v>
       </c>
       <c r="S42" t="n">
         <v>11</v>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5279,10 +5279,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125013776</v>
+        <v>125008432</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5295,21 +5295,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385692</v>
+        <v>385888</v>
       </c>
       <c r="R43" t="n">
-        <v>6797239</v>
+        <v>6797224</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5391,10 +5391,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125015572</v>
+        <v>125015401</v>
       </c>
       <c r="B44" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385709</v>
+        <v>385632</v>
       </c>
       <c r="R44" t="n">
-        <v>6797118</v>
+        <v>6797173</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5503,7 +5503,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125013977</v>
+        <v>125013949</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5543,10 +5543,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385623</v>
+        <v>385633</v>
       </c>
       <c r="R45" t="n">
-        <v>6797166</v>
+        <v>6797184</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5615,10 +5615,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125014099</v>
+        <v>125010594</v>
       </c>
       <c r="B46" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385699</v>
+        <v>385633</v>
       </c>
       <c r="R46" t="n">
-        <v>6797223</v>
+        <v>6797363</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5715,19 +5715,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125015275</v>
+        <v>125010000</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385609</v>
+        <v>385749</v>
       </c>
       <c r="R47" t="n">
-        <v>6797178</v>
+        <v>6797429</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125016946</v>
+        <v>125015797</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,13 +5879,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385697</v>
+        <v>385690</v>
       </c>
       <c r="R48" t="n">
-        <v>6796899</v>
+        <v>6797129</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5939,22 +5939,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125014604</v>
+        <v>125014769</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385586</v>
+        <v>385552</v>
       </c>
       <c r="R49" t="n">
-        <v>6797242</v>
+        <v>6797252</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6036,7 +6036,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6063,7 +6068,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125014700</v>
+        <v>125014817</v>
       </c>
       <c r="B50" t="n">
         <v>79919</v>
@@ -6103,10 +6108,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385567</v>
+        <v>385541</v>
       </c>
       <c r="R50" t="n">
-        <v>6797275</v>
+        <v>6797264</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6138,7 +6143,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6148,7 +6153,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6175,10 +6185,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125009952</v>
+        <v>125016157</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6191,21 +6201,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6215,13 +6225,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385760</v>
+        <v>385706</v>
       </c>
       <c r="R51" t="n">
-        <v>6797317</v>
+        <v>6797113</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6250,7 +6260,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6260,7 +6270,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6287,10 +6297,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125015299</v>
+        <v>125014342</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6303,21 +6313,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6327,10 +6337,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385588</v>
+        <v>385611</v>
       </c>
       <c r="R52" t="n">
-        <v>6797184</v>
+        <v>6797222</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6362,7 +6372,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6372,12 +6382,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6404,10 +6409,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125074279</v>
+        <v>125014853</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6416,42 +6421,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sätern, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385755</v>
+        <v>385539</v>
       </c>
       <c r="R53" t="n">
-        <v>6797321</v>
+        <v>6797252</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6481,18 +6482,27 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6504,17 +6514,17 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125008506</v>
+        <v>125011588</v>
       </c>
       <c r="B54" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6527,21 +6537,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6551,13 +6561,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385867</v>
+        <v>385737</v>
       </c>
       <c r="R54" t="n">
-        <v>6797218</v>
+        <v>6797241</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6586,7 +6596,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6596,7 +6606,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6623,10 +6633,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125014588</v>
+        <v>125014083</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6639,21 +6649,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6663,13 +6673,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385586</v>
+        <v>385689</v>
       </c>
       <c r="R55" t="n">
-        <v>6797244</v>
+        <v>6797223</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6698,7 +6708,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6708,12 +6718,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6740,7 +6745,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125014307</v>
+        <v>125008506</v>
       </c>
       <c r="B56" t="n">
         <v>78546</v>
@@ -6780,10 +6785,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385616</v>
+        <v>385867</v>
       </c>
       <c r="R56" t="n">
-        <v>6797214</v>
+        <v>6797218</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6815,7 +6820,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6825,7 +6830,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6852,7 +6857,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125016157</v>
+        <v>125014685</v>
       </c>
       <c r="B57" t="n">
         <v>79891</v>
@@ -6886,16 +6891,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385706</v>
+        <v>385571</v>
       </c>
       <c r="R57" t="n">
-        <v>6797113</v>
+        <v>6797259</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6927,7 +6935,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6937,7 +6945,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6946,6 +6954,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6964,10 +6973,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125014853</v>
+        <v>125006056</v>
       </c>
       <c r="B58" t="n">
-        <v>79891</v>
+        <v>56722</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6976,41 +6985,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385539</v>
+        <v>385924</v>
       </c>
       <c r="R58" t="n">
-        <v>6797252</v>
+        <v>6797115</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7039,7 +7056,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7049,7 +7066,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7076,10 +7093,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125014342</v>
+        <v>125010560</v>
       </c>
       <c r="B59" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7092,21 +7109,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7116,10 +7133,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385611</v>
+        <v>385763</v>
       </c>
       <c r="R59" t="n">
-        <v>6797222</v>
+        <v>6797307</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7151,7 +7168,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7161,7 +7178,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7188,7 +7205,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125016771</v>
+        <v>125014588</v>
       </c>
       <c r="B60" t="n">
         <v>78810</v>
@@ -7228,10 +7245,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385674</v>
+        <v>385586</v>
       </c>
       <c r="R60" t="n">
-        <v>6796981</v>
+        <v>6797244</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7263,7 +7280,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7273,7 +7290,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7300,10 +7322,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125014685</v>
+        <v>125014700</v>
       </c>
       <c r="B61" t="n">
-        <v>79891</v>
+        <v>79919</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7312,41 +7334,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385571</v>
+        <v>385567</v>
       </c>
       <c r="R61" t="n">
-        <v>6797259</v>
+        <v>6797275</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7378,7 +7397,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7388,7 +7407,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7397,7 +7416,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7416,10 +7434,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125014083</v>
+        <v>125010793</v>
       </c>
       <c r="B62" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7428,25 +7446,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7456,13 +7474,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385689</v>
+        <v>385779</v>
       </c>
       <c r="R62" t="n">
-        <v>6797223</v>
+        <v>6797286</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7491,7 +7509,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7501,7 +7519,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7528,10 +7546,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125008520</v>
+        <v>125016771</v>
       </c>
       <c r="B63" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7544,21 +7562,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7568,10 +7586,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385868</v>
+        <v>385674</v>
       </c>
       <c r="R63" t="n">
-        <v>6797226</v>
+        <v>6796981</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7603,7 +7621,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7613,7 +7631,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7640,7 +7658,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125010560</v>
+        <v>125014604</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7680,10 +7698,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385763</v>
+        <v>385586</v>
       </c>
       <c r="R64" t="n">
-        <v>6797307</v>
+        <v>6797242</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7715,7 +7733,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7725,7 +7743,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7752,10 +7770,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125010793</v>
+        <v>125015566</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7764,25 +7782,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7792,10 +7810,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385779</v>
+        <v>385640</v>
       </c>
       <c r="R65" t="n">
-        <v>6797286</v>
+        <v>6797141</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7827,7 +7845,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7837,7 +7855,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7864,10 +7882,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125006056</v>
+        <v>125008520</v>
       </c>
       <c r="B66" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7876,49 +7894,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385924</v>
+        <v>385868</v>
       </c>
       <c r="R66" t="n">
-        <v>6797115</v>
+        <v>6797226</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7947,7 +7957,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7957,7 +7967,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7984,10 +7994,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125014769</v>
+        <v>125074279</v>
       </c>
       <c r="B67" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7996,38 +8006,42 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385552</v>
+        <v>385755</v>
       </c>
       <c r="R67" t="n">
-        <v>6797252</v>
+        <v>6797321</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8057,32 +8071,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Vid myr, källa?</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8094,17 +8094,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125011588</v>
+        <v>125014307</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8117,21 +8117,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8141,13 +8141,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385737</v>
+        <v>385616</v>
       </c>
       <c r="R68" t="n">
-        <v>6797241</v>
+        <v>6797214</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8213,10 +8213,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014817</v>
+        <v>125009952</v>
       </c>
       <c r="B69" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8225,25 +8225,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8253,13 +8253,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385541</v>
+        <v>385760</v>
       </c>
       <c r="R69" t="n">
-        <v>6797264</v>
+        <v>6797317</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8298,12 +8298,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Vid myr, tjärn</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8330,10 +8325,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125010269</v>
+        <v>125015299</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8346,21 +8341,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8370,13 +8365,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385756</v>
+        <v>385588</v>
       </c>
       <c r="R70" t="n">
-        <v>6797314</v>
+        <v>6797184</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8405,7 +8400,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8415,12 +8410,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8447,10 +8442,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125015566</v>
+        <v>125010269</v>
       </c>
       <c r="B71" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8463,21 +8458,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8487,13 +8482,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385640</v>
+        <v>385756</v>
       </c>
       <c r="R71" t="n">
-        <v>6797141</v>
+        <v>6797314</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8522,7 +8517,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8532,7 +8527,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125004665</v>
+        <v>125004366</v>
       </c>
       <c r="B3" t="n">
-        <v>79428</v>
+        <v>79399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R3" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125004345</v>
+        <v>125004324</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125004587</v>
+        <v>125004665</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>79428</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125004324</v>
+        <v>125004345</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004366</v>
+        <v>125004587</v>
       </c>
       <c r="B7" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R7" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125011580</v>
+        <v>125008543</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385738</v>
+        <v>385867</v>
       </c>
       <c r="R9" t="n">
-        <v>6797251</v>
+        <v>6797219</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,22 +1559,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125013977</v>
+        <v>125008003</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385623</v>
+        <v>385900</v>
       </c>
       <c r="R10" t="n">
-        <v>6797166</v>
+        <v>6797194</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,22 +1671,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125015297</v>
+        <v>125011580</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385569</v>
+        <v>385738</v>
       </c>
       <c r="R11" t="n">
-        <v>6797152</v>
+        <v>6797251</v>
       </c>
       <c r="S11" t="n">
         <v>11</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125015273</v>
+        <v>125009311</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385579</v>
+        <v>385900</v>
       </c>
       <c r="R12" t="n">
-        <v>6797173</v>
+        <v>6797194</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125010553</v>
+        <v>125015390</v>
       </c>
       <c r="B13" t="n">
         <v>78547</v>
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385876</v>
+        <v>385632</v>
       </c>
       <c r="R13" t="n">
-        <v>6797310</v>
+        <v>6797173</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,22 +2007,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125008585</v>
+        <v>125007590</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385867</v>
+        <v>385922</v>
       </c>
       <c r="R14" t="n">
-        <v>6797219</v>
+        <v>6797211</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,22 +2119,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125008003</v>
+        <v>125014510</v>
       </c>
       <c r="B15" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385900</v>
+        <v>385699</v>
       </c>
       <c r="R15" t="n">
-        <v>6797194</v>
+        <v>6797223</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125007590</v>
+        <v>125015401</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385922</v>
+        <v>385632</v>
       </c>
       <c r="R16" t="n">
-        <v>6797211</v>
+        <v>6797173</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,22 +2343,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125014208</v>
+        <v>125013776</v>
       </c>
       <c r="B17" t="n">
-        <v>79399</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385699</v>
+        <v>385692</v>
       </c>
       <c r="R17" t="n">
-        <v>6797223</v>
+        <v>6797239</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,19 +2455,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125008665</v>
+        <v>125015297</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385900</v>
+        <v>385569</v>
       </c>
       <c r="R18" t="n">
-        <v>6797194</v>
+        <v>6797152</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125009359</v>
+        <v>125015347</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385862</v>
+        <v>385592</v>
       </c>
       <c r="R19" t="n">
-        <v>6797329</v>
+        <v>6797161</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,22 +2679,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125006190</v>
+        <v>125014208</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385871</v>
+        <v>385699</v>
       </c>
       <c r="R20" t="n">
-        <v>6797143</v>
+        <v>6797223</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,22 +2791,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125015572</v>
+        <v>125010553</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385709</v>
+        <v>385876</v>
       </c>
       <c r="R21" t="n">
-        <v>6797118</v>
+        <v>6797310</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,19 +2903,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125016913</v>
+        <v>125016901</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,7 +3027,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125012816</v>
+        <v>125006076</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385738</v>
+        <v>385896</v>
       </c>
       <c r="R23" t="n">
-        <v>6797251</v>
+        <v>6797101</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125013825</v>
+        <v>125010542</v>
       </c>
       <c r="B24" t="n">
-        <v>79892</v>
+        <v>78546</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385689</v>
+        <v>385634</v>
       </c>
       <c r="R24" t="n">
-        <v>6797243</v>
+        <v>6797413</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125010542</v>
+        <v>125010000</v>
       </c>
       <c r="B25" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385634</v>
+        <v>385749</v>
       </c>
       <c r="R25" t="n">
-        <v>6797413</v>
+        <v>6797429</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,7 +3363,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125015347</v>
+        <v>125010594</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385592</v>
+        <v>385633</v>
       </c>
       <c r="R26" t="n">
-        <v>6797161</v>
+        <v>6797363</v>
       </c>
       <c r="S26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,22 +3463,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125009342</v>
+        <v>125014011</v>
       </c>
       <c r="B27" t="n">
-        <v>79892</v>
+        <v>56722</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,38 +3487,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385861</v>
+        <v>385610</v>
       </c>
       <c r="R27" t="n">
-        <v>6797324</v>
+        <v>6797160</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3550,7 +3562,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3572,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,10 +3599,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125013776</v>
+        <v>125010031</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3615,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3639,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385692</v>
+        <v>385750</v>
       </c>
       <c r="R28" t="n">
-        <v>6797239</v>
+        <v>6797429</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3662,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3684,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,7 +3711,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125015275</v>
+        <v>125013977</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3739,10 +3751,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385609</v>
+        <v>385623</v>
       </c>
       <c r="R29" t="n">
-        <v>6797178</v>
+        <v>6797166</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3774,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3784,7 +3796,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,7 +3823,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125014757</v>
+        <v>125008665</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3851,13 +3863,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385618</v>
+        <v>385900</v>
       </c>
       <c r="R30" t="n">
-        <v>6797202</v>
+        <v>6797194</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3886,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3896,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3923,7 +3935,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125014057</v>
+        <v>125013949</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3963,10 +3975,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385607</v>
+        <v>385633</v>
       </c>
       <c r="R31" t="n">
-        <v>6797159</v>
+        <v>6797184</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3998,7 +4010,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4008,7 +4020,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,10 +4047,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125014011</v>
+        <v>125015273</v>
       </c>
       <c r="B32" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4047,53 +4059,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385610</v>
+        <v>385579</v>
       </c>
       <c r="R32" t="n">
-        <v>6797160</v>
+        <v>6797173</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,22 +4147,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125014510</v>
+        <v>125014035</v>
       </c>
       <c r="B33" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4175,21 +4175,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4199,13 +4199,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385699</v>
+        <v>385607</v>
       </c>
       <c r="R33" t="n">
-        <v>6797223</v>
+        <v>6797159</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,19 +4259,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125009430</v>
+        <v>125016946</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385862</v>
+        <v>385697</v>
       </c>
       <c r="R34" t="n">
-        <v>6797329</v>
+        <v>6796899</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4383,10 +4383,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125010031</v>
+        <v>125009359</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4399,21 +4399,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385750</v>
+        <v>385862</v>
       </c>
       <c r="R35" t="n">
-        <v>6797429</v>
+        <v>6797329</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4495,10 +4495,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125006076</v>
+        <v>125015797</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385896</v>
+        <v>385690</v>
       </c>
       <c r="R36" t="n">
-        <v>6797101</v>
+        <v>6797129</v>
       </c>
       <c r="S36" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4607,10 +4607,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125016946</v>
+        <v>125009342</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385697</v>
+        <v>385861</v>
       </c>
       <c r="R37" t="n">
-        <v>6796899</v>
+        <v>6797324</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4719,10 +4719,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125009311</v>
+        <v>125013825</v>
       </c>
       <c r="B38" t="n">
-        <v>78546</v>
+        <v>79892</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4735,21 +4735,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385900</v>
+        <v>385689</v>
       </c>
       <c r="R38" t="n">
-        <v>6797194</v>
+        <v>6797243</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,22 +4819,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125014812</v>
+        <v>125009781</v>
       </c>
       <c r="B39" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385618</v>
+        <v>385862</v>
       </c>
       <c r="R39" t="n">
-        <v>6797202</v>
+        <v>6797329</v>
       </c>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4931,22 +4931,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125009781</v>
+        <v>125006190</v>
       </c>
       <c r="B40" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4983,10 +4983,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385862</v>
+        <v>385871</v>
       </c>
       <c r="R40" t="n">
-        <v>6797329</v>
+        <v>6797143</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5055,10 +5055,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125015390</v>
+        <v>125014099</v>
       </c>
       <c r="B41" t="n">
-        <v>78547</v>
+        <v>78842</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5071,21 +5071,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385632</v>
+        <v>385699</v>
       </c>
       <c r="R41" t="n">
-        <v>6797173</v>
+        <v>6797223</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,22 +5155,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125014099</v>
+        <v>125014757</v>
       </c>
       <c r="B42" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5183,21 +5183,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385699</v>
+        <v>385618</v>
       </c>
       <c r="R42" t="n">
-        <v>6797223</v>
+        <v>6797202</v>
       </c>
       <c r="S42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5279,7 +5279,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125008432</v>
+        <v>125015275</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385888</v>
+        <v>385609</v>
       </c>
       <c r="R43" t="n">
-        <v>6797224</v>
+        <v>6797178</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5391,10 +5391,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125015401</v>
+        <v>125009430</v>
       </c>
       <c r="B44" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5431,10 +5431,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385632</v>
+        <v>385862</v>
       </c>
       <c r="R44" t="n">
-        <v>6797173</v>
+        <v>6797329</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5503,7 +5503,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125013949</v>
+        <v>125008432</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5543,10 +5543,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385633</v>
+        <v>385888</v>
       </c>
       <c r="R45" t="n">
-        <v>6797184</v>
+        <v>6797224</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5615,10 +5615,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125010594</v>
+        <v>125015572</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385633</v>
+        <v>385709</v>
       </c>
       <c r="R46" t="n">
-        <v>6797363</v>
+        <v>6797118</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5727,10 +5727,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125010000</v>
+        <v>125014812</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5743,21 +5743,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5767,13 +5767,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385749</v>
+        <v>385618</v>
       </c>
       <c r="R47" t="n">
-        <v>6797429</v>
+        <v>6797202</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5827,22 +5827,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125015797</v>
+        <v>125012816</v>
       </c>
       <c r="B48" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,13 +5879,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385690</v>
+        <v>385738</v>
       </c>
       <c r="R48" t="n">
-        <v>6797129</v>
+        <v>6797251</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5951,10 +5951,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125014769</v>
+        <v>125008520</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385552</v>
+        <v>385868</v>
       </c>
       <c r="R49" t="n">
-        <v>6797252</v>
+        <v>6797226</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6036,12 +6036,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Vid myr, källa?</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6068,10 +6063,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125014817</v>
+        <v>125016157</v>
       </c>
       <c r="B50" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6080,25 +6075,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6108,10 +6103,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385541</v>
+        <v>385706</v>
       </c>
       <c r="R50" t="n">
-        <v>6797264</v>
+        <v>6797113</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6143,7 +6138,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6153,12 +6148,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Vid myr, tjärn</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6185,10 +6175,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125016157</v>
+        <v>125009952</v>
       </c>
       <c r="B51" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6201,21 +6191,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6225,13 +6215,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385706</v>
+        <v>385760</v>
       </c>
       <c r="R51" t="n">
-        <v>6797113</v>
+        <v>6797317</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6260,7 +6250,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6270,7 +6260,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6297,10 +6287,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125014342</v>
+        <v>125014588</v>
       </c>
       <c r="B52" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6313,21 +6303,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6337,10 +6327,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385611</v>
+        <v>385586</v>
       </c>
       <c r="R52" t="n">
-        <v>6797222</v>
+        <v>6797244</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6372,7 +6362,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6382,7 +6372,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6409,10 +6404,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125014853</v>
+        <v>125011588</v>
       </c>
       <c r="B53" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6425,21 +6420,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6449,13 +6444,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385539</v>
+        <v>385737</v>
       </c>
       <c r="R53" t="n">
-        <v>6797252</v>
+        <v>6797241</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6484,7 +6479,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6494,7 +6489,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6521,10 +6516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125011588</v>
+        <v>125014817</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6533,25 +6528,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6561,13 +6556,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385737</v>
+        <v>385541</v>
       </c>
       <c r="R54" t="n">
-        <v>6797241</v>
+        <v>6797264</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6596,7 +6591,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6606,7 +6601,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6633,10 +6633,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125014083</v>
+        <v>125006056</v>
       </c>
       <c r="B55" t="n">
-        <v>78842</v>
+        <v>56722</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6645,38 +6645,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385689</v>
+        <v>385924</v>
       </c>
       <c r="R55" t="n">
-        <v>6797223</v>
+        <v>6797115</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6708,7 +6716,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6718,7 +6726,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6857,10 +6865,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125014685</v>
+        <v>125014604</v>
       </c>
       <c r="B57" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6873,37 +6881,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385571</v>
+        <v>385586</v>
       </c>
       <c r="R57" t="n">
-        <v>6797259</v>
+        <v>6797242</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6935,7 +6940,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6945,7 +6950,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6954,7 +6959,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6973,10 +6977,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125006056</v>
+        <v>125010793</v>
       </c>
       <c r="B58" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6985,49 +6989,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385924</v>
+        <v>385779</v>
       </c>
       <c r="R58" t="n">
-        <v>6797115</v>
+        <v>6797286</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7056,7 +7052,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7066,7 +7062,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7093,10 +7089,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125010560</v>
+        <v>125015566</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7109,21 +7105,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7133,10 +7129,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385763</v>
+        <v>385640</v>
       </c>
       <c r="R59" t="n">
-        <v>6797307</v>
+        <v>6797141</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7168,7 +7164,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7178,7 +7174,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7205,10 +7201,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125014588</v>
+        <v>125014685</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7221,34 +7217,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385586</v>
+        <v>385571</v>
       </c>
       <c r="R60" t="n">
-        <v>6797244</v>
+        <v>6797259</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7280,7 +7279,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7290,12 +7289,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7304,6 +7298,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7434,10 +7429,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125010793</v>
+        <v>125015299</v>
       </c>
       <c r="B62" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7446,25 +7441,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7474,10 +7469,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385779</v>
+        <v>385588</v>
       </c>
       <c r="R62" t="n">
-        <v>6797286</v>
+        <v>6797184</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7509,7 +7504,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7519,7 +7514,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7546,10 +7546,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125016771</v>
+        <v>125014853</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7562,21 +7562,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385674</v>
+        <v>385539</v>
       </c>
       <c r="R63" t="n">
-        <v>6796981</v>
+        <v>6797252</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7658,7 +7658,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125014604</v>
+        <v>125010560</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7698,10 +7698,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385586</v>
+        <v>385763</v>
       </c>
       <c r="R64" t="n">
-        <v>6797242</v>
+        <v>6797307</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7770,10 +7770,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125015566</v>
+        <v>125014083</v>
       </c>
       <c r="B65" t="n">
-        <v>78546</v>
+        <v>78842</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7786,21 +7786,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7810,13 +7810,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385640</v>
+        <v>385689</v>
       </c>
       <c r="R65" t="n">
-        <v>6797141</v>
+        <v>6797223</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7882,7 +7882,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125008520</v>
+        <v>125014342</v>
       </c>
       <c r="B66" t="n">
         <v>78547</v>
@@ -7922,10 +7922,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385868</v>
+        <v>385611</v>
       </c>
       <c r="R66" t="n">
-        <v>6797226</v>
+        <v>6797222</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7957,7 +7957,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7994,10 +7994,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125074279</v>
+        <v>125016771</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8006,42 +8006,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sätern, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385755</v>
+        <v>385674</v>
       </c>
       <c r="R67" t="n">
-        <v>6797321</v>
+        <v>6796981</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8071,18 +8067,27 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8094,17 +8099,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014307</v>
+        <v>125010269</v>
       </c>
       <c r="B68" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8117,21 +8122,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8141,13 +8146,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385616</v>
+        <v>385756</v>
       </c>
       <c r="R68" t="n">
-        <v>6797214</v>
+        <v>6797314</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8176,7 +8181,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8186,7 +8191,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8213,10 +8223,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125009952</v>
+        <v>125074279</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8225,41 +8235,45 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385760</v>
+        <v>385755</v>
       </c>
       <c r="R69" t="n">
-        <v>6797317</v>
+        <v>6797321</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8286,27 +8300,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:38</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8318,17 +8323,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125015299</v>
+        <v>125014307</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8341,21 +8346,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8365,10 +8370,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385588</v>
+        <v>385616</v>
       </c>
       <c r="R70" t="n">
-        <v>6797184</v>
+        <v>6797214</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8400,7 +8405,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8410,12 +8415,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8442,7 +8442,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125010269</v>
+        <v>125014769</v>
       </c>
       <c r="B71" t="n">
         <v>79891</v>
@@ -8482,13 +8482,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385756</v>
+        <v>385552</v>
       </c>
       <c r="R71" t="n">
-        <v>6797314</v>
+        <v>6797252</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125004576</v>
+        <v>125004345</v>
       </c>
       <c r="B2" t="n">
         <v>78547</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R2" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125004324</v>
+        <v>125004587</v>
       </c>
       <c r="B4" t="n">
         <v>78546</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R4" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125004345</v>
+        <v>125004576</v>
       </c>
       <c r="B6" t="n">
         <v>78547</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R6" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004587</v>
+        <v>125004324</v>
       </c>
       <c r="B7" t="n">
         <v>78546</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R7" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125008543</v>
+        <v>125010000</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385867</v>
+        <v>385749</v>
       </c>
       <c r="R9" t="n">
-        <v>6797219</v>
+        <v>6797429</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125008003</v>
+        <v>125008604</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385900</v>
+        <v>385867</v>
       </c>
       <c r="R10" t="n">
-        <v>6797194</v>
+        <v>6797219</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,12 +1671,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125009311</v>
+        <v>125015297</v>
       </c>
       <c r="B12" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385900</v>
+        <v>385569</v>
       </c>
       <c r="R12" t="n">
-        <v>6797194</v>
+        <v>6797152</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125015390</v>
+        <v>125013825</v>
       </c>
       <c r="B13" t="n">
-        <v>78547</v>
+        <v>79892</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385632</v>
+        <v>385689</v>
       </c>
       <c r="R13" t="n">
-        <v>6797173</v>
+        <v>6797243</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125007590</v>
+        <v>125013949</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385922</v>
+        <v>385633</v>
       </c>
       <c r="R14" t="n">
-        <v>6797211</v>
+        <v>6797184</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,22 +2119,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125014510</v>
+        <v>125016913</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,13 +2171,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385699</v>
+        <v>385697</v>
       </c>
       <c r="R15" t="n">
-        <v>6797223</v>
+        <v>6796929</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,22 +2231,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125015401</v>
+        <v>125010031</v>
       </c>
       <c r="B16" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385632</v>
+        <v>385750</v>
       </c>
       <c r="R16" t="n">
-        <v>6797173</v>
+        <v>6797429</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125013776</v>
+        <v>125014757</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385692</v>
+        <v>385618</v>
       </c>
       <c r="R17" t="n">
-        <v>6797239</v>
+        <v>6797202</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,22 +2455,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125015297</v>
+        <v>125015797</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385569</v>
+        <v>385690</v>
       </c>
       <c r="R18" t="n">
-        <v>6797152</v>
+        <v>6797129</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125015347</v>
+        <v>125006190</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385592</v>
+        <v>385871</v>
       </c>
       <c r="R19" t="n">
-        <v>6797161</v>
+        <v>6797143</v>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,22 +2679,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125014208</v>
+        <v>125016946</v>
       </c>
       <c r="B20" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385699</v>
+        <v>385697</v>
       </c>
       <c r="R20" t="n">
-        <v>6797223</v>
+        <v>6796899</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,12 +2791,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125016901</v>
+        <v>125009342</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385697</v>
+        <v>385861</v>
       </c>
       <c r="R22" t="n">
-        <v>6796929</v>
+        <v>6797324</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,7 +3027,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125006076</v>
+        <v>125014057</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385896</v>
+        <v>385607</v>
       </c>
       <c r="R23" t="n">
-        <v>6797101</v>
+        <v>6797159</v>
       </c>
       <c r="S23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,22 +3127,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125010542</v>
+        <v>125015273</v>
       </c>
       <c r="B24" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385634</v>
+        <v>385579</v>
       </c>
       <c r="R24" t="n">
-        <v>6797413</v>
+        <v>6797173</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3239,19 +3239,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125010000</v>
+        <v>125015347</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3291,13 +3291,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385749</v>
+        <v>385592</v>
       </c>
       <c r="R25" t="n">
-        <v>6797429</v>
+        <v>6797161</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3351,19 +3351,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125010594</v>
+        <v>125006076</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385633</v>
+        <v>385896</v>
       </c>
       <c r="R26" t="n">
-        <v>6797363</v>
+        <v>6797101</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,22 +3463,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014011</v>
+        <v>125014510</v>
       </c>
       <c r="B27" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,53 +3487,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385610</v>
+        <v>385699</v>
       </c>
       <c r="R27" t="n">
-        <v>6797160</v>
+        <v>6797223</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3562,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3572,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,19 +3575,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125010031</v>
+        <v>125012816</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3639,13 +3627,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385750</v>
+        <v>385738</v>
       </c>
       <c r="R28" t="n">
-        <v>6797429</v>
+        <v>6797251</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3674,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,22 +3687,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125013977</v>
+        <v>125009781</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3727,21 +3715,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3751,10 +3739,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385623</v>
+        <v>385862</v>
       </c>
       <c r="R29" t="n">
-        <v>6797166</v>
+        <v>6797329</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3786,7 +3774,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,7 +3784,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3823,10 +3811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125008665</v>
+        <v>125009311</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3839,21 +3827,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3869,7 +3857,7 @@
         <v>6797194</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3898,7 +3886,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3896,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,7 +3923,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125013949</v>
+        <v>125008665</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3975,13 +3963,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385633</v>
+        <v>385900</v>
       </c>
       <c r="R31" t="n">
-        <v>6797184</v>
+        <v>6797194</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,7 +3998,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4020,7 +4008,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,22 +4023,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125015273</v>
+        <v>125013776</v>
       </c>
       <c r="B32" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4063,21 +4051,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4087,13 +4075,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385579</v>
+        <v>385692</v>
       </c>
       <c r="R32" t="n">
-        <v>6797173</v>
+        <v>6797239</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4122,7 +4110,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4132,7 +4120,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,19 +4135,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125014035</v>
+        <v>125015275</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -4199,10 +4187,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385607</v>
+        <v>385609</v>
       </c>
       <c r="R33" t="n">
-        <v>6797159</v>
+        <v>6797178</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4234,7 +4222,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4244,7 +4232,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4271,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125016946</v>
+        <v>125014208</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4287,21 +4275,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4311,13 +4299,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385697</v>
+        <v>385699</v>
       </c>
       <c r="R34" t="n">
-        <v>6796899</v>
+        <v>6797223</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4346,7 +4334,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4356,7 +4344,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,12 +4359,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4495,10 +4483,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125015797</v>
+        <v>125015401</v>
       </c>
       <c r="B36" t="n">
-        <v>79892</v>
+        <v>78546</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,21 +4499,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,13 +4523,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385690</v>
+        <v>385632</v>
       </c>
       <c r="R36" t="n">
-        <v>6797129</v>
+        <v>6797173</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4580,7 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4595,22 +4583,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125009342</v>
+        <v>125008432</v>
       </c>
       <c r="B37" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4623,21 +4611,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4647,10 +4635,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385861</v>
+        <v>385888</v>
       </c>
       <c r="R37" t="n">
-        <v>6797324</v>
+        <v>6797224</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4682,7 +4670,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4692,7 +4680,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4719,10 +4707,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125013825</v>
+        <v>125008003</v>
       </c>
       <c r="B38" t="n">
-        <v>79892</v>
+        <v>79399</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4735,21 +4723,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,13 +4747,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385689</v>
+        <v>385900</v>
       </c>
       <c r="R38" t="n">
-        <v>6797243</v>
+        <v>6797194</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4794,7 +4782,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4804,7 +4792,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,22 +4807,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125009781</v>
+        <v>125015572</v>
       </c>
       <c r="B39" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4847,21 +4835,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4871,10 +4859,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385862</v>
+        <v>385709</v>
       </c>
       <c r="R39" t="n">
-        <v>6797329</v>
+        <v>6797118</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4906,7 +4894,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4916,7 +4904,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4943,7 +4931,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125006190</v>
+        <v>125010604</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4983,10 +4971,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385871</v>
+        <v>385633</v>
       </c>
       <c r="R40" t="n">
-        <v>6797143</v>
+        <v>6797363</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5018,7 +5006,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +5016,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5055,10 +5043,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125014099</v>
+        <v>125015390</v>
       </c>
       <c r="B41" t="n">
-        <v>78842</v>
+        <v>78547</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5071,21 +5059,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5095,13 +5083,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385699</v>
+        <v>385632</v>
       </c>
       <c r="R41" t="n">
-        <v>6797223</v>
+        <v>6797173</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5130,7 +5118,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5140,7 +5128,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,22 +5143,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125014757</v>
+        <v>125014011</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5179,41 +5167,53 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385618</v>
+        <v>385610</v>
       </c>
       <c r="R42" t="n">
-        <v>6797202</v>
+        <v>6797160</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5267,22 +5267,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125015275</v>
+        <v>125014812</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5295,21 +5295,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5319,13 +5319,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385609</v>
+        <v>385618</v>
       </c>
       <c r="R43" t="n">
-        <v>6797178</v>
+        <v>6797202</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5379,22 +5379,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125009430</v>
+        <v>125007590</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385862</v>
+        <v>385922</v>
       </c>
       <c r="R44" t="n">
-        <v>6797329</v>
+        <v>6797211</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5491,22 +5491,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125008432</v>
+        <v>125010542</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5519,21 +5519,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5543,10 +5543,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385888</v>
+        <v>385634</v>
       </c>
       <c r="R45" t="n">
-        <v>6797224</v>
+        <v>6797413</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5615,10 +5615,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125015572</v>
+        <v>125014099</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>78842</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385709</v>
+        <v>385699</v>
       </c>
       <c r="R46" t="n">
-        <v>6797118</v>
+        <v>6797223</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5715,22 +5715,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125014812</v>
+        <v>125013977</v>
       </c>
       <c r="B47" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5743,21 +5743,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5767,13 +5767,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385618</v>
+        <v>385623</v>
       </c>
       <c r="R47" t="n">
-        <v>6797202</v>
+        <v>6797166</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5827,19 +5827,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125012816</v>
+        <v>125009430</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5879,13 +5879,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385738</v>
+        <v>385862</v>
       </c>
       <c r="R48" t="n">
-        <v>6797251</v>
+        <v>6797329</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5939,22 +5939,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125008520</v>
+        <v>125014588</v>
       </c>
       <c r="B49" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385868</v>
+        <v>385586</v>
       </c>
       <c r="R49" t="n">
-        <v>6797226</v>
+        <v>6797244</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6036,7 +6036,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6063,10 +6068,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125016157</v>
+        <v>125074279</v>
       </c>
       <c r="B50" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6075,38 +6080,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385706</v>
+        <v>385755</v>
       </c>
       <c r="R50" t="n">
-        <v>6797113</v>
+        <v>6797321</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6136,27 +6145,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6168,14 +6168,14 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125009952</v>
+        <v>125016771</v>
       </c>
       <c r="B51" t="n">
         <v>78810</v>
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385760</v>
+        <v>385674</v>
       </c>
       <c r="R51" t="n">
-        <v>6797317</v>
+        <v>6796981</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6287,7 +6287,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125014588</v>
+        <v>125011588</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -6327,13 +6327,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385586</v>
+        <v>385737</v>
       </c>
       <c r="R52" t="n">
-        <v>6797244</v>
+        <v>6797241</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6372,12 +6372,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6404,10 +6399,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125011588</v>
+        <v>125014685</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6420,37 +6415,40 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385737</v>
+        <v>385571</v>
       </c>
       <c r="R53" t="n">
-        <v>6797241</v>
+        <v>6797259</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6479,7 +6477,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6489,7 +6487,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6498,6 +6496,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6516,10 +6515,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125014817</v>
+        <v>125014083</v>
       </c>
       <c r="B54" t="n">
-        <v>79919</v>
+        <v>78842</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6528,25 +6527,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6461</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6556,13 +6555,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385541</v>
+        <v>385689</v>
       </c>
       <c r="R54" t="n">
-        <v>6797264</v>
+        <v>6797223</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6591,7 +6590,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6601,12 +6600,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Vid myr, tjärn</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6633,10 +6627,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125006056</v>
+        <v>125014817</v>
       </c>
       <c r="B55" t="n">
-        <v>56722</v>
+        <v>79919</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6649,45 +6643,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385924</v>
+        <v>385541</v>
       </c>
       <c r="R55" t="n">
-        <v>6797115</v>
+        <v>6797264</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6716,7 +6702,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6726,7 +6712,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6753,10 +6744,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125008506</v>
+        <v>125014700</v>
       </c>
       <c r="B56" t="n">
-        <v>78546</v>
+        <v>79919</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6765,25 +6756,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6461</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6793,10 +6784,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385867</v>
+        <v>385567</v>
       </c>
       <c r="R56" t="n">
-        <v>6797218</v>
+        <v>6797275</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6828,7 +6819,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6838,7 +6829,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6865,10 +6856,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125014604</v>
+        <v>125015566</v>
       </c>
       <c r="B57" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6881,21 +6872,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6905,10 +6896,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385586</v>
+        <v>385640</v>
       </c>
       <c r="R57" t="n">
-        <v>6797242</v>
+        <v>6797141</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6940,7 +6931,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6950,7 +6941,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6977,10 +6968,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125010793</v>
+        <v>125014604</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6989,25 +6980,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7017,10 +7008,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385779</v>
+        <v>385586</v>
       </c>
       <c r="R58" t="n">
-        <v>6797286</v>
+        <v>6797242</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7052,7 +7043,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7062,7 +7053,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7089,10 +7080,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125015566</v>
+        <v>125016157</v>
       </c>
       <c r="B59" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7105,21 +7096,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7129,10 +7120,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385640</v>
+        <v>385706</v>
       </c>
       <c r="R59" t="n">
-        <v>6797141</v>
+        <v>6797113</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7164,7 +7155,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7174,7 +7165,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7201,10 +7192,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125014685</v>
+        <v>125008520</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7217,37 +7208,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385571</v>
+        <v>385868</v>
       </c>
       <c r="R60" t="n">
-        <v>6797259</v>
+        <v>6797226</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7279,7 +7267,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7289,7 +7277,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7298,7 +7286,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7317,10 +7304,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125014700</v>
+        <v>125010560</v>
       </c>
       <c r="B61" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7329,25 +7316,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7357,10 +7344,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385567</v>
+        <v>385763</v>
       </c>
       <c r="R61" t="n">
-        <v>6797275</v>
+        <v>6797307</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7392,7 +7379,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7402,7 +7389,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7429,10 +7416,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125015299</v>
+        <v>125010269</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7445,21 +7432,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7469,13 +7456,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385588</v>
+        <v>385756</v>
       </c>
       <c r="R62" t="n">
-        <v>6797184</v>
+        <v>6797314</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7504,7 +7491,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7514,12 +7501,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7546,10 +7533,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125014853</v>
+        <v>125015299</v>
       </c>
       <c r="B63" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7562,21 +7549,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7586,10 +7573,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385539</v>
+        <v>385588</v>
       </c>
       <c r="R63" t="n">
-        <v>6797252</v>
+        <v>6797184</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7621,7 +7608,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7631,7 +7618,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7658,7 +7650,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125010560</v>
+        <v>125009952</v>
       </c>
       <c r="B64" t="n">
         <v>78810</v>
@@ -7698,13 +7690,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385763</v>
+        <v>385760</v>
       </c>
       <c r="R64" t="n">
-        <v>6797307</v>
+        <v>6797317</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7733,7 +7725,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7743,7 +7735,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7770,10 +7762,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125014083</v>
+        <v>125010793</v>
       </c>
       <c r="B65" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7782,25 +7774,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7810,13 +7802,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385689</v>
+        <v>385779</v>
       </c>
       <c r="R65" t="n">
-        <v>6797223</v>
+        <v>6797286</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7845,7 +7837,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7855,7 +7847,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7994,10 +7986,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125016771</v>
+        <v>125008506</v>
       </c>
       <c r="B67" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8010,21 +8002,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8034,10 +8026,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385674</v>
+        <v>385867</v>
       </c>
       <c r="R67" t="n">
-        <v>6796981</v>
+        <v>6797218</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8069,7 +8061,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8079,7 +8071,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8106,7 +8098,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125010269</v>
+        <v>125014853</v>
       </c>
       <c r="B68" t="n">
         <v>79891</v>
@@ -8146,13 +8138,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385756</v>
+        <v>385539</v>
       </c>
       <c r="R68" t="n">
-        <v>6797314</v>
+        <v>6797252</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8181,7 +8173,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8191,12 +8183,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8223,10 +8210,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125074279</v>
+        <v>125006056</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8235,45 +8222,49 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sätern, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385755</v>
+        <v>385924</v>
       </c>
       <c r="R69" t="n">
-        <v>6797321</v>
+        <v>6797115</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8300,18 +8291,27 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8323,17 +8323,17 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Lisa Olson, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125014307</v>
+        <v>125014769</v>
       </c>
       <c r="B70" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8346,21 +8346,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385616</v>
+        <v>385552</v>
       </c>
       <c r="R70" t="n">
-        <v>6797214</v>
+        <v>6797252</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8415,7 +8415,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8442,10 +8447,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125014769</v>
+        <v>125014307</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8458,21 +8463,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8482,10 +8487,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385552</v>
+        <v>385616</v>
       </c>
       <c r="R71" t="n">
-        <v>6797252</v>
+        <v>6797214</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8517,7 +8522,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8527,12 +8532,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Vid myr, källa?</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125006190</v>
+        <v>125009342</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385871</v>
+        <v>385861</v>
       </c>
       <c r="R19" t="n">
-        <v>6797143</v>
+        <v>6797324</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125016946</v>
+        <v>125006190</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385697</v>
+        <v>385871</v>
       </c>
       <c r="R20" t="n">
-        <v>6796899</v>
+        <v>6797143</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125010553</v>
+        <v>125016946</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385876</v>
+        <v>385697</v>
       </c>
       <c r="R21" t="n">
-        <v>6797310</v>
+        <v>6796899</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,22 +2903,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125009342</v>
+        <v>125010553</v>
       </c>
       <c r="B22" t="n">
-        <v>79892</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385861</v>
+        <v>385876</v>
       </c>
       <c r="R22" t="n">
-        <v>6797324</v>
+        <v>6797310</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,12 +3015,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125010542</v>
+        <v>125014099</v>
       </c>
       <c r="B45" t="n">
-        <v>78546</v>
+        <v>78842</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5519,21 +5519,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5543,13 +5543,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385634</v>
+        <v>385699</v>
       </c>
       <c r="R45" t="n">
-        <v>6797413</v>
+        <v>6797223</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5603,22 +5603,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125014099</v>
+        <v>125010542</v>
       </c>
       <c r="B46" t="n">
-        <v>78842</v>
+        <v>78546</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385699</v>
+        <v>385634</v>
       </c>
       <c r="R46" t="n">
-        <v>6797223</v>
+        <v>6797413</v>
       </c>
       <c r="S46" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5715,12 +5715,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -7080,10 +7080,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125016157</v>
+        <v>125008520</v>
       </c>
       <c r="B59" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7096,21 +7096,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385706</v>
+        <v>385868</v>
       </c>
       <c r="R59" t="n">
-        <v>6797113</v>
+        <v>6797226</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7192,10 +7192,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125008520</v>
+        <v>125016157</v>
       </c>
       <c r="B60" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7208,21 +7208,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7232,10 +7232,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385868</v>
+        <v>385706</v>
       </c>
       <c r="R60" t="n">
-        <v>6797226</v>
+        <v>6797113</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125004345</v>
+        <v>125004665</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R2" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125004366</v>
+        <v>125004324</v>
       </c>
       <c r="B3" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125004587</v>
+        <v>125004366</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R4" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125004665</v>
+        <v>125004345</v>
       </c>
       <c r="B5" t="n">
-        <v>79428</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R5" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004324</v>
+        <v>125004587</v>
       </c>
       <c r="B7" t="n">
         <v>78546</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R7" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125010000</v>
+        <v>125010542</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385749</v>
+        <v>385634</v>
       </c>
       <c r="R9" t="n">
-        <v>6797429</v>
+        <v>6797413</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125008604</v>
+        <v>125015401</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385867</v>
+        <v>385632</v>
       </c>
       <c r="R10" t="n">
-        <v>6797219</v>
+        <v>6797173</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125011580</v>
+        <v>125013949</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385738</v>
+        <v>385633</v>
       </c>
       <c r="R11" t="n">
-        <v>6797251</v>
+        <v>6797184</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,22 +1783,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125015297</v>
+        <v>125008003</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385569</v>
+        <v>385900</v>
       </c>
       <c r="R12" t="n">
-        <v>6797152</v>
+        <v>6797194</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125013825</v>
+        <v>125014757</v>
       </c>
       <c r="B13" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385689</v>
+        <v>385618</v>
       </c>
       <c r="R13" t="n">
-        <v>6797243</v>
+        <v>6797202</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,22 +2007,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125013949</v>
+        <v>125015390</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385633</v>
+        <v>385632</v>
       </c>
       <c r="R14" t="n">
-        <v>6797184</v>
+        <v>6797173</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125016913</v>
+        <v>125008543</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385697</v>
+        <v>385867</v>
       </c>
       <c r="R15" t="n">
-        <v>6796929</v>
+        <v>6797219</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,7 +2243,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125010031</v>
+        <v>125006076</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385750</v>
+        <v>385896</v>
       </c>
       <c r="R16" t="n">
-        <v>6797429</v>
+        <v>6797101</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,19 +2343,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125014757</v>
+        <v>125015347</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385618</v>
+        <v>385592</v>
       </c>
       <c r="R17" t="n">
-        <v>6797202</v>
+        <v>6797161</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125015797</v>
+        <v>125010553</v>
       </c>
       <c r="B18" t="n">
-        <v>79892</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385690</v>
+        <v>385876</v>
       </c>
       <c r="R18" t="n">
-        <v>6797129</v>
+        <v>6797310</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125009342</v>
+        <v>125015275</v>
       </c>
       <c r="B19" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385861</v>
+        <v>385609</v>
       </c>
       <c r="R19" t="n">
-        <v>6797324</v>
+        <v>6797178</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125006190</v>
+        <v>125008432</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385871</v>
+        <v>385888</v>
       </c>
       <c r="R20" t="n">
-        <v>6797143</v>
+        <v>6797224</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,7 +2803,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125016946</v>
+        <v>125016901</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2846,7 +2846,7 @@
         <v>385697</v>
       </c>
       <c r="R21" t="n">
-        <v>6796899</v>
+        <v>6796929</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125010553</v>
+        <v>125011580</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385876</v>
+        <v>385738</v>
       </c>
       <c r="R22" t="n">
-        <v>6797310</v>
+        <v>6797251</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125014057</v>
+        <v>125014812</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385607</v>
+        <v>385618</v>
       </c>
       <c r="R23" t="n">
-        <v>6797159</v>
+        <v>6797202</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,22 +3127,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125015273</v>
+        <v>125015797</v>
       </c>
       <c r="B24" t="n">
-        <v>78547</v>
+        <v>79892</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385579</v>
+        <v>385690</v>
       </c>
       <c r="R24" t="n">
-        <v>6797173</v>
+        <v>6797129</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125015347</v>
+        <v>125013776</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,13 +3291,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385592</v>
+        <v>385692</v>
       </c>
       <c r="R25" t="n">
-        <v>6797161</v>
+        <v>6797239</v>
       </c>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3351,22 +3351,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125006076</v>
+        <v>125015572</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385896</v>
+        <v>385709</v>
       </c>
       <c r="R26" t="n">
-        <v>6797101</v>
+        <v>6797118</v>
       </c>
       <c r="S26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,22 +3463,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125014510</v>
+        <v>125010604</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385699</v>
+        <v>385633</v>
       </c>
       <c r="R27" t="n">
-        <v>6797223</v>
+        <v>6797363</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3575,19 +3575,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125012816</v>
+        <v>125009430</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3627,13 +3627,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385738</v>
+        <v>385862</v>
       </c>
       <c r="R28" t="n">
-        <v>6797251</v>
+        <v>6797329</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3687,12 +3687,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125009311</v>
+        <v>125013977</v>
       </c>
       <c r="B30" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3827,21 +3827,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3851,13 +3851,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385900</v>
+        <v>385623</v>
       </c>
       <c r="R30" t="n">
-        <v>6797194</v>
+        <v>6797166</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3911,19 +3911,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125008665</v>
+        <v>125012816</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385900</v>
+        <v>385738</v>
       </c>
       <c r="R31" t="n">
-        <v>6797194</v>
+        <v>6797251</v>
       </c>
       <c r="S31" t="n">
         <v>8</v>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,10 +4035,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125013776</v>
+        <v>125010000</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4051,21 +4051,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385692</v>
+        <v>385749</v>
       </c>
       <c r="R32" t="n">
-        <v>6797239</v>
+        <v>6797429</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,10 +4147,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125015275</v>
+        <v>125014099</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4163,21 +4163,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4187,13 +4187,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385609</v>
+        <v>385699</v>
       </c>
       <c r="R33" t="n">
-        <v>6797178</v>
+        <v>6797223</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4247,22 +4247,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125014208</v>
+        <v>125009311</v>
       </c>
       <c r="B34" t="n">
-        <v>79399</v>
+        <v>78546</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4275,21 +4275,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4299,13 +4299,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385699</v>
+        <v>385900</v>
       </c>
       <c r="R34" t="n">
-        <v>6797223</v>
+        <v>6797194</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,10 +4371,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125009359</v>
+        <v>125009342</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385862</v>
+        <v>385861</v>
       </c>
       <c r="R35" t="n">
-        <v>6797329</v>
+        <v>6797324</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4483,10 +4483,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125015401</v>
+        <v>125013825</v>
       </c>
       <c r="B36" t="n">
-        <v>78546</v>
+        <v>79892</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4499,21 +4499,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385632</v>
+        <v>385689</v>
       </c>
       <c r="R36" t="n">
-        <v>6797173</v>
+        <v>6797243</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4595,7 +4595,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125008432</v>
+        <v>125015297</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385888</v>
+        <v>385569</v>
       </c>
       <c r="R37" t="n">
-        <v>6797224</v>
+        <v>6797152</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4695,22 +4695,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125008003</v>
+        <v>125014035</v>
       </c>
       <c r="B38" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4747,13 +4747,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385900</v>
+        <v>385607</v>
       </c>
       <c r="R38" t="n">
-        <v>6797194</v>
+        <v>6797159</v>
       </c>
       <c r="S38" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4807,22 +4807,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125015572</v>
+        <v>125010031</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4835,21 +4835,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385709</v>
+        <v>385750</v>
       </c>
       <c r="R39" t="n">
-        <v>6797118</v>
+        <v>6797429</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4931,10 +4931,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125010604</v>
+        <v>125014011</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4943,38 +4943,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385633</v>
+        <v>385610</v>
       </c>
       <c r="R40" t="n">
-        <v>6797363</v>
+        <v>6797160</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -5006,7 +5018,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5016,7 +5028,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,7 +5055,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125015390</v>
+        <v>125007590</v>
       </c>
       <c r="B41" t="n">
         <v>78547</v>
@@ -5083,13 +5095,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385632</v>
+        <v>385922</v>
       </c>
       <c r="R41" t="n">
-        <v>6797173</v>
+        <v>6797211</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5118,7 +5130,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5128,7 +5140,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5143,22 +5155,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125014011</v>
+        <v>125015273</v>
       </c>
       <c r="B42" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5167,53 +5179,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385610</v>
+        <v>385579</v>
       </c>
       <c r="R42" t="n">
-        <v>6797160</v>
+        <v>6797173</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5267,19 +5267,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125014812</v>
+        <v>125014510</v>
       </c>
       <c r="B43" t="n">
         <v>78547</v>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385618</v>
+        <v>385699</v>
       </c>
       <c r="R43" t="n">
-        <v>6797202</v>
+        <v>6797223</v>
       </c>
       <c r="S43" t="n">
         <v>9</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5391,10 +5391,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125007590</v>
+        <v>125008665</v>
       </c>
       <c r="B44" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385922</v>
+        <v>385900</v>
       </c>
       <c r="R44" t="n">
-        <v>6797211</v>
+        <v>6797194</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5503,10 +5503,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125014099</v>
+        <v>125009359</v>
       </c>
       <c r="B45" t="n">
-        <v>78842</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5519,21 +5519,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5543,13 +5543,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385699</v>
+        <v>385862</v>
       </c>
       <c r="R45" t="n">
-        <v>6797223</v>
+        <v>6797329</v>
       </c>
       <c r="S45" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5603,22 +5603,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125010542</v>
+        <v>125006190</v>
       </c>
       <c r="B46" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5655,10 +5655,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385634</v>
+        <v>385871</v>
       </c>
       <c r="R46" t="n">
-        <v>6797413</v>
+        <v>6797143</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5727,7 +5727,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125013977</v>
+        <v>125016946</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385623</v>
+        <v>385697</v>
       </c>
       <c r="R47" t="n">
-        <v>6797166</v>
+        <v>6796899</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125009430</v>
+        <v>125014208</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,13 +5879,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385862</v>
+        <v>385699</v>
       </c>
       <c r="R48" t="n">
-        <v>6797329</v>
+        <v>6797223</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5939,12 +5939,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6068,10 +6068,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125074279</v>
+        <v>125006056</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6080,45 +6080,49 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sätern, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385755</v>
+        <v>385924</v>
       </c>
       <c r="R50" t="n">
-        <v>6797321</v>
+        <v>6797115</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6145,18 +6149,27 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6168,17 +6181,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson, Anna-Britt Olsson, Göran Ehn, Cecilia Rastad</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125016771</v>
+        <v>125014342</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6191,21 +6204,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6215,10 +6228,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385674</v>
+        <v>385611</v>
       </c>
       <c r="R51" t="n">
-        <v>6796981</v>
+        <v>6797222</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6250,7 +6263,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6260,7 +6273,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6287,10 +6300,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125011588</v>
+        <v>125010269</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6303,21 +6316,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6327,10 +6340,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385737</v>
+        <v>385756</v>
       </c>
       <c r="R52" t="n">
-        <v>6797241</v>
+        <v>6797314</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6362,7 +6375,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6372,7 +6385,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6392,7 +6410,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6515,10 +6533,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125014083</v>
+        <v>125009952</v>
       </c>
       <c r="B54" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6531,21 +6549,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6555,10 +6573,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385689</v>
+        <v>385760</v>
       </c>
       <c r="R54" t="n">
-        <v>6797223</v>
+        <v>6797317</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6590,7 +6608,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6600,7 +6618,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6620,17 +6638,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125014817</v>
+        <v>125016771</v>
       </c>
       <c r="B55" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6639,25 +6657,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6667,10 +6685,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385541</v>
+        <v>385674</v>
       </c>
       <c r="R55" t="n">
-        <v>6797264</v>
+        <v>6796981</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6702,7 +6720,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6712,12 +6730,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Vid myr, tjärn</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6744,10 +6757,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125014700</v>
+        <v>125010560</v>
       </c>
       <c r="B56" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6756,25 +6769,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6784,10 +6797,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385567</v>
+        <v>385763</v>
       </c>
       <c r="R56" t="n">
-        <v>6797275</v>
+        <v>6797307</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6819,7 +6832,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6829,7 +6842,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6856,7 +6869,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125015566</v>
+        <v>125014307</v>
       </c>
       <c r="B57" t="n">
         <v>78546</v>
@@ -6896,10 +6909,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385640</v>
+        <v>385616</v>
       </c>
       <c r="R57" t="n">
-        <v>6797141</v>
+        <v>6797214</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6931,7 +6944,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6941,7 +6954,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6968,10 +6981,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125014604</v>
+        <v>125008506</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6984,21 +6997,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7008,10 +7021,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385586</v>
+        <v>385867</v>
       </c>
       <c r="R58" t="n">
-        <v>6797242</v>
+        <v>6797218</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7043,7 +7056,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7053,7 +7066,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7080,10 +7093,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125008520</v>
+        <v>125014769</v>
       </c>
       <c r="B59" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7096,21 +7109,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7120,10 +7133,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385868</v>
+        <v>385552</v>
       </c>
       <c r="R59" t="n">
-        <v>6797226</v>
+        <v>6797252</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7155,7 +7168,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7165,7 +7178,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7192,10 +7210,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125016157</v>
+        <v>125008520</v>
       </c>
       <c r="B60" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7208,21 +7226,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7232,10 +7250,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385706</v>
+        <v>385868</v>
       </c>
       <c r="R60" t="n">
-        <v>6797113</v>
+        <v>6797226</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7267,7 +7285,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7277,7 +7295,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7304,10 +7322,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125010560</v>
+        <v>125014817</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7316,25 +7334,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7344,10 +7362,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385763</v>
+        <v>385541</v>
       </c>
       <c r="R61" t="n">
-        <v>6797307</v>
+        <v>6797264</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7379,7 +7397,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7389,7 +7407,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7416,10 +7439,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125010269</v>
+        <v>125014700</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>79919</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7428,25 +7451,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7456,13 +7479,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385756</v>
+        <v>385567</v>
       </c>
       <c r="R62" t="n">
-        <v>6797314</v>
+        <v>6797275</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7491,7 +7514,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7501,12 +7524,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7650,10 +7668,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125009952</v>
+        <v>125014853</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7666,21 +7684,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7690,13 +7708,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385760</v>
+        <v>385539</v>
       </c>
       <c r="R64" t="n">
-        <v>6797317</v>
+        <v>6797252</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7725,7 +7743,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7735,7 +7753,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7762,10 +7780,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125010793</v>
+        <v>125014604</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7774,25 +7792,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7802,10 +7820,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385779</v>
+        <v>385586</v>
       </c>
       <c r="R65" t="n">
-        <v>6797286</v>
+        <v>6797242</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7837,7 +7855,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7847,7 +7865,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7874,10 +7892,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125014342</v>
+        <v>125015566</v>
       </c>
       <c r="B66" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7890,21 +7908,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7914,10 +7932,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385611</v>
+        <v>385640</v>
       </c>
       <c r="R66" t="n">
-        <v>6797222</v>
+        <v>6797141</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7949,7 +7967,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7959,7 +7977,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7986,10 +8004,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125008506</v>
+        <v>125010793</v>
       </c>
       <c r="B67" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7998,25 +8016,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8026,10 +8044,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385867</v>
+        <v>385779</v>
       </c>
       <c r="R67" t="n">
-        <v>6797218</v>
+        <v>6797286</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -8061,7 +8079,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8071,7 +8089,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8098,10 +8116,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125014853</v>
+        <v>125074279</v>
       </c>
       <c r="B68" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8110,38 +8128,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385539</v>
+        <v>385755</v>
       </c>
       <c r="R68" t="n">
-        <v>6797252</v>
+        <v>6797321</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8171,27 +8193,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8203,17 +8216,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125006056</v>
+        <v>125011588</v>
       </c>
       <c r="B69" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8222,46 +8235,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385924</v>
+        <v>385737</v>
       </c>
       <c r="R69" t="n">
-        <v>6797115</v>
+        <v>6797241</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8293,7 +8298,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8303,7 +8308,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8330,10 +8335,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125014769</v>
+        <v>125014083</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>78842</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8346,21 +8351,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8370,13 +8375,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385552</v>
+        <v>385689</v>
       </c>
       <c r="R70" t="n">
-        <v>6797252</v>
+        <v>6797223</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8405,7 +8410,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8415,12 +8420,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Vid myr, källa?</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8440,17 +8440,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125014307</v>
+        <v>125016157</v>
       </c>
       <c r="B71" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8463,21 +8463,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385616</v>
+        <v>385706</v>
       </c>
       <c r="R71" t="n">
-        <v>6797214</v>
+        <v>6797113</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125015401</v>
+        <v>125008003</v>
       </c>
       <c r="B10" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385632</v>
+        <v>385900</v>
       </c>
       <c r="R10" t="n">
-        <v>6797173</v>
+        <v>6797194</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,22 +1671,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125013949</v>
+        <v>125015401</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385633</v>
+        <v>385632</v>
       </c>
       <c r="R11" t="n">
-        <v>6797184</v>
+        <v>6797173</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125008003</v>
+        <v>125013949</v>
       </c>
       <c r="B12" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385900</v>
+        <v>385633</v>
       </c>
       <c r="R12" t="n">
-        <v>6797194</v>
+        <v>6797184</v>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,12 +1895,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125015797</v>
+        <v>125013776</v>
       </c>
       <c r="B24" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385690</v>
+        <v>385692</v>
       </c>
       <c r="R24" t="n">
-        <v>6797129</v>
+        <v>6797239</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3239,19 +3239,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125013776</v>
+        <v>125015572</v>
       </c>
       <c r="B25" t="n">
         <v>79891</v>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385692</v>
+        <v>385709</v>
       </c>
       <c r="R25" t="n">
-        <v>6797239</v>
+        <v>6797118</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125015572</v>
+        <v>125015797</v>
       </c>
       <c r="B26" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385709</v>
+        <v>385690</v>
       </c>
       <c r="R26" t="n">
-        <v>6797118</v>
+        <v>6797129</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,12 +3463,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -6869,10 +6869,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125014307</v>
+        <v>125014769</v>
       </c>
       <c r="B57" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6885,21 +6885,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6909,10 +6909,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385616</v>
+        <v>385552</v>
       </c>
       <c r="R57" t="n">
-        <v>6797214</v>
+        <v>6797252</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6954,7 +6954,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6981,7 +6986,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125008506</v>
+        <v>125014307</v>
       </c>
       <c r="B58" t="n">
         <v>78546</v>
@@ -7021,10 +7026,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385867</v>
+        <v>385616</v>
       </c>
       <c r="R58" t="n">
-        <v>6797218</v>
+        <v>6797214</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7056,7 +7061,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7066,7 +7071,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7093,10 +7098,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125014769</v>
+        <v>125008506</v>
       </c>
       <c r="B59" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7109,21 +7114,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7133,10 +7138,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385552</v>
+        <v>385867</v>
       </c>
       <c r="R59" t="n">
-        <v>6797252</v>
+        <v>6797218</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7168,7 +7173,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7178,12 +7183,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Vid myr, källa?</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7892,10 +7892,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125015566</v>
+        <v>125074279</v>
       </c>
       <c r="B66" t="n">
-        <v>78546</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7904,38 +7904,42 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385640</v>
+        <v>385755</v>
       </c>
       <c r="R66" t="n">
-        <v>6797141</v>
+        <v>6797321</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7965,27 +7969,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7997,7 +7992,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8116,10 +8111,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125074279</v>
+        <v>125015566</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8128,42 +8123,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sätern, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385755</v>
+        <v>385640</v>
       </c>
       <c r="R68" t="n">
-        <v>6797321</v>
+        <v>6797141</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8193,18 +8184,27 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125004665</v>
+        <v>125004587</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125004324</v>
+        <v>125004345</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125004345</v>
+        <v>125004665</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>79428</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R5" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004587</v>
+        <v>125004324</v>
       </c>
       <c r="B7" t="n">
         <v>78546</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R7" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125010542</v>
+        <v>125008604</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385634</v>
+        <v>385867</v>
       </c>
       <c r="R9" t="n">
-        <v>6797413</v>
+        <v>6797219</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125008003</v>
+        <v>125010031</v>
       </c>
       <c r="B10" t="n">
-        <v>79399</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385900</v>
+        <v>385750</v>
       </c>
       <c r="R10" t="n">
-        <v>6797194</v>
+        <v>6797429</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,22 +1671,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125015401</v>
+        <v>125009359</v>
       </c>
       <c r="B11" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385632</v>
+        <v>385862</v>
       </c>
       <c r="R11" t="n">
-        <v>6797173</v>
+        <v>6797329</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125013949</v>
+        <v>125015273</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385633</v>
+        <v>385579</v>
       </c>
       <c r="R12" t="n">
-        <v>6797184</v>
+        <v>6797173</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,22 +1895,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125014757</v>
+        <v>125013825</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385618</v>
+        <v>385689</v>
       </c>
       <c r="R13" t="n">
-        <v>6797202</v>
+        <v>6797243</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,22 +2007,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125015390</v>
+        <v>125015572</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385632</v>
+        <v>385709</v>
       </c>
       <c r="R14" t="n">
-        <v>6797173</v>
+        <v>6797118</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125008543</v>
+        <v>125016901</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385867</v>
+        <v>385697</v>
       </c>
       <c r="R15" t="n">
-        <v>6797219</v>
+        <v>6796929</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,7 +2243,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125006076</v>
+        <v>125015275</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2283,13 +2283,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385896</v>
+        <v>385609</v>
       </c>
       <c r="R16" t="n">
-        <v>6797101</v>
+        <v>6797178</v>
       </c>
       <c r="S16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,19 +2343,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125015347</v>
+        <v>125013949</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385592</v>
+        <v>385633</v>
       </c>
       <c r="R17" t="n">
-        <v>6797161</v>
+        <v>6797184</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,22 +2455,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125010553</v>
+        <v>125008432</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385876</v>
+        <v>385888</v>
       </c>
       <c r="R18" t="n">
-        <v>6797310</v>
+        <v>6797224</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,19 +2567,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125015275</v>
+        <v>125006190</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385609</v>
+        <v>385871</v>
       </c>
       <c r="R19" t="n">
-        <v>6797178</v>
+        <v>6797143</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125008432</v>
+        <v>125009430</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385888</v>
+        <v>385862</v>
       </c>
       <c r="R20" t="n">
-        <v>6797224</v>
+        <v>6797329</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125016901</v>
+        <v>125011580</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385697</v>
+        <v>385738</v>
       </c>
       <c r="R21" t="n">
-        <v>6796929</v>
+        <v>6797251</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,22 +2903,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125011580</v>
+        <v>125015347</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,13 +2955,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385738</v>
+        <v>385592</v>
       </c>
       <c r="R22" t="n">
-        <v>6797251</v>
+        <v>6797161</v>
       </c>
       <c r="S22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125014812</v>
+        <v>125012816</v>
       </c>
       <c r="B23" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3043,21 +3043,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385618</v>
+        <v>385738</v>
       </c>
       <c r="R23" t="n">
-        <v>6797202</v>
+        <v>6797251</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125013776</v>
+        <v>125010553</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385692</v>
+        <v>385876</v>
       </c>
       <c r="R24" t="n">
-        <v>6797239</v>
+        <v>6797310</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3239,22 +3239,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125015572</v>
+        <v>125014035</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385709</v>
+        <v>385607</v>
       </c>
       <c r="R25" t="n">
-        <v>6797118</v>
+        <v>6797159</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125010604</v>
+        <v>125009342</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385633</v>
+        <v>385861</v>
       </c>
       <c r="R27" t="n">
-        <v>6797363</v>
+        <v>6797324</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125009430</v>
+        <v>125009781</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,10 +3699,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125009781</v>
+        <v>125013776</v>
       </c>
       <c r="B29" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3739,10 +3739,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385862</v>
+        <v>385692</v>
       </c>
       <c r="R29" t="n">
-        <v>6797329</v>
+        <v>6797239</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,7 +3811,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125013977</v>
+        <v>125010000</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3851,10 +3851,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385623</v>
+        <v>385749</v>
       </c>
       <c r="R30" t="n">
-        <v>6797166</v>
+        <v>6797429</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3923,10 +3923,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125012816</v>
+        <v>125014099</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3939,21 +3939,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385738</v>
+        <v>385699</v>
       </c>
       <c r="R31" t="n">
-        <v>6797251</v>
+        <v>6797223</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,7 +4035,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125010000</v>
+        <v>125016946</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385749</v>
+        <v>385697</v>
       </c>
       <c r="R32" t="n">
-        <v>6797429</v>
+        <v>6796899</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,10 +4147,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125014099</v>
+        <v>125007590</v>
       </c>
       <c r="B33" t="n">
-        <v>78842</v>
+        <v>78547</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4163,21 +4163,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4187,13 +4187,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385699</v>
+        <v>385922</v>
       </c>
       <c r="R33" t="n">
-        <v>6797223</v>
+        <v>6797211</v>
       </c>
       <c r="S33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,10 +4259,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125009311</v>
+        <v>125014208</v>
       </c>
       <c r="B34" t="n">
-        <v>78546</v>
+        <v>79399</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4275,21 +4275,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4299,13 +4299,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385900</v>
+        <v>385699</v>
       </c>
       <c r="R34" t="n">
-        <v>6797194</v>
+        <v>6797223</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,10 +4371,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125009342</v>
+        <v>125009311</v>
       </c>
       <c r="B35" t="n">
-        <v>79892</v>
+        <v>78546</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4411,13 +4411,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385861</v>
+        <v>385900</v>
       </c>
       <c r="R35" t="n">
-        <v>6797324</v>
+        <v>6797194</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4471,22 +4471,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125013825</v>
+        <v>125014757</v>
       </c>
       <c r="B36" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4499,21 +4499,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,13 +4523,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385689</v>
+        <v>385618</v>
       </c>
       <c r="R36" t="n">
-        <v>6797243</v>
+        <v>6797202</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,12 +4583,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4707,7 +4707,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125014035</v>
+        <v>125010604</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385607</v>
+        <v>385633</v>
       </c>
       <c r="R38" t="n">
-        <v>6797159</v>
+        <v>6797363</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,7 +4819,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125010031</v>
+        <v>125013977</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4859,10 +4859,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385750</v>
+        <v>385623</v>
       </c>
       <c r="R39" t="n">
-        <v>6797429</v>
+        <v>6797166</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4931,10 +4931,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125014011</v>
+        <v>125014510</v>
       </c>
       <c r="B40" t="n">
-        <v>56722</v>
+        <v>78547</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4943,53 +4943,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385610</v>
+        <v>385699</v>
       </c>
       <c r="R40" t="n">
-        <v>6797160</v>
+        <v>6797223</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5018,7 +5006,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +5016,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,22 +5031,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125007590</v>
+        <v>125008665</v>
       </c>
       <c r="B41" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5071,21 +5059,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5095,13 +5083,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385922</v>
+        <v>385900</v>
       </c>
       <c r="R41" t="n">
-        <v>6797211</v>
+        <v>6797194</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5130,7 +5118,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5140,7 +5128,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5167,10 +5155,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125015273</v>
+        <v>125006076</v>
       </c>
       <c r="B42" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5183,21 +5171,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5207,13 +5195,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385579</v>
+        <v>385896</v>
       </c>
       <c r="R42" t="n">
-        <v>6797173</v>
+        <v>6797101</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5242,7 +5230,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5252,7 +5240,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5279,10 +5267,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125014510</v>
+        <v>125015401</v>
       </c>
       <c r="B43" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5295,21 +5283,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5319,13 +5307,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385699</v>
+        <v>385632</v>
       </c>
       <c r="R43" t="n">
-        <v>6797223</v>
+        <v>6797173</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5354,7 +5342,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5364,7 +5352,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5379,22 +5367,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125008665</v>
+        <v>125008003</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>79399</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5407,21 +5395,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5437,7 +5425,7 @@
         <v>6797194</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5466,7 +5454,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5476,7 +5464,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5503,10 +5491,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125009359</v>
+        <v>125014812</v>
       </c>
       <c r="B45" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5519,21 +5507,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5543,13 +5531,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385862</v>
+        <v>385618</v>
       </c>
       <c r="R45" t="n">
-        <v>6797329</v>
+        <v>6797202</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5578,7 +5566,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5588,7 +5576,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5603,22 +5591,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125006190</v>
+        <v>125010542</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5631,21 +5619,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5655,10 +5643,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385871</v>
+        <v>385634</v>
       </c>
       <c r="R46" t="n">
-        <v>6797143</v>
+        <v>6797413</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5690,7 +5678,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5700,7 +5688,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5727,10 +5715,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125016946</v>
+        <v>125014011</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>56722</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5739,38 +5727,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385697</v>
+        <v>385610</v>
       </c>
       <c r="R47" t="n">
-        <v>6796899</v>
+        <v>6797160</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125014208</v>
+        <v>125015390</v>
       </c>
       <c r="B48" t="n">
-        <v>79399</v>
+        <v>78547</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,13 +5879,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385699</v>
+        <v>385632</v>
       </c>
       <c r="R48" t="n">
-        <v>6797223</v>
+        <v>6797173</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5939,22 +5939,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125014588</v>
+        <v>125010793</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5963,25 +5963,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385586</v>
+        <v>385779</v>
       </c>
       <c r="R49" t="n">
-        <v>6797244</v>
+        <v>6797286</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6036,12 +6036,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6068,10 +6063,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125006056</v>
+        <v>125015299</v>
       </c>
       <c r="B50" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6080,49 +6075,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385924</v>
+        <v>385588</v>
       </c>
       <c r="R50" t="n">
-        <v>6797115</v>
+        <v>6797184</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6151,7 +6138,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6161,7 +6148,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6188,10 +6180,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125014342</v>
+        <v>125014700</v>
       </c>
       <c r="B51" t="n">
-        <v>78547</v>
+        <v>79919</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6200,25 +6192,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6228,10 +6220,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385611</v>
+        <v>385567</v>
       </c>
       <c r="R51" t="n">
-        <v>6797222</v>
+        <v>6797275</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6263,7 +6255,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6273,7 +6265,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6300,10 +6292,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125010269</v>
+        <v>125008520</v>
       </c>
       <c r="B52" t="n">
-        <v>79891</v>
+        <v>78547</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6316,21 +6308,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6340,13 +6332,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385756</v>
+        <v>385868</v>
       </c>
       <c r="R52" t="n">
-        <v>6797314</v>
+        <v>6797226</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6375,7 +6367,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6385,12 +6377,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6410,14 +6397,14 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125014685</v>
+        <v>125016157</v>
       </c>
       <c r="B53" t="n">
         <v>79891</v>
@@ -6451,19 +6438,16 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385571</v>
+        <v>385706</v>
       </c>
       <c r="R53" t="n">
-        <v>6797259</v>
+        <v>6797113</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6495,7 +6479,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6505,7 +6489,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6514,7 +6498,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6533,10 +6516,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125009952</v>
+        <v>125010269</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6549,21 +6532,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6573,10 +6556,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385760</v>
+        <v>385756</v>
       </c>
       <c r="R54" t="n">
-        <v>6797317</v>
+        <v>6797314</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6608,7 +6591,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6618,7 +6601,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6638,17 +6626,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125016771</v>
+        <v>125014685</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6661,34 +6649,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385674</v>
+        <v>385571</v>
       </c>
       <c r="R55" t="n">
-        <v>6796981</v>
+        <v>6797259</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6720,7 +6711,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6730,7 +6721,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6739,6 +6730,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6757,10 +6749,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125010560</v>
+        <v>125014307</v>
       </c>
       <c r="B56" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6773,21 +6765,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6797,10 +6789,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385763</v>
+        <v>385616</v>
       </c>
       <c r="R56" t="n">
-        <v>6797307</v>
+        <v>6797214</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6832,7 +6824,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6842,7 +6834,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6986,10 +6978,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125014307</v>
+        <v>125014604</v>
       </c>
       <c r="B58" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7002,21 +6994,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7026,10 +7018,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385616</v>
+        <v>385586</v>
       </c>
       <c r="R58" t="n">
-        <v>6797214</v>
+        <v>6797242</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7061,7 +7053,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7071,7 +7063,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7098,10 +7090,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125008506</v>
+        <v>125014083</v>
       </c>
       <c r="B59" t="n">
-        <v>78546</v>
+        <v>78842</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7114,21 +7106,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7138,13 +7130,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385867</v>
+        <v>385689</v>
       </c>
       <c r="R59" t="n">
-        <v>6797218</v>
+        <v>6797223</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7173,7 +7165,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7183,7 +7175,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7210,7 +7202,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125008520</v>
+        <v>125014342</v>
       </c>
       <c r="B60" t="n">
         <v>78547</v>
@@ -7250,10 +7242,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385868</v>
+        <v>385611</v>
       </c>
       <c r="R60" t="n">
-        <v>6797226</v>
+        <v>6797222</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7285,7 +7277,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7295,7 +7287,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7322,10 +7314,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125014817</v>
+        <v>125009952</v>
       </c>
       <c r="B61" t="n">
-        <v>79919</v>
+        <v>78810</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7334,25 +7326,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7362,13 +7354,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385541</v>
+        <v>385760</v>
       </c>
       <c r="R61" t="n">
-        <v>6797264</v>
+        <v>6797317</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7397,7 +7389,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7407,12 +7399,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Vid myr, tjärn</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7439,10 +7426,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125014700</v>
+        <v>125014853</v>
       </c>
       <c r="B62" t="n">
-        <v>79919</v>
+        <v>79891</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7451,25 +7438,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7479,10 +7466,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385567</v>
+        <v>385539</v>
       </c>
       <c r="R62" t="n">
-        <v>6797275</v>
+        <v>6797252</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7514,7 +7501,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7524,7 +7511,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7551,10 +7538,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125015299</v>
+        <v>125074279</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7563,38 +7550,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385588</v>
+        <v>385755</v>
       </c>
       <c r="R63" t="n">
-        <v>6797184</v>
+        <v>6797321</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7624,32 +7615,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7661,17 +7638,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125014853</v>
+        <v>125016771</v>
       </c>
       <c r="B64" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7684,21 +7661,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7708,10 +7685,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385539</v>
+        <v>385674</v>
       </c>
       <c r="R64" t="n">
-        <v>6797252</v>
+        <v>6796981</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7743,7 +7720,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7753,7 +7730,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7780,7 +7757,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125014604</v>
+        <v>125010560</v>
       </c>
       <c r="B65" t="n">
         <v>78810</v>
@@ -7820,10 +7797,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385586</v>
+        <v>385763</v>
       </c>
       <c r="R65" t="n">
-        <v>6797242</v>
+        <v>6797307</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7855,7 +7832,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7865,7 +7842,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7892,10 +7869,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125074279</v>
+        <v>125008506</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>78546</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7904,42 +7881,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sätern, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385755</v>
+        <v>385867</v>
       </c>
       <c r="R66" t="n">
-        <v>6797321</v>
+        <v>6797218</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7969,18 +7942,27 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7992,17 +7974,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125010793</v>
+        <v>125006056</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8011,41 +7993,49 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385779</v>
+        <v>385924</v>
       </c>
       <c r="R67" t="n">
-        <v>6797286</v>
+        <v>6797115</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8074,7 +8064,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8084,7 +8074,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8111,10 +8101,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125015566</v>
+        <v>125011588</v>
       </c>
       <c r="B68" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8127,21 +8117,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8151,13 +8141,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385640</v>
+        <v>385737</v>
       </c>
       <c r="R68" t="n">
-        <v>6797141</v>
+        <v>6797241</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8186,7 +8176,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8196,7 +8186,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8223,10 +8213,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125011588</v>
+        <v>125014817</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8235,25 +8225,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8263,13 +8253,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385737</v>
+        <v>385541</v>
       </c>
       <c r="R69" t="n">
-        <v>6797241</v>
+        <v>6797264</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8298,7 +8288,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8308,7 +8298,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8335,10 +8330,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125014083</v>
+        <v>125014588</v>
       </c>
       <c r="B70" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8351,21 +8346,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8375,13 +8370,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385689</v>
+        <v>385586</v>
       </c>
       <c r="R70" t="n">
-        <v>6797223</v>
+        <v>6797244</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8410,7 +8405,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8420,7 +8415,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8440,17 +8440,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125016157</v>
+        <v>125015566</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8463,21 +8463,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385706</v>
+        <v>385640</v>
       </c>
       <c r="R71" t="n">
-        <v>6797113</v>
+        <v>6797141</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Lisa Olson, Göran Ehn, Anna-Britt Olsson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125004587</v>
+        <v>125004345</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>78684</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R2" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125004345</v>
+        <v>125004366</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>79536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125004366</v>
+        <v>125004587</v>
       </c>
       <c r="B4" t="n">
-        <v>79399</v>
+        <v>78683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R4" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125004665</v>
+        <v>125004324</v>
       </c>
       <c r="B5" t="n">
-        <v>79428</v>
+        <v>78683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R5" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125004576</v>
+        <v>125004665</v>
       </c>
       <c r="B6" t="n">
-        <v>78547</v>
+        <v>79565</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004324</v>
+        <v>125004576</v>
       </c>
       <c r="B7" t="n">
-        <v>78546</v>
+        <v>78684</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R7" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,7 +1350,7 @@
         <v>125004325</v>
       </c>
       <c r="B8" t="n">
-        <v>78834</v>
+        <v>78971</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125008604</v>
+        <v>125014757</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385867</v>
+        <v>385618</v>
       </c>
       <c r="R9" t="n">
-        <v>6797219</v>
+        <v>6797202</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,22 +1559,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125010031</v>
+        <v>125014057</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385750</v>
+        <v>385607</v>
       </c>
       <c r="R10" t="n">
-        <v>6797429</v>
+        <v>6797159</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125009359</v>
+        <v>125013825</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>80029</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385862</v>
+        <v>385689</v>
       </c>
       <c r="R11" t="n">
-        <v>6797329</v>
+        <v>6797243</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125015273</v>
+        <v>125007590</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385579</v>
+        <v>385922</v>
       </c>
       <c r="R12" t="n">
-        <v>6797173</v>
+        <v>6797211</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125013825</v>
+        <v>125013949</v>
       </c>
       <c r="B13" t="n">
-        <v>79892</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385689</v>
+        <v>385633</v>
       </c>
       <c r="R13" t="n">
-        <v>6797243</v>
+        <v>6797184</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125015572</v>
+        <v>125016901</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385709</v>
+        <v>385697</v>
       </c>
       <c r="R14" t="n">
-        <v>6797118</v>
+        <v>6796929</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125016901</v>
+        <v>125008649</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385697</v>
+        <v>385867</v>
       </c>
       <c r="R15" t="n">
-        <v>6796929</v>
+        <v>6797219</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125015275</v>
+        <v>125014011</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>56836</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,38 +2255,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385609</v>
+        <v>385610</v>
       </c>
       <c r="R16" t="n">
-        <v>6797178</v>
+        <v>6797160</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2318,7 +2330,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2340,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125013949</v>
+        <v>125016946</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,10 +2407,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385633</v>
+        <v>385697</v>
       </c>
       <c r="R17" t="n">
-        <v>6797184</v>
+        <v>6796899</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2430,7 +2442,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2452,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125008432</v>
+        <v>125009342</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>80029</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2495,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2519,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385888</v>
+        <v>385861</v>
       </c>
       <c r="R18" t="n">
-        <v>6797224</v>
+        <v>6797324</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2542,7 +2554,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2564,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,10 +2591,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125006190</v>
+        <v>125010553</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78684</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,13 +2631,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385871</v>
+        <v>385876</v>
       </c>
       <c r="R19" t="n">
-        <v>6797143</v>
+        <v>6797310</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,7 +2666,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2676,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,22 +2691,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125009430</v>
+        <v>125015797</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>80029</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,21 +2719,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,13 +2743,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385862</v>
+        <v>385690</v>
       </c>
       <c r="R20" t="n">
-        <v>6797329</v>
+        <v>6797129</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2766,7 +2778,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2788,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,22 +2803,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125011580</v>
+        <v>125015275</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2831,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,13 +2855,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385738</v>
+        <v>385609</v>
       </c>
       <c r="R21" t="n">
-        <v>6797251</v>
+        <v>6797178</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,7 +2890,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2900,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,22 +2915,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125015347</v>
+        <v>125013977</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2955,13 +2967,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385592</v>
+        <v>385623</v>
       </c>
       <c r="R22" t="n">
-        <v>6797161</v>
+        <v>6797166</v>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2990,7 +3002,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3012,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3015,22 +3027,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125012816</v>
+        <v>125010000</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3067,13 +3079,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385738</v>
+        <v>385749</v>
       </c>
       <c r="R23" t="n">
-        <v>6797251</v>
+        <v>6797429</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3102,7 +3114,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3112,7 +3124,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3127,22 +3139,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125010553</v>
+        <v>125008003</v>
       </c>
       <c r="B24" t="n">
-        <v>78547</v>
+        <v>79536</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3167,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,13 +3191,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385876</v>
+        <v>385900</v>
       </c>
       <c r="R24" t="n">
-        <v>6797310</v>
+        <v>6797194</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3214,7 +3226,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3236,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,10 +3263,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125014035</v>
+        <v>125015347</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3291,13 +3303,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385607</v>
+        <v>385592</v>
       </c>
       <c r="R25" t="n">
-        <v>6797159</v>
+        <v>6797161</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3326,7 +3338,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3348,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3351,22 +3363,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125015797</v>
+        <v>125008432</v>
       </c>
       <c r="B26" t="n">
-        <v>79892</v>
+        <v>78947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3391,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,13 +3415,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385690</v>
+        <v>385888</v>
       </c>
       <c r="R26" t="n">
-        <v>6797129</v>
+        <v>6797224</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3438,7 +3450,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3460,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,22 +3475,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125009342</v>
+        <v>125011580</v>
       </c>
       <c r="B27" t="n">
-        <v>79892</v>
+        <v>80028</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3503,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,13 +3527,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385861</v>
+        <v>385738</v>
       </c>
       <c r="R27" t="n">
-        <v>6797324</v>
+        <v>6797251</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3550,7 +3562,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3572,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3575,22 +3587,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125009781</v>
+        <v>125006190</v>
       </c>
       <c r="B28" t="n">
-        <v>78546</v>
+        <v>78947</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3615,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3639,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385862</v>
+        <v>385871</v>
       </c>
       <c r="R28" t="n">
-        <v>6797329</v>
+        <v>6797143</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3662,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3672,7 +3684,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,10 +3711,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125013776</v>
+        <v>125015273</v>
       </c>
       <c r="B29" t="n">
-        <v>79891</v>
+        <v>78684</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3715,21 +3727,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3739,13 +3751,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385692</v>
+        <v>385579</v>
       </c>
       <c r="R29" t="n">
-        <v>6797239</v>
+        <v>6797173</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3774,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3784,7 +3796,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3799,22 +3811,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125010000</v>
+        <v>125015390</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>78684</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3827,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3851,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385749</v>
+        <v>385632</v>
       </c>
       <c r="R30" t="n">
-        <v>6797429</v>
+        <v>6797173</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3886,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3896,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3923,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125014099</v>
+        <v>125010594</v>
       </c>
       <c r="B31" t="n">
-        <v>78842</v>
+        <v>78947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3939,21 +3951,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3963,13 +3975,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385699</v>
+        <v>385633</v>
       </c>
       <c r="R31" t="n">
-        <v>6797223</v>
+        <v>6797363</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3998,7 +4010,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4008,7 +4020,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4023,22 +4035,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125016946</v>
+        <v>125009430</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4075,10 +4087,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385697</v>
+        <v>385862</v>
       </c>
       <c r="R32" t="n">
-        <v>6796899</v>
+        <v>6797329</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4110,7 +4122,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4120,7 +4132,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4147,10 +4159,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125007590</v>
+        <v>125014812</v>
       </c>
       <c r="B33" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4187,13 +4199,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385922</v>
+        <v>385618</v>
       </c>
       <c r="R33" t="n">
-        <v>6797211</v>
+        <v>6797202</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4222,7 +4234,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4232,7 +4244,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,10 +4271,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125014208</v>
+        <v>125014099</v>
       </c>
       <c r="B34" t="n">
-        <v>79399</v>
+        <v>78979</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4275,21 +4287,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4305,7 +4317,7 @@
         <v>6797223</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4334,7 +4346,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4344,7 +4356,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,10 +4383,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125009311</v>
+        <v>125006076</v>
       </c>
       <c r="B35" t="n">
-        <v>78546</v>
+        <v>78947</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4387,21 +4399,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4411,13 +4423,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385900</v>
+        <v>385896</v>
       </c>
       <c r="R35" t="n">
-        <v>6797194</v>
+        <v>6797101</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4446,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4456,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,10 +4495,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125014757</v>
+        <v>125010542</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4499,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4523,13 +4535,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385618</v>
+        <v>385634</v>
       </c>
       <c r="R36" t="n">
-        <v>6797202</v>
+        <v>6797413</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4558,7 +4570,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4568,7 +4580,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,22 +4595,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125015297</v>
+        <v>125009359</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4611,21 +4623,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4635,13 +4647,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385569</v>
+        <v>385862</v>
       </c>
       <c r="R37" t="n">
-        <v>6797152</v>
+        <v>6797329</v>
       </c>
       <c r="S37" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4670,7 +4682,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4680,7 +4692,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4695,22 +4707,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125010604</v>
+        <v>125008665</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4747,13 +4759,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385633</v>
+        <v>385900</v>
       </c>
       <c r="R38" t="n">
-        <v>6797363</v>
+        <v>6797194</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4782,7 +4794,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4792,7 +4804,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4807,22 +4819,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125013977</v>
+        <v>125013776</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4835,21 +4847,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4859,10 +4871,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385623</v>
+        <v>385692</v>
       </c>
       <c r="R39" t="n">
-        <v>6797166</v>
+        <v>6797239</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4894,7 +4906,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4904,7 +4916,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4931,10 +4943,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125014510</v>
+        <v>125012816</v>
       </c>
       <c r="B40" t="n">
-        <v>78547</v>
+        <v>78947</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4947,21 +4959,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4971,13 +4983,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385699</v>
+        <v>385738</v>
       </c>
       <c r="R40" t="n">
-        <v>6797223</v>
+        <v>6797251</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5006,7 +5018,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5016,7 +5028,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,10 +5055,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125008665</v>
+        <v>125015297</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5083,13 +5095,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385900</v>
+        <v>385569</v>
       </c>
       <c r="R41" t="n">
-        <v>6797194</v>
+        <v>6797152</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5118,7 +5130,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5128,7 +5140,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,10 +5167,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125006076</v>
+        <v>125015401</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5171,21 +5183,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5195,13 +5207,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385896</v>
+        <v>385632</v>
       </c>
       <c r="R42" t="n">
-        <v>6797101</v>
+        <v>6797173</v>
       </c>
       <c r="S42" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5230,7 +5242,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5240,7 +5252,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5255,22 +5267,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125015401</v>
+        <v>125009311</v>
       </c>
       <c r="B43" t="n">
-        <v>78546</v>
+        <v>78683</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5307,13 +5319,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385632</v>
+        <v>385900</v>
       </c>
       <c r="R43" t="n">
-        <v>6797173</v>
+        <v>6797194</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5342,7 +5354,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5352,7 +5364,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5367,22 +5379,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125008003</v>
+        <v>125014208</v>
       </c>
       <c r="B44" t="n">
-        <v>79399</v>
+        <v>79536</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5419,13 +5431,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385900</v>
+        <v>385699</v>
       </c>
       <c r="R44" t="n">
-        <v>6797194</v>
+        <v>6797223</v>
       </c>
       <c r="S44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5454,7 +5466,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5464,7 +5476,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5491,10 +5503,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125014812</v>
+        <v>125014510</v>
       </c>
       <c r="B45" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5531,10 +5543,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385618</v>
+        <v>385699</v>
       </c>
       <c r="R45" t="n">
-        <v>6797202</v>
+        <v>6797223</v>
       </c>
       <c r="S45" t="n">
         <v>9</v>
@@ -5566,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5576,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5603,10 +5615,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125010542</v>
+        <v>125009781</v>
       </c>
       <c r="B46" t="n">
-        <v>78546</v>
+        <v>78683</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5643,10 +5655,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385634</v>
+        <v>385862</v>
       </c>
       <c r="R46" t="n">
-        <v>6797413</v>
+        <v>6797329</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5678,7 +5690,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5688,7 +5700,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5715,10 +5727,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125014011</v>
+        <v>125015572</v>
       </c>
       <c r="B47" t="n">
-        <v>56722</v>
+        <v>80028</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5727,50 +5739,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385610</v>
+        <v>385709</v>
       </c>
       <c r="R47" t="n">
-        <v>6797160</v>
+        <v>6797118</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5839,10 +5839,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125015390</v>
+        <v>125010031</v>
       </c>
       <c r="B48" t="n">
-        <v>78547</v>
+        <v>78947</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5855,21 +5855,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385632</v>
+        <v>385750</v>
       </c>
       <c r="R48" t="n">
-        <v>6797173</v>
+        <v>6797429</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5951,10 +5951,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125010793</v>
+        <v>125015299</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5963,25 +5963,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385779</v>
+        <v>385588</v>
       </c>
       <c r="R49" t="n">
-        <v>6797286</v>
+        <v>6797184</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6036,7 +6036,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6063,10 +6068,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125015299</v>
+        <v>125014685</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6079,34 +6084,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385588</v>
+        <v>385571</v>
       </c>
       <c r="R50" t="n">
-        <v>6797184</v>
+        <v>6797259</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6138,7 +6146,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6148,12 +6156,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6162,6 +6165,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6180,10 +6184,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125014700</v>
+        <v>125074279</v>
       </c>
       <c r="B51" t="n">
-        <v>79919</v>
+        <v>98269</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6192,38 +6196,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385567</v>
+        <v>385755</v>
       </c>
       <c r="R51" t="n">
-        <v>6797275</v>
+        <v>6797321</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6253,27 +6261,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6285,17 +6284,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125008520</v>
+        <v>125014307</v>
       </c>
       <c r="B52" t="n">
-        <v>78547</v>
+        <v>78683</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6308,21 +6307,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6332,10 +6331,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385868</v>
+        <v>385616</v>
       </c>
       <c r="R52" t="n">
-        <v>6797226</v>
+        <v>6797214</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6367,7 +6366,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6377,7 +6376,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6404,10 +6403,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125016157</v>
+        <v>125014853</v>
       </c>
       <c r="B53" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6444,10 +6443,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385706</v>
+        <v>385539</v>
       </c>
       <c r="R53" t="n">
-        <v>6797113</v>
+        <v>6797252</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6479,7 +6478,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6489,7 +6488,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6516,10 +6515,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125010269</v>
+        <v>125014588</v>
       </c>
       <c r="B54" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6532,21 +6531,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6556,13 +6555,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385756</v>
+        <v>385586</v>
       </c>
       <c r="R54" t="n">
-        <v>6797314</v>
+        <v>6797244</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6591,7 +6590,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6601,12 +6600,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6633,10 +6632,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125014685</v>
+        <v>125016771</v>
       </c>
       <c r="B55" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6649,37 +6648,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385571</v>
+        <v>385674</v>
       </c>
       <c r="R55" t="n">
-        <v>6797259</v>
+        <v>6796981</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6711,7 +6707,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6721,7 +6717,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6730,7 +6726,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6749,10 +6744,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125014307</v>
+        <v>125010269</v>
       </c>
       <c r="B56" t="n">
-        <v>78546</v>
+        <v>80028</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6765,21 +6760,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6789,13 +6784,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385616</v>
+        <v>385756</v>
       </c>
       <c r="R56" t="n">
-        <v>6797214</v>
+        <v>6797314</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6824,7 +6819,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6834,7 +6829,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6861,10 +6861,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125014769</v>
+        <v>125009952</v>
       </c>
       <c r="B57" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6877,21 +6877,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6901,13 +6901,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385552</v>
+        <v>385760</v>
       </c>
       <c r="R57" t="n">
-        <v>6797252</v>
+        <v>6797317</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6946,12 +6946,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Vid myr, källa?</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6978,10 +6973,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125014604</v>
+        <v>125010793</v>
       </c>
       <c r="B58" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6990,25 +6985,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7018,10 +7013,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385586</v>
+        <v>385779</v>
       </c>
       <c r="R58" t="n">
-        <v>6797242</v>
+        <v>6797286</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7053,7 +7048,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7063,7 +7058,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7090,10 +7085,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125014083</v>
+        <v>125006056</v>
       </c>
       <c r="B59" t="n">
-        <v>78842</v>
+        <v>56836</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7102,38 +7097,46 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385689</v>
+        <v>385924</v>
       </c>
       <c r="R59" t="n">
-        <v>6797223</v>
+        <v>6797115</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7165,7 +7168,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7175,7 +7178,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7202,10 +7205,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125014342</v>
+        <v>125014700</v>
       </c>
       <c r="B60" t="n">
-        <v>78547</v>
+        <v>80056</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7214,25 +7217,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6461</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7242,10 +7245,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385611</v>
+        <v>385567</v>
       </c>
       <c r="R60" t="n">
-        <v>6797222</v>
+        <v>6797275</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7277,7 +7280,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7287,7 +7290,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7314,10 +7317,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125009952</v>
+        <v>125014604</v>
       </c>
       <c r="B61" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7354,13 +7357,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385760</v>
+        <v>385586</v>
       </c>
       <c r="R61" t="n">
-        <v>6797317</v>
+        <v>6797242</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7389,7 +7392,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7399,7 +7402,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7426,10 +7429,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125014853</v>
+        <v>125008520</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>78684</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7442,21 +7445,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7466,10 +7469,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385539</v>
+        <v>385868</v>
       </c>
       <c r="R62" t="n">
-        <v>6797252</v>
+        <v>6797226</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7501,7 +7504,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7511,7 +7514,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7538,10 +7541,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125074279</v>
+        <v>125015566</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>78683</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7550,42 +7553,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sätern, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385755</v>
+        <v>385640</v>
       </c>
       <c r="R63" t="n">
-        <v>6797321</v>
+        <v>6797141</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7615,18 +7614,27 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7638,17 +7646,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125016771</v>
+        <v>125014083</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>78979</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7661,21 +7669,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7685,13 +7693,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385674</v>
+        <v>385689</v>
       </c>
       <c r="R64" t="n">
-        <v>6796981</v>
+        <v>6797223</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7720,7 +7728,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7730,7 +7738,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7757,10 +7765,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125010560</v>
+        <v>125016157</v>
       </c>
       <c r="B65" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7773,21 +7781,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7797,10 +7805,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385763</v>
+        <v>385706</v>
       </c>
       <c r="R65" t="n">
-        <v>6797307</v>
+        <v>6797113</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7832,7 +7840,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7842,7 +7850,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7869,10 +7877,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125008506</v>
+        <v>125011588</v>
       </c>
       <c r="B66" t="n">
-        <v>78546</v>
+        <v>78947</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7885,21 +7893,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7909,13 +7917,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385867</v>
+        <v>385737</v>
       </c>
       <c r="R66" t="n">
-        <v>6797218</v>
+        <v>6797241</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7944,7 +7952,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7954,7 +7962,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7981,10 +7989,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125006056</v>
+        <v>125014817</v>
       </c>
       <c r="B67" t="n">
-        <v>56722</v>
+        <v>80056</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7997,45 +8005,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6461</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385924</v>
+        <v>385541</v>
       </c>
       <c r="R67" t="n">
-        <v>6797115</v>
+        <v>6797264</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8074,7 +8074,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8101,10 +8106,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125011588</v>
+        <v>125008506</v>
       </c>
       <c r="B68" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8117,21 +8122,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8141,13 +8146,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385737</v>
+        <v>385867</v>
       </c>
       <c r="R68" t="n">
-        <v>6797241</v>
+        <v>6797218</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8176,7 +8181,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8186,7 +8191,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8213,10 +8218,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014817</v>
+        <v>125014769</v>
       </c>
       <c r="B69" t="n">
-        <v>79919</v>
+        <v>80028</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8225,25 +8230,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8253,10 +8258,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385541</v>
+        <v>385552</v>
       </c>
       <c r="R69" t="n">
-        <v>6797264</v>
+        <v>6797252</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8288,7 +8293,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8298,12 +8303,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Vid myr, tjärn</t>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8330,10 +8335,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125014588</v>
+        <v>125010560</v>
       </c>
       <c r="B70" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8370,10 +8375,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385586</v>
+        <v>385763</v>
       </c>
       <c r="R70" t="n">
-        <v>6797244</v>
+        <v>6797307</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8405,7 +8410,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8415,12 +8420,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8447,10 +8447,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125015566</v>
+        <v>125014342</v>
       </c>
       <c r="B71" t="n">
-        <v>78546</v>
+        <v>78684</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8463,21 +8463,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8487,10 +8487,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385640</v>
+        <v>385611</v>
       </c>
       <c r="R71" t="n">
-        <v>6797141</v>
+        <v>6797222</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -2479,10 +2479,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125009342</v>
+        <v>125010553</v>
       </c>
       <c r="B18" t="n">
-        <v>80029</v>
+        <v>78684</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2495,21 +2495,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385861</v>
+        <v>385876</v>
       </c>
       <c r="R18" t="n">
-        <v>6797324</v>
+        <v>6797310</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,22 +2579,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125010553</v>
+        <v>125009342</v>
       </c>
       <c r="B19" t="n">
-        <v>78684</v>
+        <v>80029</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,21 +2607,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385876</v>
+        <v>385861</v>
       </c>
       <c r="R19" t="n">
-        <v>6797310</v>
+        <v>6797324</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,12 +2691,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125004345</v>
+        <v>125004665</v>
       </c>
       <c r="B2" t="n">
-        <v>78684</v>
+        <v>79565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R2" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125004366</v>
+        <v>125004345</v>
       </c>
       <c r="B3" t="n">
-        <v>79536</v>
+        <v>78684</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125004587</v>
+        <v>125004576</v>
       </c>
       <c r="B4" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125004324</v>
+        <v>125004587</v>
       </c>
       <c r="B5" t="n">
         <v>78683</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R5" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125004665</v>
+        <v>125004324</v>
       </c>
       <c r="B6" t="n">
-        <v>79565</v>
+        <v>78683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R6" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004576</v>
+        <v>125004366</v>
       </c>
       <c r="B7" t="n">
-        <v>78684</v>
+        <v>79536</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R7" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125014757</v>
+        <v>125009781</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385618</v>
+        <v>385862</v>
       </c>
       <c r="R9" t="n">
-        <v>6797202</v>
+        <v>6797329</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,22 +1559,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125014057</v>
+        <v>125011580</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385607</v>
+        <v>385738</v>
       </c>
       <c r="R10" t="n">
-        <v>6797159</v>
+        <v>6797251</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,22 +1671,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125013825</v>
+        <v>125010604</v>
       </c>
       <c r="B11" t="n">
-        <v>80029</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385689</v>
+        <v>385633</v>
       </c>
       <c r="R11" t="n">
-        <v>6797243</v>
+        <v>6797363</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125007590</v>
+        <v>125013977</v>
       </c>
       <c r="B12" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385922</v>
+        <v>385623</v>
       </c>
       <c r="R12" t="n">
-        <v>6797211</v>
+        <v>6797166</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,22 +1895,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125013949</v>
+        <v>125009311</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385633</v>
+        <v>385900</v>
       </c>
       <c r="R13" t="n">
-        <v>6797184</v>
+        <v>6797194</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,19 +2007,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125016901</v>
+        <v>125016913</v>
       </c>
       <c r="B14" t="n">
         <v>78947</v>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125008649</v>
+        <v>125015401</v>
       </c>
       <c r="B15" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385867</v>
+        <v>385632</v>
       </c>
       <c r="R15" t="n">
-        <v>6797219</v>
+        <v>6797173</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125014011</v>
+        <v>125014057</v>
       </c>
       <c r="B16" t="n">
-        <v>56836</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,50 +2255,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385610</v>
+        <v>385607</v>
       </c>
       <c r="R16" t="n">
-        <v>6797160</v>
+        <v>6797159</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2330,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2340,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125016946</v>
+        <v>125014510</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2383,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2407,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385697</v>
+        <v>385699</v>
       </c>
       <c r="R17" t="n">
-        <v>6796899</v>
+        <v>6797223</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2442,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2452,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,22 +2455,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125010553</v>
+        <v>125015797</v>
       </c>
       <c r="B18" t="n">
-        <v>78684</v>
+        <v>80029</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2495,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2519,13 +2507,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385876</v>
+        <v>385690</v>
       </c>
       <c r="R18" t="n">
-        <v>6797310</v>
+        <v>6797129</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2554,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2564,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125009342</v>
+        <v>125008543</v>
       </c>
       <c r="B19" t="n">
-        <v>80029</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2607,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385861</v>
+        <v>385867</v>
       </c>
       <c r="R19" t="n">
-        <v>6797324</v>
+        <v>6797219</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2666,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2676,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2703,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125015797</v>
+        <v>125010542</v>
       </c>
       <c r="B20" t="n">
-        <v>80029</v>
+        <v>78683</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2719,21 +2707,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2743,13 +2731,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385690</v>
+        <v>385634</v>
       </c>
       <c r="R20" t="n">
-        <v>6797129</v>
+        <v>6797413</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2778,7 +2766,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2788,7 +2776,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,19 +2791,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125015275</v>
+        <v>125010031</v>
       </c>
       <c r="B21" t="n">
         <v>78947</v>
@@ -2855,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385609</v>
+        <v>385750</v>
       </c>
       <c r="R21" t="n">
-        <v>6797178</v>
+        <v>6797429</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2890,7 +2878,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2900,7 +2888,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2927,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125013977</v>
+        <v>125014011</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
+        <v>56836</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2939,38 +2927,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385623</v>
+        <v>385610</v>
       </c>
       <c r="R22" t="n">
-        <v>6797166</v>
+        <v>6797160</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3039,10 +3039,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125010000</v>
+        <v>125007590</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3055,21 +3055,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3079,13 +3079,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385749</v>
+        <v>385922</v>
       </c>
       <c r="R23" t="n">
-        <v>6797429</v>
+        <v>6797211</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,22 +3139,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125008003</v>
+        <v>125014757</v>
       </c>
       <c r="B24" t="n">
-        <v>79536</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3167,21 +3167,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3191,13 +3191,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385900</v>
+        <v>385618</v>
       </c>
       <c r="R24" t="n">
-        <v>6797194</v>
+        <v>6797202</v>
       </c>
       <c r="S24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125008432</v>
+        <v>125010553</v>
       </c>
       <c r="B26" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3391,21 +3391,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3415,13 +3415,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385888</v>
+        <v>385876</v>
       </c>
       <c r="R26" t="n">
-        <v>6797224</v>
+        <v>6797310</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,22 +3475,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125011580</v>
+        <v>125015297</v>
       </c>
       <c r="B27" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3503,21 +3503,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385738</v>
+        <v>385569</v>
       </c>
       <c r="R27" t="n">
-        <v>6797251</v>
+        <v>6797152</v>
       </c>
       <c r="S27" t="n">
         <v>11</v>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3599,7 +3599,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125006190</v>
+        <v>125008432</v>
       </c>
       <c r="B28" t="n">
         <v>78947</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385871</v>
+        <v>385888</v>
       </c>
       <c r="R28" t="n">
-        <v>6797143</v>
+        <v>6797224</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3711,7 +3711,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125015273</v>
+        <v>125014812</v>
       </c>
       <c r="B29" t="n">
         <v>78684</v>
@@ -3751,13 +3751,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385579</v>
+        <v>385618</v>
       </c>
       <c r="R29" t="n">
-        <v>6797173</v>
+        <v>6797202</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3823,10 +3823,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125015390</v>
+        <v>125013776</v>
       </c>
       <c r="B30" t="n">
-        <v>78684</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3839,21 +3839,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385632</v>
+        <v>385692</v>
       </c>
       <c r="R30" t="n">
-        <v>6797173</v>
+        <v>6797239</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125010594</v>
+        <v>125014099</v>
       </c>
       <c r="B31" t="n">
-        <v>78947</v>
+        <v>78979</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3951,21 +3951,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3975,13 +3975,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385633</v>
+        <v>385699</v>
       </c>
       <c r="R31" t="n">
-        <v>6797363</v>
+        <v>6797223</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,22 +4035,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125009430</v>
+        <v>125015390</v>
       </c>
       <c r="B32" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4063,21 +4063,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385862</v>
+        <v>385632</v>
       </c>
       <c r="R32" t="n">
-        <v>6797329</v>
+        <v>6797173</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4159,10 +4159,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125014812</v>
+        <v>125009430</v>
       </c>
       <c r="B33" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4175,21 +4175,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4199,13 +4199,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385618</v>
+        <v>385862</v>
       </c>
       <c r="R33" t="n">
-        <v>6797202</v>
+        <v>6797329</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4259,22 +4259,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125014099</v>
+        <v>125015572</v>
       </c>
       <c r="B34" t="n">
-        <v>78979</v>
+        <v>80028</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385699</v>
+        <v>385709</v>
       </c>
       <c r="R34" t="n">
-        <v>6797223</v>
+        <v>6797118</v>
       </c>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4371,22 +4371,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125006076</v>
+        <v>125013825</v>
       </c>
       <c r="B35" t="n">
-        <v>78947</v>
+        <v>80029</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4399,21 +4399,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385896</v>
+        <v>385689</v>
       </c>
       <c r="R35" t="n">
-        <v>6797101</v>
+        <v>6797243</v>
       </c>
       <c r="S35" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,22 +4483,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125010542</v>
+        <v>125010000</v>
       </c>
       <c r="B36" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385634</v>
+        <v>385749</v>
       </c>
       <c r="R36" t="n">
-        <v>6797413</v>
+        <v>6797429</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4719,7 +4719,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125008665</v>
+        <v>125006076</v>
       </c>
       <c r="B38" t="n">
         <v>78947</v>
@@ -4759,13 +4759,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385900</v>
+        <v>385896</v>
       </c>
       <c r="R38" t="n">
-        <v>6797194</v>
+        <v>6797101</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4831,10 +4831,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125013776</v>
+        <v>125016946</v>
       </c>
       <c r="B39" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4847,21 +4847,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385692</v>
+        <v>385697</v>
       </c>
       <c r="R39" t="n">
-        <v>6797239</v>
+        <v>6796899</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4943,10 +4943,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125012816</v>
+        <v>125009342</v>
       </c>
       <c r="B40" t="n">
-        <v>78947</v>
+        <v>80029</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,21 +4959,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4983,13 +4983,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385738</v>
+        <v>385861</v>
       </c>
       <c r="R40" t="n">
-        <v>6797251</v>
+        <v>6797324</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,19 +5043,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125015297</v>
+        <v>125008665</v>
       </c>
       <c r="B41" t="n">
         <v>78947</v>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385569</v>
+        <v>385900</v>
       </c>
       <c r="R41" t="n">
-        <v>6797152</v>
+        <v>6797194</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5167,10 +5167,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125015401</v>
+        <v>125015273</v>
       </c>
       <c r="B42" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5183,21 +5183,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385632</v>
+        <v>385579</v>
       </c>
       <c r="R42" t="n">
         <v>6797173</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5267,22 +5267,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125009311</v>
+        <v>125014208</v>
       </c>
       <c r="B43" t="n">
-        <v>78683</v>
+        <v>79536</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5295,21 +5295,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5319,13 +5319,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385900</v>
+        <v>385699</v>
       </c>
       <c r="R43" t="n">
-        <v>6797194</v>
+        <v>6797223</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5391,10 +5391,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125014208</v>
+        <v>125015275</v>
       </c>
       <c r="B44" t="n">
-        <v>79536</v>
+        <v>78947</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5407,21 +5407,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385699</v>
+        <v>385609</v>
       </c>
       <c r="R44" t="n">
-        <v>6797223</v>
+        <v>6797178</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5491,22 +5491,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125014510</v>
+        <v>125006190</v>
       </c>
       <c r="B45" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5519,21 +5519,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5543,13 +5543,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385699</v>
+        <v>385871</v>
       </c>
       <c r="R45" t="n">
-        <v>6797223</v>
+        <v>6797143</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5603,22 +5603,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125009781</v>
+        <v>125012816</v>
       </c>
       <c r="B46" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5631,21 +5631,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5655,13 +5655,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385862</v>
+        <v>385738</v>
       </c>
       <c r="R46" t="n">
-        <v>6797329</v>
+        <v>6797251</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5715,22 +5715,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125015572</v>
+        <v>125008003</v>
       </c>
       <c r="B47" t="n">
-        <v>80028</v>
+        <v>79536</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5743,21 +5743,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5767,13 +5767,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385709</v>
+        <v>385900</v>
       </c>
       <c r="R47" t="n">
-        <v>6797118</v>
+        <v>6797194</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5827,19 +5827,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125010031</v>
+        <v>125013949</v>
       </c>
       <c r="B48" t="n">
         <v>78947</v>
@@ -5879,10 +5879,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>385750</v>
+        <v>385633</v>
       </c>
       <c r="R48" t="n">
-        <v>6797429</v>
+        <v>6797184</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5951,10 +5951,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125015299</v>
+        <v>125014342</v>
       </c>
       <c r="B49" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385588</v>
+        <v>385611</v>
       </c>
       <c r="R49" t="n">
-        <v>6797184</v>
+        <v>6797222</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6036,12 +6036,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6068,10 +6063,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125014685</v>
+        <v>125015299</v>
       </c>
       <c r="B50" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6084,37 +6079,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385571</v>
+        <v>385588</v>
       </c>
       <c r="R50" t="n">
-        <v>6797259</v>
+        <v>6797184</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6146,7 +6138,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6156,7 +6148,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6165,7 +6162,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6291,10 +6287,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125014307</v>
+        <v>125008520</v>
       </c>
       <c r="B52" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6307,21 +6303,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6331,10 +6327,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385616</v>
+        <v>385868</v>
       </c>
       <c r="R52" t="n">
-        <v>6797214</v>
+        <v>6797226</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6366,7 +6362,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6376,7 +6372,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6403,10 +6399,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125014853</v>
+        <v>125009952</v>
       </c>
       <c r="B53" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6419,21 +6415,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6443,13 +6439,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385539</v>
+        <v>385760</v>
       </c>
       <c r="R53" t="n">
-        <v>6797252</v>
+        <v>6797317</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6478,7 +6474,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6488,7 +6484,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6515,10 +6511,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125014588</v>
+        <v>125014307</v>
       </c>
       <c r="B54" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6531,21 +6527,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6555,10 +6551,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385586</v>
+        <v>385616</v>
       </c>
       <c r="R54" t="n">
-        <v>6797244</v>
+        <v>6797214</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6590,7 +6586,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6600,12 +6596,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6632,7 +6623,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125016771</v>
+        <v>125010560</v>
       </c>
       <c r="B55" t="n">
         <v>78947</v>
@@ -6672,10 +6663,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385674</v>
+        <v>385763</v>
       </c>
       <c r="R55" t="n">
-        <v>6796981</v>
+        <v>6797307</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6707,7 +6698,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6717,7 +6708,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6744,10 +6735,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125010269</v>
+        <v>125008506</v>
       </c>
       <c r="B56" t="n">
-        <v>80028</v>
+        <v>78683</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6760,21 +6751,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6784,13 +6775,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385756</v>
+        <v>385867</v>
       </c>
       <c r="R56" t="n">
-        <v>6797314</v>
+        <v>6797218</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6819,7 +6810,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6829,12 +6820,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6861,7 +6847,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125009952</v>
+        <v>125014588</v>
       </c>
       <c r="B57" t="n">
         <v>78947</v>
@@ -6901,13 +6887,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385760</v>
+        <v>385586</v>
       </c>
       <c r="R57" t="n">
-        <v>6797317</v>
+        <v>6797244</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6936,7 +6922,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6946,7 +6932,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6973,10 +6964,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125010793</v>
+        <v>125014700</v>
       </c>
       <c r="B58" t="n">
-        <v>98269</v>
+        <v>80056</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6985,25 +6976,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7013,10 +7004,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385779</v>
+        <v>385567</v>
       </c>
       <c r="R58" t="n">
-        <v>6797286</v>
+        <v>6797275</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7048,7 +7039,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7058,7 +7049,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7085,10 +7076,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125006056</v>
+        <v>125014685</v>
       </c>
       <c r="B59" t="n">
-        <v>56836</v>
+        <v>80028</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7097,35 +7088,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7133,13 +7119,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>385924</v>
+        <v>385571</v>
       </c>
       <c r="R59" t="n">
-        <v>6797115</v>
+        <v>6797259</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7168,7 +7154,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7178,7 +7164,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7187,6 +7173,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7205,10 +7192,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125014700</v>
+        <v>125016157</v>
       </c>
       <c r="B60" t="n">
-        <v>80056</v>
+        <v>80028</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7217,25 +7204,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7245,10 +7232,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385567</v>
+        <v>385706</v>
       </c>
       <c r="R60" t="n">
-        <v>6797275</v>
+        <v>6797113</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7280,7 +7267,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7290,7 +7277,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7317,10 +7304,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125014604</v>
+        <v>125014853</v>
       </c>
       <c r="B61" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7333,21 +7320,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7357,10 +7344,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385586</v>
+        <v>385539</v>
       </c>
       <c r="R61" t="n">
-        <v>6797242</v>
+        <v>6797252</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7392,7 +7379,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7402,7 +7389,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7429,10 +7416,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125008520</v>
+        <v>125010793</v>
       </c>
       <c r="B62" t="n">
-        <v>78684</v>
+        <v>98269</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7441,25 +7428,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7469,10 +7456,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385868</v>
+        <v>385779</v>
       </c>
       <c r="R62" t="n">
-        <v>6797226</v>
+        <v>6797286</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7504,7 +7491,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7514,7 +7501,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7541,10 +7528,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125015566</v>
+        <v>125014604</v>
       </c>
       <c r="B63" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7557,21 +7544,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7581,10 +7568,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385640</v>
+        <v>385586</v>
       </c>
       <c r="R63" t="n">
-        <v>6797141</v>
+        <v>6797242</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7616,7 +7603,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7626,7 +7613,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7653,10 +7640,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125014083</v>
+        <v>125010269</v>
       </c>
       <c r="B64" t="n">
-        <v>78979</v>
+        <v>80028</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7669,21 +7656,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7693,10 +7680,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385689</v>
+        <v>385756</v>
       </c>
       <c r="R64" t="n">
-        <v>6797223</v>
+        <v>6797314</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7728,7 +7715,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7738,7 +7725,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7765,10 +7757,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125016157</v>
+        <v>125014817</v>
       </c>
       <c r="B65" t="n">
-        <v>80028</v>
+        <v>80056</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7777,25 +7769,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7805,10 +7797,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385706</v>
+        <v>385541</v>
       </c>
       <c r="R65" t="n">
-        <v>6797113</v>
+        <v>6797264</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7840,7 +7832,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7850,7 +7842,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7877,10 +7874,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125011588</v>
+        <v>125014769</v>
       </c>
       <c r="B66" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7893,21 +7890,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7917,13 +7914,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>385737</v>
+        <v>385552</v>
       </c>
       <c r="R66" t="n">
-        <v>6797241</v>
+        <v>6797252</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7952,7 +7949,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7962,7 +7959,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Vid myr, källa?</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7989,10 +7991,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125014817</v>
+        <v>125014083</v>
       </c>
       <c r="B67" t="n">
-        <v>80056</v>
+        <v>78979</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8001,25 +8003,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6461</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8029,13 +8031,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385541</v>
+        <v>385689</v>
       </c>
       <c r="R67" t="n">
-        <v>6797264</v>
+        <v>6797223</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8064,7 +8066,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8074,12 +8076,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Vid myr, tjärn</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8106,10 +8103,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125008506</v>
+        <v>125016771</v>
       </c>
       <c r="B68" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8122,21 +8119,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8146,10 +8143,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>385867</v>
+        <v>385674</v>
       </c>
       <c r="R68" t="n">
-        <v>6797218</v>
+        <v>6796981</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -8181,7 +8178,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8191,7 +8188,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8218,10 +8215,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125014769</v>
+        <v>125015566</v>
       </c>
       <c r="B69" t="n">
-        <v>80028</v>
+        <v>78683</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8234,21 +8231,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8258,10 +8255,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385552</v>
+        <v>385640</v>
       </c>
       <c r="R69" t="n">
-        <v>6797252</v>
+        <v>6797141</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8293,7 +8290,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8303,12 +8300,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Vid myr, källa?</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8335,10 +8327,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125010560</v>
+        <v>125006056</v>
       </c>
       <c r="B70" t="n">
-        <v>78947</v>
+        <v>56836</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8347,41 +8339,49 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385763</v>
+        <v>385924</v>
       </c>
       <c r="R70" t="n">
-        <v>6797307</v>
+        <v>6797115</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8447,10 +8447,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125014342</v>
+        <v>125011588</v>
       </c>
       <c r="B71" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8463,21 +8463,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8487,13 +8487,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385611</v>
+        <v>385737</v>
       </c>
       <c r="R71" t="n">
-        <v>6797222</v>
+        <v>6797241</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -4159,10 +4159,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125009430</v>
+        <v>125013825</v>
       </c>
       <c r="B33" t="n">
-        <v>78947</v>
+        <v>80029</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4175,21 +4175,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385862</v>
+        <v>385689</v>
       </c>
       <c r="R33" t="n">
-        <v>6797329</v>
+        <v>6797243</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4271,10 +4271,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125015572</v>
+        <v>125009430</v>
       </c>
       <c r="B34" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385709</v>
+        <v>385862</v>
       </c>
       <c r="R34" t="n">
-        <v>6797118</v>
+        <v>6797329</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4383,10 +4383,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125013825</v>
+        <v>125015572</v>
       </c>
       <c r="B35" t="n">
-        <v>80029</v>
+        <v>80028</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4399,21 +4399,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385689</v>
+        <v>385709</v>
       </c>
       <c r="R35" t="n">
-        <v>6797243</v>
+        <v>6797118</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -6623,10 +6623,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125010560</v>
+        <v>125008506</v>
       </c>
       <c r="B55" t="n">
-        <v>78947</v>
+        <v>78683</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6639,21 +6639,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385763</v>
+        <v>385867</v>
       </c>
       <c r="R55" t="n">
-        <v>6797307</v>
+        <v>6797218</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6735,10 +6735,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125008506</v>
+        <v>125010560</v>
       </c>
       <c r="B56" t="n">
-        <v>78683</v>
+        <v>78947</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6751,21 +6751,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385867</v>
+        <v>385763</v>
       </c>
       <c r="R56" t="n">
-        <v>6797218</v>
+        <v>6797307</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125015797</v>
+        <v>125008543</v>
       </c>
       <c r="B18" t="n">
-        <v>80029</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,13 +2507,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385690</v>
+        <v>385867</v>
       </c>
       <c r="R18" t="n">
-        <v>6797129</v>
+        <v>6797219</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,22 +2567,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125008543</v>
+        <v>125015797</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>80029</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2595,21 +2595,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385867</v>
+        <v>385690</v>
       </c>
       <c r="R19" t="n">
-        <v>6797219</v>
+        <v>6797129</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2679,12 +2679,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 12426-2025 artfynd.xlsx
+++ b/artfynd/A 12426-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125004665</v>
+        <v>125004576</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125004345</v>
+        <v>125004665</v>
       </c>
       <c r="B3" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R3" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125004576</v>
+        <v>125004366</v>
       </c>
       <c r="B4" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79536</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R4" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,16 +996,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125004587</v>
+        <v>125004324</v>
       </c>
       <c r="B5" t="n">
         <v>78683</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>385935</v>
+        <v>385975</v>
       </c>
       <c r="R5" t="n">
-        <v>6796995</v>
+        <v>6797012</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125004324</v>
+        <v>125004345</v>
       </c>
       <c r="B6" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1198,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125004366</v>
+        <v>125004587</v>
       </c>
       <c r="B7" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78683</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>385975</v>
+        <v>385935</v>
       </c>
       <c r="R7" t="n">
-        <v>6797012</v>
+        <v>6796995</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,12 +1320,7 @@
         <v>125004325</v>
       </c>
       <c r="B8" t="n">
-        <v>78971</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78991</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125009781</v>
+        <v>125014757</v>
       </c>
       <c r="B9" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,13 +1459,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>385862</v>
+        <v>385618</v>
       </c>
       <c r="R9" t="n">
-        <v>6797329</v>
+        <v>6797202</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,27 +1519,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125011580</v>
+        <v>125015275</v>
       </c>
       <c r="B10" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1566,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>385738</v>
+        <v>385609</v>
       </c>
       <c r="R10" t="n">
-        <v>6797251</v>
+        <v>6797178</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,27 +1626,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125010604</v>
+        <v>125007590</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1649,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,13 +1673,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>385633</v>
+        <v>385922</v>
       </c>
       <c r="R11" t="n">
-        <v>6797363</v>
+        <v>6797211</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1758,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,28 +1733,23 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125013977</v>
+        <v>125008649</v>
       </c>
       <c r="B12" t="n">
         <v>78947</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1835,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>385623</v>
+        <v>385867</v>
       </c>
       <c r="R12" t="n">
-        <v>6797166</v>
+        <v>6797219</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1870,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125009311</v>
+        <v>125009359</v>
       </c>
       <c r="B13" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1863,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,13 +1887,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>385900</v>
+        <v>385862</v>
       </c>
       <c r="R13" t="n">
-        <v>6797194</v>
+        <v>6797329</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,27 +1947,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125016913</v>
+        <v>125014208</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,21 +1970,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,13 +1994,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>385697</v>
+        <v>385699</v>
       </c>
       <c r="R14" t="n">
-        <v>6796929</v>
+        <v>6797223</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,27 +2054,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125015401</v>
+        <v>125013825</v>
       </c>
       <c r="B15" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2147,21 +2077,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>385632</v>
+        <v>385689</v>
       </c>
       <c r="R15" t="n">
-        <v>6797173</v>
+        <v>6797243</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2206,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,15 +2173,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125014057</v>
+        <v>125009311</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78683</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2259,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>385607</v>
+        <v>385900</v>
       </c>
       <c r="R16" t="n">
-        <v>6797159</v>
+        <v>6797194</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2318,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2343,28 +2268,23 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125014510</v>
+        <v>125015390</v>
       </c>
       <c r="B17" t="n">
         <v>78684</v>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2395,13 +2315,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>385699</v>
+        <v>385632</v>
       </c>
       <c r="R17" t="n">
-        <v>6797223</v>
+        <v>6797173</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2440,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2455,27 +2375,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125008543</v>
+        <v>125010553</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,21 +2398,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,13 +2422,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>385867</v>
+        <v>385876</v>
       </c>
       <c r="R18" t="n">
-        <v>6797219</v>
+        <v>6797310</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,7 +2457,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2552,7 +2467,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2567,27 +2482,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125015797</v>
+        <v>125015347</v>
       </c>
       <c r="B19" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2595,21 +2505,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,13 +2529,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>385690</v>
+        <v>385592</v>
       </c>
       <c r="R19" t="n">
-        <v>6797129</v>
+        <v>6797161</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2654,7 +2564,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2664,7 +2574,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,15 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125010542</v>
+        <v>125011580</v>
       </c>
       <c r="B20" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,21 +2612,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,13 +2636,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>385634</v>
+        <v>385738</v>
       </c>
       <c r="R20" t="n">
-        <v>6797413</v>
+        <v>6797251</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2766,7 +2671,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2681,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2791,28 +2696,23 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125010031</v>
+        <v>125006076</v>
       </c>
       <c r="B21" t="n">
         <v>78947</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2843,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>385750</v>
+        <v>385896</v>
       </c>
       <c r="R21" t="n">
-        <v>6797429</v>
+        <v>6797101</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,7 +2778,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2888,7 +2788,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2903,74 +2803,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125014011</v>
+        <v>125009781</v>
       </c>
       <c r="B22" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78683</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>385610</v>
+        <v>385862</v>
       </c>
       <c r="R22" t="n">
-        <v>6797160</v>
+        <v>6797329</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3002,7 +2885,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3012,7 +2895,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3039,15 +2922,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125007590</v>
+        <v>125016913</v>
       </c>
       <c r="B23" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3055,21 +2933,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3079,13 +2957,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>385922</v>
+        <v>385697</v>
       </c>
       <c r="R23" t="n">
-        <v>6797211</v>
+        <v>6796929</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3114,7 +2992,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3124,7 +3002,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,28 +3017,23 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125014757</v>
+        <v>125008665</v>
       </c>
       <c r="B24" t="n">
         <v>78947</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3191,13 +3064,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>385618</v>
+        <v>385900</v>
       </c>
       <c r="R24" t="n">
-        <v>6797202</v>
+        <v>6797194</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3226,7 +3099,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3109,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3263,15 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125015347</v>
+        <v>125015273</v>
       </c>
       <c r="B25" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3279,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3303,13 +3171,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>385592</v>
+        <v>385579</v>
       </c>
       <c r="R25" t="n">
-        <v>6797161</v>
+        <v>6797173</v>
       </c>
       <c r="S25" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3338,7 +3206,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3348,7 +3216,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3375,15 +3243,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125010553</v>
+        <v>125010031</v>
       </c>
       <c r="B26" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3391,21 +3254,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3415,13 +3278,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>385876</v>
+        <v>385750</v>
       </c>
       <c r="R26" t="n">
-        <v>6797310</v>
+        <v>6797429</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3450,7 +3313,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3460,7 +3323,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,28 +3338,23 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125015297</v>
+        <v>125014057</v>
       </c>
       <c r="B27" t="n">
         <v>78947</v>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3527,13 +3385,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>385569</v>
+        <v>385607</v>
       </c>
       <c r="R27" t="n">
-        <v>6797152</v>
+        <v>6797159</v>
       </c>
       <c r="S27" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3562,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3572,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,27 +3445,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125008432</v>
+        <v>125013776</v>
       </c>
       <c r="B28" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3615,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3639,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>385888</v>
+        <v>385692</v>
       </c>
       <c r="R28" t="n">
-        <v>6797224</v>
+        <v>6797239</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3674,7 +3527,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,7 +3537,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3711,15 +3564,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125014812</v>
+        <v>125010604</v>
       </c>
       <c r="B29" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,21 +3575,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3751,13 +3599,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>385618</v>
+        <v>385633</v>
       </c>
       <c r="R29" t="n">
-        <v>6797202</v>
+        <v>6797363</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3786,7 +3634,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3796,7 +3644,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,28 +3659,23 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125013776</v>
+        <v>125015572</v>
       </c>
       <c r="B30" t="n">
         <v>80028</v>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3863,10 +3706,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>385692</v>
+        <v>385709</v>
       </c>
       <c r="R30" t="n">
-        <v>6797239</v>
+        <v>6797118</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3898,7 +3741,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3908,7 +3751,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3935,15 +3778,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125014099</v>
+        <v>125010542</v>
       </c>
       <c r="B31" t="n">
-        <v>78979</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78683</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3951,21 +3789,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3975,13 +3813,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>385699</v>
+        <v>385634</v>
       </c>
       <c r="R31" t="n">
-        <v>6797223</v>
+        <v>6797413</v>
       </c>
       <c r="S31" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4010,7 +3848,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4020,7 +3858,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4035,27 +3873,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125015390</v>
+        <v>125008432</v>
       </c>
       <c r="B32" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4063,21 +3896,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4087,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>385632</v>
+        <v>385888</v>
       </c>
       <c r="R32" t="n">
-        <v>6797173</v>
+        <v>6797224</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -4122,7 +3955,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4132,7 +3965,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4159,16 +3992,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125013825</v>
+        <v>125009342</v>
       </c>
       <c r="B33" t="n">
         <v>80029</v>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4199,10 +4027,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>385689</v>
+        <v>385861</v>
       </c>
       <c r="R33" t="n">
-        <v>6797243</v>
+        <v>6797324</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4234,7 +4062,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4244,7 +4072,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4271,16 +4099,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125009430</v>
+        <v>125010000</v>
       </c>
       <c r="B34" t="n">
         <v>78947</v>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4311,10 +4134,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>385862</v>
+        <v>385749</v>
       </c>
       <c r="R34" t="n">
-        <v>6797329</v>
+        <v>6797429</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4346,7 +4169,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4356,7 +4179,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4383,15 +4206,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125015572</v>
+        <v>125012816</v>
       </c>
       <c r="B35" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4399,21 +4217,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4423,13 +4241,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>385709</v>
+        <v>385738</v>
       </c>
       <c r="R35" t="n">
-        <v>6797118</v>
+        <v>6797251</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4458,7 +4276,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4468,7 +4286,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,27 +4301,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125010000</v>
+        <v>125015797</v>
       </c>
       <c r="B36" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4511,21 +4324,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4535,13 +4348,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>385749</v>
+        <v>385690</v>
       </c>
       <c r="R36" t="n">
-        <v>6797429</v>
+        <v>6797129</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4570,7 +4383,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4580,7 +4393,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4595,27 +4408,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125009359</v>
+        <v>125006190</v>
       </c>
       <c r="B37" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4623,21 +4431,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4647,10 +4455,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>385862</v>
+        <v>385871</v>
       </c>
       <c r="R37" t="n">
-        <v>6797329</v>
+        <v>6797143</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4682,7 +4490,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4692,7 +4500,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4719,15 +4527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125006076</v>
+        <v>125014812</v>
       </c>
       <c r="B38" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4735,21 +4538,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,13 +4562,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>385896</v>
+        <v>385618</v>
       </c>
       <c r="R38" t="n">
-        <v>6797101</v>
+        <v>6797202</v>
       </c>
       <c r="S38" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4794,7 +4597,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4804,7 +4607,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4831,16 +4634,11 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125016946</v>
+        <v>125013977</v>
       </c>
       <c r="B39" t="n">
         <v>78947</v>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>NT</t>
@@ -4871,10 +4669,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>385697</v>
+        <v>385623</v>
       </c>
       <c r="R39" t="n">
-        <v>6796899</v>
+        <v>6797166</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4906,7 +4704,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4916,7 +4714,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4943,15 +4741,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125009342</v>
+        <v>125015297</v>
       </c>
       <c r="B40" t="n">
-        <v>80029</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4959,21 +4752,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4983,13 +4776,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>385861</v>
+        <v>385569</v>
       </c>
       <c r="R40" t="n">
-        <v>6797324</v>
+        <v>6797152</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5018,7 +4811,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5028,7 +4821,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,27 +4836,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125008665</v>
+        <v>125015401</v>
       </c>
       <c r="B41" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78683</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5071,21 +4859,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5095,13 +4883,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>385900</v>
+        <v>385632</v>
       </c>
       <c r="R41" t="n">
-        <v>6797194</v>
+        <v>6797173</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5130,7 +4918,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5140,7 +4928,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,27 +4943,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125015273</v>
+        <v>125014099</v>
       </c>
       <c r="B42" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78979</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5183,21 +4966,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5207,13 +4990,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>385579</v>
+        <v>385699</v>
       </c>
       <c r="R42" t="n">
-        <v>6797173</v>
+        <v>6797223</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5242,7 +5025,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5252,7 +5035,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5279,53 +5062,60 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125014208</v>
+        <v>125014011</v>
       </c>
       <c r="B43" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56836</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>385699</v>
+        <v>385610</v>
       </c>
       <c r="R43" t="n">
-        <v>6797223</v>
+        <v>6797160</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5354,7 +5144,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5364,7 +5154,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5379,27 +5169,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125015275</v>
+        <v>125008003</v>
       </c>
       <c r="B44" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79536</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5407,21 +5192,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5431,13 +5216,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>385609</v>
+        <v>385900</v>
       </c>
       <c r="R44" t="n">
-        <v>6797178</v>
+        <v>6797194</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5466,7 +5251,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5476,7 +5261,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5491,28 +5276,23 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125006190</v>
+        <v>125016946</v>
       </c>
       <c r="B45" t="n">
         <v>78947</v>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5543,10 +5323,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>385871</v>
+        <v>385697</v>
       </c>
       <c r="R45" t="n">
-        <v>6797143</v>
+        <v>6796899</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5578,7 +5358,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5588,7 +5368,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5615,16 +5395,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125012816</v>
+        <v>125009430</v>
       </c>
       <c r="B46" t="n">
         <v>78947</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5655,13 +5430,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>385738</v>
+        <v>385862</v>
       </c>
       <c r="R46" t="n">
-        <v>6797251</v>
+        <v>6797329</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5690,7 +5465,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5700,7 +5475,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5715,27 +5490,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125008003</v>
+        <v>125014510</v>
       </c>
       <c r="B47" t="n">
-        <v>79536</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78684</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5743,21 +5513,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5767,13 +5537,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>385900</v>
+        <v>385699</v>
       </c>
       <c r="R47" t="n">
-        <v>6797194</v>
+        <v>6797223</v>
       </c>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5802,7 +5572,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5812,7 +5582,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5844,11 +5614,6 @@
       <c r="B48" t="n">
         <v>78947</v>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5951,15 +5716,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125014342</v>
+        <v>125014083</v>
       </c>
       <c r="B49" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78999</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5967,21 +5727,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5991,13 +5751,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>385611</v>
+        <v>385689</v>
       </c>
       <c r="R49" t="n">
-        <v>6797222</v>
+        <v>6797223</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6026,7 +5786,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6036,7 +5796,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6063,37 +5823,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125015299</v>
+        <v>125014700</v>
       </c>
       <c r="B50" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80098</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6103,10 +5858,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>385588</v>
+        <v>385567</v>
       </c>
       <c r="R50" t="n">
-        <v>6797184</v>
+        <v>6797275</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6138,7 +5893,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6148,12 +5903,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6180,54 +5930,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125074279</v>
+        <v>125014588</v>
       </c>
       <c r="B51" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sätern, Dlr</t>
+          <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>385755</v>
+        <v>385586</v>
       </c>
       <c r="R51" t="n">
-        <v>6797321</v>
+        <v>6797244</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6257,18 +5998,32 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6280,22 +6035,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
+          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125008520</v>
+        <v>125009952</v>
       </c>
       <c r="B52" t="n">
-        <v>78684</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6303,21 +6053,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6327,13 +6077,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>385868</v>
+        <v>385760</v>
       </c>
       <c r="R52" t="n">
-        <v>6797226</v>
+        <v>6797317</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6362,7 +6112,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6372,7 +6122,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6399,15 +6149,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125009952</v>
+        <v>125014307</v>
       </c>
       <c r="B53" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6415,21 +6160,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6439,13 +6184,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>385760</v>
+        <v>385616</v>
       </c>
       <c r="R53" t="n">
-        <v>6797317</v>
+        <v>6797214</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6474,7 +6219,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6484,7 +6229,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6511,50 +6256,49 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125014307</v>
+        <v>125074279</v>
       </c>
       <c r="B54" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sätern, Sätern, Dlr</t>
+          <t>Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>385616</v>
+        <v>385755</v>
       </c>
       <c r="R54" t="n">
-        <v>6797214</v>
+        <v>6797321</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6584,27 +6328,18 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6616,22 +6351,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Rastad, Anna-Britt Olsson, Göran Ehn, Lisa Olson</t>
+          <t>Cecilia Rastad, Göran Ehn, Anna-Britt Olsson, Lisa Olson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125008506</v>
+        <v>125015299</v>
       </c>
       <c r="B55" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6639,21 +6369,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6663,10 +6393,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>385867</v>
+        <v>385588</v>
       </c>
       <c r="R55" t="n">
-        <v>6797218</v>
+        <v>6797184</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6698,7 +6428,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6708,7 +6438,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt i en fin skog där skogsmaskinerna nu närmar sig från två håll. Rikligt med brandspår på stubbar, dimensionsavverkade för länge sedan.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6735,15 +6470,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125010560</v>
+        <v>125011588</v>
       </c>
       <c r="B56" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6775,13 +6505,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>385763</v>
+        <v>385737</v>
       </c>
       <c r="R56" t="n">
-        <v>6797307</v>
+        <v>6797241</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6810,7 +6540,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6820,7 +6550,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6847,15 +6577,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125014588</v>
+        <v>125010560</v>
       </c>
       <c r="B57" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6887,10 +6612,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>385586</v>
+        <v>385763</v>
       </c>
       <c r="R57" t="n">
-        <v>6797244</v>
+        <v>6797307</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6922,7 +6647,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6932,12 +6657,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6964,15 +6684,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125014700</v>
+        <v>125006056</v>
       </c>
       <c r="B58" t="n">
-        <v>80056</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6980,37 +6695,45 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6461</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>385567</v>
+        <v>385924</v>
       </c>
       <c r="R58" t="n">
-        <v>6797275</v>
+        <v>6797115</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7039,7 +6762,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7049,7 +6772,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7079,12 +6802,7 @@
         <v>125014685</v>
       </c>
       <c r="B59" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7192,15 +6910,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125016157</v>
+        <v>125010269</v>
       </c>
       <c r="B60" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7232,13 +6945,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>385706</v>
+        <v>385756</v>
       </c>
       <c r="R60" t="n">
-        <v>6797113</v>
+        <v>6797314</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7267,7 +6980,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7277,7 +6990,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal sälg</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7304,15 +7022,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125014853</v>
+        <v>125016157</v>
       </c>
       <c r="B61" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,10 +7057,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>385539</v>
+        <v>385706</v>
       </c>
       <c r="R61" t="n">
-        <v>6797252</v>
+        <v>6797113</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7379,7 +7092,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7389,7 +7102,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7416,37 +7129,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125010793</v>
+        <v>125014604</v>
       </c>
       <c r="B62" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7456,10 +7164,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>385779</v>
+        <v>385586</v>
       </c>
       <c r="R62" t="n">
-        <v>6797286</v>
+        <v>6797242</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7491,7 +7199,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7501,7 +7209,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7528,15 +7236,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125014604</v>
+        <v>125008506</v>
       </c>
       <c r="B63" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7544,21 +7247,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7568,10 +7271,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>385586</v>
+        <v>385867</v>
       </c>
       <c r="R63" t="n">
-        <v>6797242</v>
+        <v>6797218</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7603,7 +7306,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7613,7 +7316,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7640,15 +7343,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125010269</v>
+        <v>125014853</v>
       </c>
       <c r="B64" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7680,13 +7378,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>385756</v>
+        <v>385539</v>
       </c>
       <c r="R64" t="n">
-        <v>6797314</v>
+        <v>6797252</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7715,7 +7413,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7725,12 +7423,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:45</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal sälg</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7757,37 +7450,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125014817</v>
+        <v>125010793</v>
       </c>
       <c r="B65" t="n">
-        <v>80056</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7797,10 +7485,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>385541</v>
+        <v>385779</v>
       </c>
       <c r="R65" t="n">
-        <v>6797264</v>
+        <v>6797286</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7832,7 +7520,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7842,12 +7530,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:05</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Vid myr, tjärn</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7877,12 +7560,7 @@
         <v>125014769</v>
       </c>
       <c r="B66" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7991,37 +7669,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125014083</v>
+        <v>125014817</v>
       </c>
       <c r="B67" t="n">
-        <v>78979</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80098</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6461</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8031,13 +7704,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>385689</v>
+        <v>385541</v>
       </c>
       <c r="R67" t="n">
-        <v>6797223</v>
+        <v>6797264</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8066,7 +7739,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8076,7 +7749,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Vid myr, tjärn</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8106,12 +7784,7 @@
         <v>125016771</v>
       </c>
       <c r="B68" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8215,15 +7888,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125015566</v>
+        <v>125008520</v>
       </c>
       <c r="B69" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8231,21 +7899,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8255,10 +7923,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>385640</v>
+        <v>385868</v>
       </c>
       <c r="R69" t="n">
-        <v>6797141</v>
+        <v>6797226</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -8290,7 +7958,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8300,7 +7968,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8327,61 +7995,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125006056</v>
+        <v>125014342</v>
       </c>
       <c r="B70" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78726</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sätern, Sätern, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>385924</v>
+        <v>385611</v>
       </c>
       <c r="R70" t="n">
-        <v>6797115</v>
+        <v>6797222</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8410,7 +8065,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8420,7 +8075,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8447,15 +8102,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125011588</v>
+        <v>125015566</v>
       </c>
       <c r="B71" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8463,21 +8113,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8487,13 +8137,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>385737</v>
+        <v>385640</v>
       </c>
       <c r="R71" t="n">
-        <v>6797241</v>
+        <v>6797141</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8522,7 +8172,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8532,7 +8182,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD71" t="b">
